--- a/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D70B213-23B7-4855-9B8C-29BBC3080CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C5C4E4-D1D2-4F12-9ABA-762D4569B3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="10" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8891" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8891" uniqueCount="1029">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -3144,12 +3144,6 @@
     <t>NBR.Temáticas</t>
   </si>
   <si>
-    <t>[ OST_Materials ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ IfcMaterial ] </t>
-  </si>
-  <si>
     <t>[ - ]</t>
   </si>
   <si>
@@ -3165,16 +3159,25 @@
     <t>[ OST_Rooms : OST_MEPSpaces : OST_MEPSystemZone ]</t>
   </si>
   <si>
-    <t>[ IfcSpace ]</t>
-  </si>
-  <si>
-    <t>[ IfcProperty ]</t>
-  </si>
-  <si>
     <t>[ OST_Sheets : OST_TitleBlocks : OST_Revisions : OST_RevisionNumberingSequences ]</t>
   </si>
   <si>
     <t>[ IfcAnnotation ]</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_MaterialTags ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial : IfcText : IfcLabel : IfcMaterialRelationship ]</t>
+  </si>
+  <si>
+    <t>[ BuiltInParameter ]</t>
+  </si>
+  <si>
+    <t>[ IfcProperty : IfcIdentifier : IfcText ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
   </si>
 </sst>
 </file>
@@ -3737,7 +3740,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{001CC4A1-5641-437E-9DC4-857BB9658EC6}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
     <dxf>
       <font>
         <b val="0"/>
@@ -3815,6 +3818,13 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -4163,14 +4173,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B80B61-09F0-4F35-A733-85777283AFC6}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="56.6640625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="56.69921875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" customWidth="1"/>
-    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="1" max="1" width="11.19921875" customWidth="1"/>
+    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -4181,7 +4191,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>320</v>
       </c>
@@ -4192,7 +4202,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>321</v>
       </c>
@@ -4203,7 +4213,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4214,7 +4224,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -4226,7 +4236,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -4238,7 +4248,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4249,7 +4259,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
         <v>9</v>
       </c>
@@ -4260,7 +4270,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>322</v>
       </c>
@@ -4271,7 +4281,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>324</v>
       </c>
@@ -4282,7 +4292,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>325</v>
       </c>
@@ -4293,7 +4303,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -4304,7 +4314,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>326</v>
       </c>
@@ -4315,7 +4325,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>327</v>
       </c>
@@ -4326,7 +4336,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>328</v>
       </c>
@@ -4337,7 +4347,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>329</v>
       </c>
@@ -4348,7 +4358,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -4359,19 +4369,19 @@
         <v>704</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B18" s="38">
         <f ca="1">NOW()</f>
-        <v>46244.497776041666</v>
+        <v>46249.323895486108</v>
       </c>
       <c r="C18" s="37" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>713</v>
       </c>
@@ -4382,7 +4392,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34" t="s">
         <v>708</v>
       </c>
@@ -4394,7 +4404,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>714</v>
       </c>
@@ -4406,7 +4416,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34" t="s">
         <v>319</v>
       </c>
@@ -4417,7 +4427,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>331</v>
       </c>
@@ -4428,7 +4438,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>336</v>
       </c>
@@ -4439,7 +4449,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>338</v>
       </c>
@@ -4450,7 +4460,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34" t="s">
         <v>700</v>
       </c>
@@ -4461,7 +4471,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34" t="s">
         <v>988</v>
       </c>
@@ -4472,7 +4482,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34" t="s">
         <v>990</v>
       </c>
@@ -4483,7 +4493,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34" t="s">
         <v>992</v>
       </c>
@@ -4494,7 +4504,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="34" t="s">
         <v>994</v>
       </c>
@@ -4505,7 +4515,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="34" t="s">
         <v>996</v>
       </c>
@@ -4516,7 +4526,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="34" t="s">
         <v>998</v>
       </c>
@@ -4527,7 +4537,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="34" t="s">
         <v>1000</v>
       </c>
@@ -4538,7 +4548,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="34" t="s">
         <v>1002</v>
       </c>
@@ -4549,7 +4559,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="34" t="s">
         <v>1004</v>
       </c>
@@ -4560,7 +4570,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="34" t="s">
         <v>1006</v>
       </c>
@@ -4571,7 +4581,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="34" t="s">
         <v>1008</v>
       </c>
@@ -4582,7 +4592,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>1010</v>
       </c>
@@ -4593,7 +4603,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="34" t="s">
         <v>1012</v>
       </c>
@@ -4620,34 +4630,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFFE5C0-D3D8-4876-B71B-E260AD929073}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA47"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.5" style="39" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" style="66" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" style="66" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="66" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="66" customWidth="1"/>
-    <col min="6" max="6" width="15" style="66" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="66" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" style="39" customWidth="1"/>
-    <col min="13" max="13" width="8.6640625" style="39" customWidth="1"/>
-    <col min="14" max="14" width="8.83203125" style="39" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="62" style="39" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="68.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.83203125" style="66" customWidth="1"/>
-    <col min="19" max="19" width="7" style="39" customWidth="1"/>
-    <col min="20" max="20" width="8.83203125" style="39" customWidth="1"/>
-    <col min="21" max="21" width="8.5" style="39" customWidth="1"/>
-    <col min="22" max="22" width="9.1640625" style="39" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" style="66" customWidth="1"/>
-    <col min="24" max="24" width="31" style="39" customWidth="1"/>
-    <col min="25" max="26" width="8.83203125" style="39"/>
-    <col min="27" max="27" width="64.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.83203125" style="39"/>
+    <col min="1" max="1" width="1.8984375" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="66" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.09765625" style="66" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.8984375" style="66" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.59765625" style="66" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="66" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.3984375" style="66" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.8984375" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.59765625" style="39" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="39" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="62.296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.69921875" style="39" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.796875" style="66" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.09765625" style="39" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.8984375" style="39" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.59765625" style="39" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.796875" style="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5" style="66" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.8984375" style="39" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="36.09765625" style="39" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.59765625" style="39" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="57" style="39" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.796875" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>649</v>
       </c>
@@ -4730,7 +4741,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48">
         <v>2</v>
       </c>
@@ -4809,10 +4820,10 @@
         <v>Key-ABNT-2</v>
       </c>
       <c r="X2" s="33" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="Y2" s="33" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="Z2" s="33" t="s">
         <v>717</v>
@@ -4821,7 +4832,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="48">
         <v>3</v>
       </c>
@@ -4900,10 +4911,10 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="X3" s="33" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="Y3" s="33" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="Z3" s="33" t="s">
         <v>718</v>
@@ -4912,7 +4923,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="48">
         <v>4</v>
       </c>
@@ -4991,10 +5002,10 @@
         <v>Key-ABNT-4</v>
       </c>
       <c r="X4" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y4" s="33" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="Z4" s="33" t="s">
         <v>719</v>
@@ -5003,7 +5014,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="48">
         <v>5</v>
       </c>
@@ -5082,10 +5093,10 @@
         <v>Key-ABNT-5</v>
       </c>
       <c r="X5" s="33" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="Y5" s="33" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="Z5" s="33" t="s">
         <v>720</v>
@@ -5094,7 +5105,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="48">
         <v>6</v>
       </c>
@@ -5173,10 +5184,10 @@
         <v>Key-ABNT-6</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="Z6" s="33" t="s">
         <v>721</v>
@@ -5185,7 +5196,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="7" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="48">
         <v>7</v>
       </c>
@@ -5264,10 +5275,10 @@
         <v>Key-ABNT-7</v>
       </c>
       <c r="X7" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y7" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z7" s="33" t="s">
         <v>722</v>
@@ -5276,7 +5287,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="8" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="48">
         <v>8</v>
       </c>
@@ -5355,10 +5366,10 @@
         <v>Key-ABNT-8</v>
       </c>
       <c r="X8" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y8" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z8" s="33" t="s">
         <v>723</v>
@@ -5367,7 +5378,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="9" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="48">
         <v>9</v>
       </c>
@@ -5446,10 +5457,10 @@
         <v>Key-ABNT-9</v>
       </c>
       <c r="X9" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y9" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z9" s="33" t="s">
         <v>724</v>
@@ -5458,7 +5469,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="10" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48">
         <v>10</v>
       </c>
@@ -5537,10 +5548,10 @@
         <v>Key-ABNT-10</v>
       </c>
       <c r="X10" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y10" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z10" s="33" t="s">
         <v>725</v>
@@ -5549,7 +5560,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="11" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="48">
         <v>11</v>
       </c>
@@ -5628,10 +5639,10 @@
         <v>Key-ABNT-11</v>
       </c>
       <c r="X11" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y11" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z11" s="33" t="s">
         <v>341</v>
@@ -5640,7 +5651,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="12" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48">
         <v>12</v>
       </c>
@@ -5719,10 +5730,10 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="X12" s="33" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="Y12" s="33" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="Z12" s="33" t="s">
         <v>726</v>
@@ -5731,7 +5742,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="13" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="48">
         <v>13</v>
       </c>
@@ -5810,10 +5821,10 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="X13" s="33" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="Y13" s="33" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="Z13" s="33" t="s">
         <v>727</v>
@@ -5822,7 +5833,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="14" spans="1:27" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="48">
         <v>14</v>
       </c>
@@ -5901,10 +5912,10 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="X14" s="67" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="Y14" s="68" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="Z14" s="33" t="s">
         <v>728</v>
@@ -5913,7 +5924,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="48">
         <v>15</v>
       </c>
@@ -5992,10 +6003,10 @@
         <v>Key-ABNT-15</v>
       </c>
       <c r="X15" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y15" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z15" s="55" t="s">
         <v>802</v>
@@ -6004,7 +6015,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="48">
         <v>16</v>
       </c>
@@ -6083,10 +6094,10 @@
         <v>Key-ABNT-16</v>
       </c>
       <c r="X16" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y16" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z16" s="55" t="s">
         <v>803</v>
@@ -6095,7 +6106,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48">
         <v>17</v>
       </c>
@@ -6174,10 +6185,10 @@
         <v>Key-ABNT-17</v>
       </c>
       <c r="X17" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y17" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z17" s="55" t="s">
         <v>804</v>
@@ -6186,7 +6197,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="48">
         <v>18</v>
       </c>
@@ -6265,10 +6276,10 @@
         <v>Key-ABNT-18</v>
       </c>
       <c r="X18" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y18" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z18" s="55" t="s">
         <v>805</v>
@@ -6277,7 +6288,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48">
         <v>19</v>
       </c>
@@ -6356,10 +6367,10 @@
         <v>Key-ABNT-19</v>
       </c>
       <c r="X19" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y19" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z19" s="55" t="s">
         <v>806</v>
@@ -6368,7 +6379,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="48">
         <v>20</v>
       </c>
@@ -6447,10 +6458,10 @@
         <v>Key-ABNT-20</v>
       </c>
       <c r="X20" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y20" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z20" s="55" t="s">
         <v>807</v>
@@ -6459,7 +6470,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48">
         <v>21</v>
       </c>
@@ -6538,10 +6549,10 @@
         <v>Key-ABNT-21</v>
       </c>
       <c r="X21" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y21" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z21" s="55" t="s">
         <v>808</v>
@@ -6550,7 +6561,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48">
         <v>22</v>
       </c>
@@ -6629,10 +6640,10 @@
         <v>Key-ABNT-22</v>
       </c>
       <c r="X22" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y22" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z22" s="55" t="s">
         <v>809</v>
@@ -6641,7 +6652,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="48">
         <v>23</v>
       </c>
@@ -6720,10 +6731,10 @@
         <v>Key-ABNT-23</v>
       </c>
       <c r="X23" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y23" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z23" s="55" t="s">
         <v>810</v>
@@ -6732,7 +6743,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="48">
         <v>24</v>
       </c>
@@ -6811,10 +6822,10 @@
         <v>Key-ABNT-24</v>
       </c>
       <c r="X24" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y24" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z24" s="55" t="s">
         <v>811</v>
@@ -6823,7 +6834,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="48">
         <v>25</v>
       </c>
@@ -6902,10 +6913,10 @@
         <v>Key-ABNT-25</v>
       </c>
       <c r="X25" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y25" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z25" s="55" t="s">
         <v>812</v>
@@ -6914,7 +6925,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="48">
         <v>26</v>
       </c>
@@ -6993,10 +7004,10 @@
         <v>Key-ABNT-26</v>
       </c>
       <c r="X26" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y26" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z26" s="55" t="s">
         <v>813</v>
@@ -7005,7 +7016,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="48">
         <v>27</v>
       </c>
@@ -7084,10 +7095,10 @@
         <v>Key-ABNT-27</v>
       </c>
       <c r="X27" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y27" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z27" s="55" t="s">
         <v>814</v>
@@ -7096,7 +7107,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="48">
         <v>28</v>
       </c>
@@ -7175,10 +7186,10 @@
         <v>Key-ABNT-28</v>
       </c>
       <c r="X28" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y28" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z28" s="55" t="s">
         <v>815</v>
@@ -7187,7 +7198,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="48">
         <v>29</v>
       </c>
@@ -7266,10 +7277,10 @@
         <v>Key-ABNT-29</v>
       </c>
       <c r="X29" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y29" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z29" s="55" t="s">
         <v>816</v>
@@ -7278,7 +7289,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="48">
         <v>30</v>
       </c>
@@ -7357,10 +7368,10 @@
         <v>Key-ABNT-30</v>
       </c>
       <c r="X30" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y30" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z30" s="55" t="s">
         <v>817</v>
@@ -7369,7 +7380,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="48">
         <v>31</v>
       </c>
@@ -7448,10 +7459,10 @@
         <v>Key-ABNT-31</v>
       </c>
       <c r="X31" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y31" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z31" s="55" t="s">
         <v>818</v>
@@ -7460,7 +7471,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="48">
         <v>32</v>
       </c>
@@ -7539,10 +7550,10 @@
         <v>Key-ABNT-32</v>
       </c>
       <c r="X32" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y32" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z32" s="55" t="s">
         <v>819</v>
@@ -7551,7 +7562,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="48">
         <v>33</v>
       </c>
@@ -7630,10 +7641,10 @@
         <v>Key-ABNT-33</v>
       </c>
       <c r="X33" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y33" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z33" s="55" t="s">
         <v>820</v>
@@ -7642,7 +7653,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="48">
         <v>34</v>
       </c>
@@ -7721,10 +7732,10 @@
         <v>Key-ABNT-34</v>
       </c>
       <c r="X34" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y34" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z34" s="55" t="s">
         <v>821</v>
@@ -7733,7 +7744,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="48">
         <v>35</v>
       </c>
@@ -7812,10 +7823,10 @@
         <v>Key-ABNT-35</v>
       </c>
       <c r="X35" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y35" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z35" s="55" t="s">
         <v>822</v>
@@ -7824,7 +7835,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="48">
         <v>36</v>
       </c>
@@ -7903,10 +7914,10 @@
         <v>Key-ABNT-36</v>
       </c>
       <c r="X36" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y36" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z36" s="55" t="s">
         <v>823</v>
@@ -7915,7 +7926,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="48">
         <v>37</v>
       </c>
@@ -7994,10 +8005,10 @@
         <v>Key-ABNT-37</v>
       </c>
       <c r="X37" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y37" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z37" s="55" t="s">
         <v>824</v>
@@ -8006,7 +8017,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="48">
         <v>38</v>
       </c>
@@ -8085,10 +8096,10 @@
         <v>Key-ABNT-38</v>
       </c>
       <c r="X38" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y38" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z38" s="55" t="s">
         <v>825</v>
@@ -8097,7 +8108,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="48">
         <v>39</v>
       </c>
@@ -8176,10 +8187,10 @@
         <v>Key-ABNT-39</v>
       </c>
       <c r="X39" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y39" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z39" s="55" t="s">
         <v>826</v>
@@ -8188,7 +8199,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="48">
         <v>40</v>
       </c>
@@ -8267,10 +8278,10 @@
         <v>Key-ABNT-40</v>
       </c>
       <c r="X40" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y40" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z40" s="55" t="s">
         <v>827</v>
@@ -8279,7 +8290,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="48">
         <v>41</v>
       </c>
@@ -8358,10 +8369,10 @@
         <v>Key-ABNT-41</v>
       </c>
       <c r="X41" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y41" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z41" s="55" t="s">
         <v>828</v>
@@ -8370,7 +8381,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="48">
         <v>42</v>
       </c>
@@ -8449,10 +8460,10 @@
         <v>Key-ABNT-42</v>
       </c>
       <c r="X42" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y42" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z42" s="55" t="s">
         <v>829</v>
@@ -8461,7 +8472,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="48">
         <v>43</v>
       </c>
@@ -8540,10 +8551,10 @@
         <v>Key-ABNT-43</v>
       </c>
       <c r="X43" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y43" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z43" s="55" t="s">
         <v>830</v>
@@ -8552,7 +8563,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="48">
         <v>44</v>
       </c>
@@ -8631,10 +8642,10 @@
         <v>Key-ABNT-44</v>
       </c>
       <c r="X44" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y44" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z44" s="55" t="s">
         <v>831</v>
@@ -8643,7 +8654,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="48">
         <v>45</v>
       </c>
@@ -8722,10 +8733,10 @@
         <v>Key-ABNT-45</v>
       </c>
       <c r="X45" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y45" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z45" s="55" t="s">
         <v>832</v>
@@ -8734,7 +8745,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="48">
         <v>46</v>
       </c>
@@ -8813,10 +8824,10 @@
         <v>Key-ABNT-46</v>
       </c>
       <c r="X46" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y46" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z46" s="55" t="s">
         <v>833</v>
@@ -8825,7 +8836,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="48">
         <v>47</v>
       </c>
@@ -8904,10 +8915,10 @@
         <v>Key-ABNT-47</v>
       </c>
       <c r="X47" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Y47" s="33" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z47" s="55" t="s">
         <v>834</v>
@@ -8918,14 +8929,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y2">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z15:AA47">
-    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA14 A2:B47">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8940,13 +8956,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B5591C-1220-489B-957E-6F42AD7CFACA}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>650</v>
       </c>
@@ -9011,7 +9027,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -9093,13 +9109,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26462613-E7D7-4ABD-BD2B-4B8A0B104ED0}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="26">
         <v>1</v>
       </c>
@@ -9110,7 +9126,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="17">
         <v>2</v>
       </c>
@@ -9135,35 +9151,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4160801D-A855-4DB1-BB60-92D2B856BA2E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AA303"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.69921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="47" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" style="47" customWidth="1"/>
+    <col min="7" max="7" width="9.296875" style="47" customWidth="1"/>
     <col min="8" max="8" width="5" style="47" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.69921875" style="47" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" style="47" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.1640625" style="47" customWidth="1"/>
+    <col min="11" max="11" width="9.19921875" style="47" customWidth="1"/>
     <col min="12" max="12" width="6.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="25.33203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="25.296875" style="1" customWidth="1"/>
     <col min="14" max="14" width="7" style="47" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="82.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.83203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="82.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.796875" style="1" customWidth="1"/>
     <col min="17" max="17" width="4.5" style="1" customWidth="1"/>
     <col min="18" max="18" width="6.5" style="1" customWidth="1"/>
     <col min="19" max="19" width="4.5" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.33203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" style="1" customWidth="1"/>
-    <col min="22" max="26" width="5.1640625" style="47" customWidth="1"/>
-    <col min="27" max="27" width="4.33203125" style="47" customWidth="1"/>
-    <col min="28" max="16384" width="9.1640625" style="1"/>
+    <col min="20" max="20" width="6.296875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="5.69921875" style="1" customWidth="1"/>
+    <col min="22" max="26" width="5.19921875" style="47" customWidth="1"/>
+    <col min="27" max="27" width="4.296875" style="47" customWidth="1"/>
+    <col min="28" max="16384" width="9.19921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>333</v>
       </c>
@@ -9246,7 +9262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -9329,7 +9345,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -9412,7 +9428,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>4</v>
       </c>
@@ -9495,7 +9511,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>5</v>
       </c>
@@ -9578,7 +9594,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>6</v>
       </c>
@@ -9661,7 +9677,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>7</v>
       </c>
@@ -9744,7 +9760,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>8</v>
       </c>
@@ -9827,7 +9843,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>9</v>
       </c>
@@ -9910,7 +9926,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>10</v>
       </c>
@@ -9993,7 +10009,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>11</v>
       </c>
@@ -10076,7 +10092,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>12</v>
       </c>
@@ -10159,7 +10175,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>13</v>
       </c>
@@ -10242,7 +10258,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>14</v>
       </c>
@@ -10325,7 +10341,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>15</v>
       </c>
@@ -10408,7 +10424,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>16</v>
       </c>
@@ -10491,7 +10507,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>17</v>
       </c>
@@ -10574,7 +10590,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>18</v>
       </c>
@@ -10657,7 +10673,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>19</v>
       </c>
@@ -10740,7 +10756,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>20</v>
       </c>
@@ -10823,7 +10839,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>21</v>
       </c>
@@ -10906,7 +10922,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>22</v>
       </c>
@@ -10989,7 +11005,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>23</v>
       </c>
@@ -11072,7 +11088,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>24</v>
       </c>
@@ -11155,7 +11171,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>25</v>
       </c>
@@ -11238,7 +11254,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>26</v>
       </c>
@@ -11321,7 +11337,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>27</v>
       </c>
@@ -11404,7 +11420,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>28</v>
       </c>
@@ -11487,7 +11503,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>29</v>
       </c>
@@ -11570,7 +11586,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>30</v>
       </c>
@@ -11653,7 +11669,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>31</v>
       </c>
@@ -11736,7 +11752,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>32</v>
       </c>
@@ -11819,7 +11835,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>33</v>
       </c>
@@ -11902,7 +11918,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>34</v>
       </c>
@@ -11985,7 +12001,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>35</v>
       </c>
@@ -12068,7 +12084,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>36</v>
       </c>
@@ -12151,7 +12167,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>37</v>
       </c>
@@ -12234,7 +12250,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>38</v>
       </c>
@@ -12317,7 +12333,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>39</v>
       </c>
@@ -12400,7 +12416,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>40</v>
       </c>
@@ -12483,7 +12499,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>41</v>
       </c>
@@ -12566,7 +12582,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>42</v>
       </c>
@@ -12649,7 +12665,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43</v>
       </c>
@@ -12732,7 +12748,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>44</v>
       </c>
@@ -12815,7 +12831,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>45</v>
       </c>
@@ -12898,7 +12914,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>46</v>
       </c>
@@ -12981,7 +12997,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>47</v>
       </c>
@@ -13064,7 +13080,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>48</v>
       </c>
@@ -13147,7 +13163,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>49</v>
       </c>
@@ -13230,7 +13246,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>50</v>
       </c>
@@ -13313,7 +13329,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>51</v>
       </c>
@@ -13396,7 +13412,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>52</v>
       </c>
@@ -13479,7 +13495,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>53</v>
       </c>
@@ -13562,7 +13578,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>54</v>
       </c>
@@ -13645,7 +13661,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>55</v>
       </c>
@@ -13728,7 +13744,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>56</v>
       </c>
@@ -13811,7 +13827,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>57</v>
       </c>
@@ -13894,7 +13910,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>58</v>
       </c>
@@ -13977,7 +13993,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>59</v>
       </c>
@@ -14060,7 +14076,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>60</v>
       </c>
@@ -14143,7 +14159,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>61</v>
       </c>
@@ -14226,7 +14242,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>62</v>
       </c>
@@ -14309,7 +14325,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>63</v>
       </c>
@@ -14392,7 +14408,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>64</v>
       </c>
@@ -14475,7 +14491,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>65</v>
       </c>
@@ -14558,7 +14574,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>66</v>
       </c>
@@ -14641,7 +14657,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>67</v>
       </c>
@@ -14724,7 +14740,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>68</v>
       </c>
@@ -14807,7 +14823,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>69</v>
       </c>
@@ -14890,7 +14906,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>70</v>
       </c>
@@ -14973,7 +14989,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>71</v>
       </c>
@@ -15056,7 +15072,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>72</v>
       </c>
@@ -15139,7 +15155,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>73</v>
       </c>
@@ -15222,7 +15238,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>74</v>
       </c>
@@ -15305,7 +15321,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>75</v>
       </c>
@@ -15388,7 +15404,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>76</v>
       </c>
@@ -15471,7 +15487,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>77</v>
       </c>
@@ -15554,7 +15570,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>78</v>
       </c>
@@ -15637,7 +15653,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>79</v>
       </c>
@@ -15720,7 +15736,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>80</v>
       </c>
@@ -15803,7 +15819,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>81</v>
       </c>
@@ -15886,7 +15902,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>82</v>
       </c>
@@ -15969,7 +15985,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>83</v>
       </c>
@@ -16052,7 +16068,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>84</v>
       </c>
@@ -16135,7 +16151,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>85</v>
       </c>
@@ -16218,7 +16234,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>86</v>
       </c>
@@ -16301,7 +16317,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>87</v>
       </c>
@@ -16384,7 +16400,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>88</v>
       </c>
@@ -16467,7 +16483,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -16550,7 +16566,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>90</v>
       </c>
@@ -16633,7 +16649,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>91</v>
       </c>
@@ -16716,7 +16732,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>92</v>
       </c>
@@ -16799,7 +16815,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>93</v>
       </c>
@@ -16882,7 +16898,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>94</v>
       </c>
@@ -16965,7 +16981,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>95</v>
       </c>
@@ -17048,7 +17064,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>96</v>
       </c>
@@ -17131,7 +17147,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>97</v>
       </c>
@@ -17214,7 +17230,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>98</v>
       </c>
@@ -17297,7 +17313,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -17380,7 +17396,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>100</v>
       </c>
@@ -17463,7 +17479,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>101</v>
       </c>
@@ -17546,7 +17562,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>102</v>
       </c>
@@ -17629,7 +17645,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>103</v>
       </c>
@@ -17712,7 +17728,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>104</v>
       </c>
@@ -17795,7 +17811,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>105</v>
       </c>
@@ -17878,7 +17894,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>106</v>
       </c>
@@ -17961,7 +17977,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -18044,7 +18060,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -18127,7 +18143,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>109</v>
       </c>
@@ -18210,7 +18226,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>110</v>
       </c>
@@ -18293,7 +18309,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>111</v>
       </c>
@@ -18376,7 +18392,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>112</v>
       </c>
@@ -18459,7 +18475,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>113</v>
       </c>
@@ -18542,7 +18558,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>114</v>
       </c>
@@ -18625,7 +18641,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>115</v>
       </c>
@@ -18708,7 +18724,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>116</v>
       </c>
@@ -18791,7 +18807,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>117</v>
       </c>
@@ -18874,7 +18890,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>118</v>
       </c>
@@ -18957,7 +18973,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>119</v>
       </c>
@@ -19040,7 +19056,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>120</v>
       </c>
@@ -19123,7 +19139,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>121</v>
       </c>
@@ -19206,7 +19222,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>122</v>
       </c>
@@ -19289,7 +19305,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>123</v>
       </c>
@@ -19372,7 +19388,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>124</v>
       </c>
@@ -19455,7 +19471,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>125</v>
       </c>
@@ -19538,7 +19554,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>126</v>
       </c>
@@ -19621,7 +19637,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>127</v>
       </c>
@@ -19704,7 +19720,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>128</v>
       </c>
@@ -19787,7 +19803,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>129</v>
       </c>
@@ -19870,7 +19886,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>130</v>
       </c>
@@ -19953,7 +19969,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>131</v>
       </c>
@@ -20036,7 +20052,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>132</v>
       </c>
@@ -20119,7 +20135,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>133</v>
       </c>
@@ -20202,7 +20218,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>134</v>
       </c>
@@ -20285,7 +20301,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>135</v>
       </c>
@@ -20368,7 +20384,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>136</v>
       </c>
@@ -20451,7 +20467,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>137</v>
       </c>
@@ -20534,7 +20550,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>138</v>
       </c>
@@ -20617,7 +20633,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>139</v>
       </c>
@@ -20700,7 +20716,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>140</v>
       </c>
@@ -20783,7 +20799,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>141</v>
       </c>
@@ -20866,7 +20882,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>142</v>
       </c>
@@ -20949,7 +20965,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>143</v>
       </c>
@@ -21032,7 +21048,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>144</v>
       </c>
@@ -21115,7 +21131,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>145</v>
       </c>
@@ -21198,7 +21214,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>146</v>
       </c>
@@ -21281,7 +21297,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="147" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>147</v>
       </c>
@@ -21364,7 +21380,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>148</v>
       </c>
@@ -21447,7 +21463,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="149" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>149</v>
       </c>
@@ -21530,7 +21546,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="150" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>150</v>
       </c>
@@ -21613,7 +21629,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>151</v>
       </c>
@@ -21696,7 +21712,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>152</v>
       </c>
@@ -21779,7 +21795,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="153" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>153</v>
       </c>
@@ -21862,7 +21878,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="154" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>154</v>
       </c>
@@ -21945,7 +21961,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="155" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>155</v>
       </c>
@@ -22028,7 +22044,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>156</v>
       </c>
@@ -22111,7 +22127,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>157</v>
       </c>
@@ -22194,7 +22210,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="158" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>158</v>
       </c>
@@ -22277,7 +22293,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="159" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>159</v>
       </c>
@@ -22360,7 +22376,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="160" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>160</v>
       </c>
@@ -22443,7 +22459,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="161" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>161</v>
       </c>
@@ -22526,7 +22542,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="162" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>162</v>
       </c>
@@ -22609,7 +22625,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="163" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>163</v>
       </c>
@@ -22692,7 +22708,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="164" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>164</v>
       </c>
@@ -22775,7 +22791,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="165" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>165</v>
       </c>
@@ -22858,7 +22874,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="166" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>166</v>
       </c>
@@ -22941,7 +22957,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>167</v>
       </c>
@@ -23024,7 +23040,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="168" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>168</v>
       </c>
@@ -23107,7 +23123,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="169" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>169</v>
       </c>
@@ -23190,7 +23206,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="170" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>170</v>
       </c>
@@ -23273,7 +23289,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="171" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>171</v>
       </c>
@@ -23356,7 +23372,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="172" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>172</v>
       </c>
@@ -23439,7 +23455,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="173" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>173</v>
       </c>
@@ -23522,7 +23538,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="174" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>174</v>
       </c>
@@ -23605,7 +23621,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="175" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>175</v>
       </c>
@@ -23688,7 +23704,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="176" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>176</v>
       </c>
@@ -23771,7 +23787,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="177" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>177</v>
       </c>
@@ -23854,7 +23870,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="178" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>178</v>
       </c>
@@ -23937,7 +23953,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="179" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>179</v>
       </c>
@@ -24020,7 +24036,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="180" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>180</v>
       </c>
@@ -24103,7 +24119,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="181" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -24186,7 +24202,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="182" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>182</v>
       </c>
@@ -24269,7 +24285,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="183" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>183</v>
       </c>
@@ -24352,7 +24368,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="184" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>184</v>
       </c>
@@ -24435,7 +24451,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="185" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>185</v>
       </c>
@@ -24518,7 +24534,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="186" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>186</v>
       </c>
@@ -24601,7 +24617,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="187" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>187</v>
       </c>
@@ -24684,7 +24700,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="188" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>188</v>
       </c>
@@ -24767,7 +24783,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="189" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>189</v>
       </c>
@@ -24850,7 +24866,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="190" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>190</v>
       </c>
@@ -24933,7 +24949,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="191" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>191</v>
       </c>
@@ -25016,7 +25032,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="192" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>192</v>
       </c>
@@ -25099,7 +25115,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="193" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>193</v>
       </c>
@@ -25182,7 +25198,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="194" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>194</v>
       </c>
@@ -25265,7 +25281,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="195" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>195</v>
       </c>
@@ -25348,7 +25364,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="196" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>196</v>
       </c>
@@ -25431,7 +25447,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="197" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>197</v>
       </c>
@@ -25514,7 +25530,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="198" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>198</v>
       </c>
@@ -25597,7 +25613,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="199" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>199</v>
       </c>
@@ -25680,7 +25696,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="200" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>200</v>
       </c>
@@ -25763,7 +25779,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="201" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>201</v>
       </c>
@@ -25846,7 +25862,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="202" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>202</v>
       </c>
@@ -25929,7 +25945,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="203" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>203</v>
       </c>
@@ -26012,7 +26028,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="204" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>204</v>
       </c>
@@ -26095,7 +26111,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="205" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>205</v>
       </c>
@@ -26178,7 +26194,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="206" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>206</v>
       </c>
@@ -26261,7 +26277,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="207" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>207</v>
       </c>
@@ -26344,7 +26360,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="208" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>208</v>
       </c>
@@ -26427,7 +26443,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="209" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>209</v>
       </c>
@@ -26510,7 +26526,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="210" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>210</v>
       </c>
@@ -26593,7 +26609,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="211" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>211</v>
       </c>
@@ -26676,7 +26692,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="212" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>212</v>
       </c>
@@ -26759,7 +26775,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="213" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>213</v>
       </c>
@@ -26842,7 +26858,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="214" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>214</v>
       </c>
@@ -26925,7 +26941,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="215" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>215</v>
       </c>
@@ -27008,7 +27024,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="216" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>216</v>
       </c>
@@ -27091,7 +27107,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="217" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>217</v>
       </c>
@@ -27174,7 +27190,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="218" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -27257,7 +27273,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="219" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>219</v>
       </c>
@@ -27340,7 +27356,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="220" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>220</v>
       </c>
@@ -27423,7 +27439,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="221" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>221</v>
       </c>
@@ -27506,7 +27522,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="222" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>222</v>
       </c>
@@ -27589,7 +27605,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="223" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>223</v>
       </c>
@@ -27672,7 +27688,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="224" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>224</v>
       </c>
@@ -27755,7 +27771,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="225" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>225</v>
       </c>
@@ -27838,7 +27854,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="226" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>226</v>
       </c>
@@ -27921,7 +27937,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="227" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>227</v>
       </c>
@@ -28004,7 +28020,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="228" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>228</v>
       </c>
@@ -28087,7 +28103,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="229" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>229</v>
       </c>
@@ -28170,7 +28186,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="230" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>230</v>
       </c>
@@ -28253,7 +28269,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="231" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>231</v>
       </c>
@@ -28336,7 +28352,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="232" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>232</v>
       </c>
@@ -28419,7 +28435,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="233" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>233</v>
       </c>
@@ -28502,7 +28518,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="234" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>234</v>
       </c>
@@ -28585,7 +28601,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="235" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>235</v>
       </c>
@@ -28668,7 +28684,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="236" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>236</v>
       </c>
@@ -28751,7 +28767,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="237" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>237</v>
       </c>
@@ -28834,7 +28850,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="238" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>238</v>
       </c>
@@ -28917,7 +28933,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="239" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>239</v>
       </c>
@@ -29000,7 +29016,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="240" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>240</v>
       </c>
@@ -29083,7 +29099,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="241" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>241</v>
       </c>
@@ -29166,7 +29182,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="242" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>242</v>
       </c>
@@ -29249,7 +29265,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="243" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>243</v>
       </c>
@@ -29332,7 +29348,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="244" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>244</v>
       </c>
@@ -29415,7 +29431,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="245" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>245</v>
       </c>
@@ -29498,7 +29514,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="246" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>246</v>
       </c>
@@ -29581,7 +29597,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="247" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>247</v>
       </c>
@@ -29664,7 +29680,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="248" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>248</v>
       </c>
@@ -29747,7 +29763,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="249" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>249</v>
       </c>
@@ -29830,7 +29846,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="250" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>250</v>
       </c>
@@ -29913,7 +29929,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="251" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -29996,7 +30012,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="252" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>252</v>
       </c>
@@ -30079,7 +30095,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="253" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6">
         <v>253</v>
       </c>
@@ -30162,7 +30178,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="254" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6">
         <v>254</v>
       </c>
@@ -30245,7 +30261,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="255" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6">
         <v>255</v>
       </c>
@@ -30328,7 +30344,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="256" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6">
         <v>256</v>
       </c>
@@ -30411,7 +30427,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="257" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6">
         <v>257</v>
       </c>
@@ -30494,7 +30510,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="258" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6">
         <v>258</v>
       </c>
@@ -30577,7 +30593,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="259" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
         <v>259</v>
       </c>
@@ -30660,7 +30676,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="260" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6">
         <v>260</v>
       </c>
@@ -30743,7 +30759,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="261" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6">
         <v>261</v>
       </c>
@@ -30826,7 +30842,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="262" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6">
         <v>262</v>
       </c>
@@ -30909,7 +30925,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="263" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>263</v>
       </c>
@@ -30992,7 +31008,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="264" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6">
         <v>264</v>
       </c>
@@ -31075,7 +31091,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="265" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6">
         <v>265</v>
       </c>
@@ -31158,7 +31174,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="266" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6">
         <v>266</v>
       </c>
@@ -31241,7 +31257,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="267" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6">
         <v>267</v>
       </c>
@@ -31324,7 +31340,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="268" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6">
         <v>268</v>
       </c>
@@ -31407,7 +31423,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="269" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6">
         <v>269</v>
       </c>
@@ -31490,7 +31506,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="270" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6">
         <v>270</v>
       </c>
@@ -31573,7 +31589,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="271" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -31656,7 +31672,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="272" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6">
         <v>272</v>
       </c>
@@ -31739,7 +31755,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="273" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
         <v>273</v>
       </c>
@@ -31822,7 +31838,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="274" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6">
         <v>274</v>
       </c>
@@ -31905,7 +31921,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="275" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6">
         <v>275</v>
       </c>
@@ -31988,7 +32004,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="276" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6">
         <v>276</v>
       </c>
@@ -32071,7 +32087,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="277" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6">
         <v>277</v>
       </c>
@@ -32154,7 +32170,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="278" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6">
         <v>278</v>
       </c>
@@ -32237,7 +32253,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="279" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6">
         <v>279</v>
       </c>
@@ -32320,7 +32336,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="280" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6">
         <v>280</v>
       </c>
@@ -32403,7 +32419,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="281" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
         <v>281</v>
       </c>
@@ -32486,7 +32502,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="282" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6">
         <v>282</v>
       </c>
@@ -32569,7 +32585,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="283" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6">
         <v>283</v>
       </c>
@@ -32652,7 +32668,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="284" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6">
         <v>284</v>
       </c>
@@ -32735,7 +32751,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="285" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
         <v>285</v>
       </c>
@@ -32818,7 +32834,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="286" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6">
         <v>286</v>
       </c>
@@ -32901,7 +32917,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="287" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6">
         <v>287</v>
       </c>
@@ -32984,7 +33000,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="288" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6">
         <v>288</v>
       </c>
@@ -33067,7 +33083,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="289" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6">
         <v>289</v>
       </c>
@@ -33150,7 +33166,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="290" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6">
         <v>290</v>
       </c>
@@ -33233,7 +33249,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="291" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6">
         <v>291</v>
       </c>
@@ -33316,7 +33332,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="292" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6">
         <v>292</v>
       </c>
@@ -33399,7 +33415,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="293" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6">
         <v>293</v>
       </c>
@@ -33482,7 +33498,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="294" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6">
         <v>294</v>
       </c>
@@ -33565,7 +33581,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="295" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
         <v>295</v>
       </c>
@@ -33648,7 +33664,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="296" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6">
         <v>296</v>
       </c>
@@ -33731,7 +33747,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="297" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6">
         <v>297</v>
       </c>
@@ -33814,7 +33830,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="298" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6">
         <v>298</v>
       </c>
@@ -33897,7 +33913,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="299" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6">
         <v>299</v>
       </c>
@@ -33980,7 +33996,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="300" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6">
         <v>300</v>
       </c>
@@ -34063,7 +34079,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="301" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6">
         <v>301</v>
       </c>
@@ -34146,7 +34162,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="302" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6">
         <v>302</v>
       </c>
@@ -34229,7 +34245,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="303" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6">
         <v>303</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C5C4E4-D1D2-4F12-9ABA-762D4569B3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C7F6D7-4814-42A4-91F5-EE72157D93F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="10" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8891" uniqueCount="1029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8985" uniqueCount="1031">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -3178,6 +3178,12 @@
   </si>
   <si>
     <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Atributo Ifc</t>
   </si>
 </sst>
 </file>
@@ -3740,7 +3746,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{001CC4A1-5641-437E-9DC4-857BB9658EC6}"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="14">
     <dxf>
       <font>
         <b val="0"/>
@@ -3793,14 +3799,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3835,6 +3833,42 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4173,14 +4207,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B80B61-09F0-4F35-A733-85777283AFC6}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="56.69921875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="56.6640625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.19921875" customWidth="1"/>
-    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.296875" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" customWidth="1"/>
+    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -4191,7 +4225,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>320</v>
       </c>
@@ -4202,7 +4236,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>321</v>
       </c>
@@ -4213,7 +4247,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4224,7 +4258,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -4236,7 +4270,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -4248,7 +4282,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4259,7 +4293,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
         <v>9</v>
       </c>
@@ -4270,7 +4304,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>322</v>
       </c>
@@ -4281,7 +4315,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>324</v>
       </c>
@@ -4292,7 +4326,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>325</v>
       </c>
@@ -4303,7 +4337,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -4314,7 +4348,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>326</v>
       </c>
@@ -4325,7 +4359,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>327</v>
       </c>
@@ -4336,7 +4370,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>328</v>
       </c>
@@ -4347,7 +4381,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>329</v>
       </c>
@@ -4358,7 +4392,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -4369,19 +4403,19 @@
         <v>704</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B18" s="38">
         <f ca="1">NOW()</f>
-        <v>46249.323895486108</v>
+        <v>46253.615240624997</v>
       </c>
       <c r="C18" s="37" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>713</v>
       </c>
@@ -4392,7 +4426,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="34" t="s">
         <v>708</v>
       </c>
@@ -4404,7 +4438,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="34" t="s">
         <v>714</v>
       </c>
@@ -4416,7 +4450,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="34" t="s">
         <v>319</v>
       </c>
@@ -4427,7 +4461,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="34" t="s">
         <v>331</v>
       </c>
@@ -4438,7 +4472,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>336</v>
       </c>
@@ -4449,7 +4483,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>338</v>
       </c>
@@ -4460,7 +4494,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="34" t="s">
         <v>700</v>
       </c>
@@ -4471,7 +4505,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
         <v>988</v>
       </c>
@@ -4482,7 +4516,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="34" t="s">
         <v>990</v>
       </c>
@@ -4493,7 +4527,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="34" t="s">
         <v>992</v>
       </c>
@@ -4504,7 +4538,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="34" t="s">
         <v>994</v>
       </c>
@@ -4515,7 +4549,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="34" t="s">
         <v>996</v>
       </c>
@@ -4526,7 +4560,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="34" t="s">
         <v>998</v>
       </c>
@@ -4537,7 +4571,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="34" t="s">
         <v>1000</v>
       </c>
@@ -4548,7 +4582,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="34" t="s">
         <v>1002</v>
       </c>
@@ -4559,7 +4593,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="34" t="s">
         <v>1004</v>
       </c>
@@ -4570,7 +4604,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="34" t="s">
         <v>1006</v>
       </c>
@@ -4581,7 +4615,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="34" t="s">
         <v>1008</v>
       </c>
@@ -4592,7 +4626,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>1010</v>
       </c>
@@ -4603,7 +4637,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="34" t="s">
         <v>1012</v>
       </c>
@@ -4629,36 +4663,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFFE5C0-D3D8-4876-B71B-E260AD929073}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA47"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC47"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.8984375" style="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="66" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.09765625" style="66" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.8984375" style="66" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.59765625" style="66" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="66" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.3984375" style="66" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.8984375" style="39" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.59765625" style="39" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="39" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="62.296875" style="39" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.69921875" style="39" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.796875" style="66" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.09765625" style="39" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.8984375" style="39" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.59765625" style="39" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.796875" style="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.5" style="66" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="30.8984375" style="39" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="36.09765625" style="39" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.59765625" style="39" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="57" style="39" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.796875" style="39"/>
+    <col min="1" max="1" width="2.83203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="66" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="66" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="66" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="66" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="66" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.5" style="66" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" style="39" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="78.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="62.33203125" style="39" customWidth="1"/>
+    <col min="18" max="18" width="54.5" style="39" customWidth="1"/>
+    <col min="19" max="19" width="5" style="66" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" style="39" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="66" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="38.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9" style="39" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.6640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.83203125" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>649</v>
       </c>
@@ -4710,38 +4746,44 @@
       <c r="Q1" s="20" t="s">
         <v>669</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="R1" s="32" t="s">
+        <v>699</v>
+      </c>
+      <c r="S1" s="20" t="s">
         <v>693</v>
       </c>
-      <c r="S1" s="20" t="s">
+      <c r="T1" s="20" t="s">
         <v>651</v>
       </c>
-      <c r="T1" s="20" t="s">
+      <c r="U1" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="U1" s="20" t="s">
+      <c r="V1" s="20" t="s">
         <v>653</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="W1" s="20" t="s">
         <v>652</v>
       </c>
-      <c r="W1" s="57" t="s">
+      <c r="X1" s="57" t="s">
         <v>671</v>
       </c>
-      <c r="X1" s="20" t="s">
+      <c r="Y1" s="20" t="s">
         <v>697</v>
       </c>
-      <c r="Y1" s="20" t="s">
+      <c r="Z1" s="20" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AA1" s="20" t="s">
         <v>698</v>
       </c>
-      <c r="Z1" s="20" t="s">
+      <c r="AB1" s="20" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AC1" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="AA1" s="32" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48">
         <v>2</v>
       </c>
@@ -4797,42 +4839,48 @@
       <c r="Q2" s="50" t="s">
         <v>950</v>
       </c>
-      <c r="R2" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S2" s="51" t="str">
-        <f t="shared" ref="S2:U14" si="2">SUBSTITUTE(C2, "_", " ")</f>
+      <c r="R2" s="52" t="s">
+        <v>951</v>
+      </c>
+      <c r="S2" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T2" s="51" t="str">
+        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T2" s="51" t="str">
+      <c r="U2" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U2" s="50" t="str">
+      <c r="V2" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V2" s="33" t="s">
+      <c r="W2" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W2" s="56" t="str">
-        <f t="shared" ref="W2:W14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
+      <c r="X2" s="56" t="str">
+        <f t="shared" ref="X2:X14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
         <v>Key-ABNT-2</v>
       </c>
-      <c r="X2" s="33" t="s">
+      <c r="Y2" s="33" t="s">
         <v>1024</v>
       </c>
-      <c r="Y2" s="33" t="s">
+      <c r="Z2" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA2" s="33" t="s">
         <v>1025</v>
       </c>
-      <c r="Z2" s="33" t="s">
+      <c r="AB2" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC2" s="33" t="s">
         <v>717</v>
       </c>
-      <c r="AA2" s="52" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="48">
         <v>3</v>
       </c>
@@ -4888,42 +4936,48 @@
       <c r="Q3" s="50" t="s">
         <v>953</v>
       </c>
-      <c r="R3" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S3" s="51" t="str">
+      <c r="R3" s="52" t="s">
+        <v>954</v>
+      </c>
+      <c r="S3" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T3" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T3" s="51" t="str">
+      <c r="U3" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U3" s="50" t="str">
+      <c r="V3" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V3" s="33" t="s">
+      <c r="W3" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W3" s="56" t="str">
+      <c r="X3" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-3</v>
       </c>
-      <c r="X3" s="33" t="s">
+      <c r="Y3" s="33" t="s">
         <v>1026</v>
       </c>
-      <c r="Y3" s="33" t="s">
+      <c r="Z3" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA3" s="33" t="s">
         <v>1027</v>
       </c>
-      <c r="Z3" s="33" t="s">
+      <c r="AB3" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC3" s="33" t="s">
         <v>718</v>
       </c>
-      <c r="AA3" s="52" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="48">
         <v>4</v>
       </c>
@@ -4979,42 +5033,48 @@
       <c r="Q4" s="50" t="s">
         <v>956</v>
       </c>
-      <c r="R4" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S4" s="51" t="str">
+      <c r="R4" s="52" t="s">
+        <v>957</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T4" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T4" s="51" t="str">
+      <c r="U4" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U4" s="50" t="str">
+      <c r="V4" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V4" s="33" t="s">
+      <c r="W4" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W4" s="56" t="str">
+      <c r="X4" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-4</v>
       </c>
-      <c r="X4" s="33" t="s">
+      <c r="Y4" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Y4" s="33" t="s">
+      <c r="Z4" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA4" s="33" t="s">
         <v>1018</v>
       </c>
-      <c r="Z4" s="33" t="s">
+      <c r="AB4" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC4" s="33" t="s">
         <v>719</v>
       </c>
-      <c r="AA4" s="52" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="48">
         <v>5</v>
       </c>
@@ -5070,42 +5130,48 @@
       <c r="Q5" s="50" t="s">
         <v>959</v>
       </c>
-      <c r="R5" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S5" s="51" t="str">
+      <c r="R5" s="52" t="s">
+        <v>960</v>
+      </c>
+      <c r="S5" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T5" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T5" s="51" t="str">
+      <c r="U5" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U5" s="50" t="str">
+      <c r="V5" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V5" s="33" t="s">
+      <c r="W5" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W5" s="56" t="str">
+      <c r="X5" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-5</v>
       </c>
-      <c r="X5" s="33" t="s">
+      <c r="Y5" s="33" t="s">
         <v>1019</v>
       </c>
-      <c r="Y5" s="33" t="s">
+      <c r="Z5" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA5" s="33" t="s">
         <v>1020</v>
       </c>
-      <c r="Z5" s="33" t="s">
+      <c r="AB5" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC5" s="33" t="s">
         <v>720</v>
       </c>
-      <c r="AA5" s="52" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="48">
         <v>6</v>
       </c>
@@ -5161,42 +5227,48 @@
       <c r="Q6" s="50" t="s">
         <v>962</v>
       </c>
-      <c r="R6" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S6" s="51" t="str">
+      <c r="R6" s="52" t="s">
+        <v>963</v>
+      </c>
+      <c r="S6" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T6" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T6" s="51" t="str">
+      <c r="U6" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U6" s="50" t="str">
+      <c r="V6" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V6" s="33" t="s">
+      <c r="W6" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W6" s="56" t="str">
+      <c r="X6" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-6</v>
       </c>
-      <c r="X6" s="33" t="s">
+      <c r="Y6" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Y6" s="33" t="s">
+      <c r="Z6" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA6" s="33" t="s">
         <v>1018</v>
       </c>
-      <c r="Z6" s="33" t="s">
+      <c r="AB6" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC6" s="33" t="s">
         <v>721</v>
       </c>
-      <c r="AA6" s="52" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="48">
         <v>7</v>
       </c>
@@ -5252,42 +5324,48 @@
       <c r="Q7" s="50" t="s">
         <v>965</v>
       </c>
-      <c r="R7" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S7" s="51" t="str">
+      <c r="R7" s="52" t="s">
+        <v>966</v>
+      </c>
+      <c r="S7" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T7" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T7" s="51" t="str">
+      <c r="U7" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U7" s="50" t="str">
+      <c r="V7" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V7" s="33" t="s">
+      <c r="W7" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W7" s="56" t="str">
+      <c r="X7" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-7</v>
       </c>
-      <c r="X7" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y7" s="33" t="s">
         <v>1017</v>
       </c>
       <c r="Z7" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA7" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB7" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC7" s="33" t="s">
         <v>722</v>
       </c>
-      <c r="AA7" s="52" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="48">
         <v>8</v>
       </c>
@@ -5343,42 +5421,48 @@
       <c r="Q8" s="50" t="s">
         <v>968</v>
       </c>
-      <c r="R8" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S8" s="51" t="str">
+      <c r="R8" s="52" t="s">
+        <v>969</v>
+      </c>
+      <c r="S8" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T8" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T8" s="51" t="str">
+      <c r="U8" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U8" s="50" t="str">
+      <c r="V8" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V8" s="33" t="s">
+      <c r="W8" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W8" s="56" t="str">
+      <c r="X8" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-8</v>
       </c>
-      <c r="X8" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y8" s="33" t="s">
         <v>1017</v>
       </c>
       <c r="Z8" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA8" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB8" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC8" s="33" t="s">
         <v>723</v>
       </c>
-      <c r="AA8" s="52" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="48">
         <v>9</v>
       </c>
@@ -5434,42 +5518,48 @@
       <c r="Q9" s="50" t="s">
         <v>971</v>
       </c>
-      <c r="R9" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S9" s="51" t="str">
+      <c r="R9" s="52" t="s">
+        <v>972</v>
+      </c>
+      <c r="S9" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T9" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T9" s="51" t="str">
+      <c r="U9" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U9" s="50" t="str">
+      <c r="V9" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V9" s="33" t="s">
+      <c r="W9" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W9" s="56" t="str">
+      <c r="X9" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-9</v>
       </c>
-      <c r="X9" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y9" s="33" t="s">
         <v>1017</v>
       </c>
       <c r="Z9" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA9" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB9" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC9" s="33" t="s">
         <v>724</v>
       </c>
-      <c r="AA9" s="52" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="48">
         <v>10</v>
       </c>
@@ -5525,42 +5615,48 @@
       <c r="Q10" s="50" t="s">
         <v>974</v>
       </c>
-      <c r="R10" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S10" s="51" t="str">
+      <c r="R10" s="52" t="s">
+        <v>975</v>
+      </c>
+      <c r="S10" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T10" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T10" s="51" t="str">
+      <c r="U10" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U10" s="50" t="str">
+      <c r="V10" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V10" s="33" t="s">
+      <c r="W10" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W10" s="56" t="str">
+      <c r="X10" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-10</v>
       </c>
-      <c r="X10" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y10" s="33" t="s">
         <v>1017</v>
       </c>
       <c r="Z10" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA10" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB10" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC10" s="33" t="s">
         <v>725</v>
       </c>
-      <c r="AA10" s="52" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="48">
         <v>11</v>
       </c>
@@ -5616,42 +5712,48 @@
       <c r="Q11" s="50" t="s">
         <v>977</v>
       </c>
-      <c r="R11" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S11" s="51" t="str">
+      <c r="R11" s="52" t="s">
+        <v>978</v>
+      </c>
+      <c r="S11" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T11" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T11" s="51" t="str">
+      <c r="U11" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U11" s="50" t="str">
+      <c r="V11" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V11" s="33" t="s">
+      <c r="W11" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W11" s="56" t="str">
+      <c r="X11" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-11</v>
       </c>
-      <c r="X11" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y11" s="33" t="s">
         <v>1017</v>
       </c>
       <c r="Z11" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA11" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB11" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC11" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="AA11" s="52" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="48">
         <v>12</v>
       </c>
@@ -5707,42 +5809,48 @@
       <c r="Q12" s="50" t="s">
         <v>980</v>
       </c>
-      <c r="R12" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S12" s="51" t="str">
+      <c r="R12" s="52" t="s">
+        <v>981</v>
+      </c>
+      <c r="S12" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T12" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T12" s="51" t="str">
+      <c r="U12" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U12" s="50" t="str">
+      <c r="V12" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V12" s="33" t="s">
+      <c r="W12" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W12" s="56" t="str">
+      <c r="X12" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-12</v>
       </c>
-      <c r="X12" s="33" t="s">
+      <c r="Y12" s="33" t="s">
         <v>1021</v>
       </c>
-      <c r="Y12" s="33" t="s">
+      <c r="Z12" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA12" s="33" t="s">
         <v>1028</v>
       </c>
-      <c r="Z12" s="33" t="s">
+      <c r="AB12" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC12" s="33" t="s">
         <v>726</v>
       </c>
-      <c r="AA12" s="52" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="48">
         <v>13</v>
       </c>
@@ -5798,42 +5906,48 @@
       <c r="Q13" s="50" t="s">
         <v>983</v>
       </c>
-      <c r="R13" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S13" s="51" t="str">
+      <c r="R13" s="52" t="s">
+        <v>984</v>
+      </c>
+      <c r="S13" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T13" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T13" s="51" t="str">
+      <c r="U13" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U13" s="50" t="str">
+      <c r="V13" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V13" s="33" t="s">
+      <c r="W13" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W13" s="56" t="str">
+      <c r="X13" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-13</v>
       </c>
-      <c r="X13" s="33" t="s">
+      <c r="Y13" s="33" t="s">
         <v>1021</v>
       </c>
-      <c r="Y13" s="33" t="s">
+      <c r="Z13" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA13" s="33" t="s">
         <v>1028</v>
       </c>
-      <c r="Z13" s="33" t="s">
+      <c r="AB13" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC13" s="33" t="s">
         <v>727</v>
       </c>
-      <c r="AA13" s="52" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="48">
         <v>14</v>
       </c>
@@ -5889,42 +6003,48 @@
       <c r="Q14" s="50" t="s">
         <v>986</v>
       </c>
-      <c r="R14" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S14" s="51" t="str">
+      <c r="R14" s="52" t="s">
+        <v>987</v>
+      </c>
+      <c r="S14" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T14" s="51" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T14" s="51" t="str">
+      <c r="U14" s="51" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U14" s="50" t="str">
+      <c r="V14" s="50" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V14" s="33" t="s">
+      <c r="W14" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W14" s="56" t="str">
+      <c r="X14" s="56" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-14</v>
       </c>
-      <c r="X14" s="67" t="s">
+      <c r="Y14" s="67" t="s">
         <v>1022</v>
       </c>
-      <c r="Y14" s="68" t="s">
+      <c r="Z14" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA14" s="68" t="s">
         <v>1023</v>
       </c>
-      <c r="Z14" s="33" t="s">
+      <c r="AB14" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC14" s="33" t="s">
         <v>728</v>
       </c>
-      <c r="AA14" s="52" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="48">
         <v>15</v>
       </c>
@@ -5980,42 +6100,48 @@
       <c r="Q15" s="52" t="s">
         <v>902</v>
       </c>
-      <c r="R15" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S15" s="51" t="str">
-        <f t="shared" ref="S15:S47" si="8">SUBSTITUTE(C15, "_", " ")</f>
+      <c r="R15" s="55" t="s">
+        <v>869</v>
+      </c>
+      <c r="S15" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T15" s="51" t="str">
+        <f t="shared" ref="T15:T47" si="8">SUBSTITUTE(C15, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T15" s="51" t="str">
-        <f t="shared" ref="T15:T47" si="9">SUBSTITUTE(D15, "_", " ")</f>
+      <c r="U15" s="51" t="str">
+        <f t="shared" ref="U15:U47" si="9">SUBSTITUTE(D15, "_", " ")</f>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U15" s="50" t="str">
-        <f t="shared" ref="U15:U47" si="10">SUBSTITUTE(E15, "_", " ")</f>
+      <c r="V15" s="50" t="str">
+        <f t="shared" ref="V15:V47" si="10">SUBSTITUTE(E15, "_", " ")</f>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V15" s="33" t="s">
+      <c r="W15" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W15" s="56" t="str">
-        <f t="shared" ref="W15:W47" si="11">CONCATENATE("Key-ABNT-",A15)</f>
+      <c r="X15" s="56" t="str">
+        <f t="shared" ref="X15:X47" si="11">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
-      </c>
-      <c r="X15" s="33" t="s">
-        <v>1017</v>
       </c>
       <c r="Y15" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z15" s="55" t="s">
+      <c r="Z15" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA15" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB15" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC15" s="55" t="s">
         <v>802</v>
       </c>
-      <c r="AA15" s="55" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="48">
         <v>16</v>
       </c>
@@ -6071,42 +6197,48 @@
       <c r="Q16" s="52" t="s">
         <v>903</v>
       </c>
-      <c r="R16" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S16" s="51" t="str">
+      <c r="R16" s="55" t="s">
+        <v>870</v>
+      </c>
+      <c r="S16" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T16" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T16" s="51" t="str">
+      <c r="U16" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U16" s="50" t="str">
+      <c r="V16" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V16" s="33" t="s">
+      <c r="W16" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W16" s="56" t="str">
+      <c r="X16" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-16</v>
       </c>
-      <c r="X16" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y16" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z16" s="55" t="s">
+      <c r="Z16" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA16" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB16" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC16" s="55" t="s">
         <v>803</v>
       </c>
-      <c r="AA16" s="55" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="48">
         <v>17</v>
       </c>
@@ -6162,42 +6294,48 @@
       <c r="Q17" s="52" t="s">
         <v>904</v>
       </c>
-      <c r="R17" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S17" s="51" t="str">
+      <c r="R17" s="55" t="s">
+        <v>871</v>
+      </c>
+      <c r="S17" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T17" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T17" s="51" t="str">
+      <c r="U17" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U17" s="50" t="str">
+      <c r="V17" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V17" s="33" t="s">
+      <c r="W17" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W17" s="56" t="str">
+      <c r="X17" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-17</v>
       </c>
-      <c r="X17" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y17" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z17" s="55" t="s">
+      <c r="Z17" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA17" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB17" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC17" s="55" t="s">
         <v>804</v>
       </c>
-      <c r="AA17" s="55" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="48">
         <v>18</v>
       </c>
@@ -6253,42 +6391,48 @@
       <c r="Q18" s="52" t="s">
         <v>905</v>
       </c>
-      <c r="R18" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S18" s="51" t="str">
+      <c r="R18" s="55" t="s">
+        <v>872</v>
+      </c>
+      <c r="S18" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T18" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T18" s="51" t="str">
+      <c r="U18" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U18" s="50" t="str">
+      <c r="V18" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V18" s="33" t="s">
+      <c r="W18" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W18" s="56" t="str">
+      <c r="X18" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-18</v>
       </c>
-      <c r="X18" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y18" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z18" s="55" t="s">
+      <c r="Z18" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA18" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB18" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC18" s="55" t="s">
         <v>805</v>
       </c>
-      <c r="AA18" s="55" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="48">
         <v>19</v>
       </c>
@@ -6344,42 +6488,48 @@
       <c r="Q19" s="52" t="s">
         <v>906</v>
       </c>
-      <c r="R19" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S19" s="51" t="str">
+      <c r="R19" s="55" t="s">
+        <v>873</v>
+      </c>
+      <c r="S19" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T19" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T19" s="51" t="str">
+      <c r="U19" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U19" s="50" t="str">
+      <c r="V19" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V19" s="33" t="s">
+      <c r="W19" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W19" s="56" t="str">
+      <c r="X19" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-19</v>
       </c>
-      <c r="X19" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y19" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z19" s="55" t="s">
+      <c r="Z19" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA19" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB19" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC19" s="55" t="s">
         <v>806</v>
       </c>
-      <c r="AA19" s="55" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="48">
         <v>20</v>
       </c>
@@ -6435,42 +6585,48 @@
       <c r="Q20" s="52" t="s">
         <v>907</v>
       </c>
-      <c r="R20" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S20" s="51" t="str">
+      <c r="R20" s="55" t="s">
+        <v>874</v>
+      </c>
+      <c r="S20" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T20" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T20" s="51" t="str">
+      <c r="U20" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U20" s="50" t="str">
+      <c r="V20" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V20" s="33" t="s">
+      <c r="W20" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W20" s="56" t="str">
+      <c r="X20" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-20</v>
       </c>
-      <c r="X20" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y20" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z20" s="55" t="s">
+      <c r="Z20" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA20" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB20" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC20" s="55" t="s">
         <v>807</v>
       </c>
-      <c r="AA20" s="55" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="48">
         <v>21</v>
       </c>
@@ -6526,42 +6682,48 @@
       <c r="Q21" s="52" t="s">
         <v>908</v>
       </c>
-      <c r="R21" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S21" s="51" t="str">
+      <c r="R21" s="55" t="s">
+        <v>875</v>
+      </c>
+      <c r="S21" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T21" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T21" s="51" t="str">
+      <c r="U21" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U21" s="50" t="str">
+      <c r="V21" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V21" s="33" t="s">
+      <c r="W21" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W21" s="56" t="str">
+      <c r="X21" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-21</v>
       </c>
-      <c r="X21" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y21" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z21" s="55" t="s">
+      <c r="Z21" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA21" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB21" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC21" s="55" t="s">
         <v>808</v>
       </c>
-      <c r="AA21" s="55" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="48">
         <v>22</v>
       </c>
@@ -6617,42 +6779,48 @@
       <c r="Q22" s="52" t="s">
         <v>909</v>
       </c>
-      <c r="R22" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S22" s="51" t="str">
+      <c r="R22" s="55" t="s">
+        <v>876</v>
+      </c>
+      <c r="S22" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T22" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T22" s="51" t="str">
+      <c r="U22" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U22" s="50" t="str">
+      <c r="V22" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V22" s="33" t="s">
+      <c r="W22" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W22" s="56" t="str">
+      <c r="X22" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-22</v>
       </c>
-      <c r="X22" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y22" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z22" s="55" t="s">
+      <c r="Z22" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA22" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB22" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC22" s="55" t="s">
         <v>809</v>
       </c>
-      <c r="AA22" s="55" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="48">
         <v>23</v>
       </c>
@@ -6708,42 +6876,48 @@
       <c r="Q23" s="52" t="s">
         <v>910</v>
       </c>
-      <c r="R23" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S23" s="51" t="str">
+      <c r="R23" s="55" t="s">
+        <v>877</v>
+      </c>
+      <c r="S23" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T23" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T23" s="51" t="str">
+      <c r="U23" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U23" s="50" t="str">
+      <c r="V23" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V23" s="33" t="s">
+      <c r="W23" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W23" s="56" t="str">
+      <c r="X23" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-23</v>
       </c>
-      <c r="X23" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y23" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z23" s="55" t="s">
+      <c r="Z23" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA23" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB23" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC23" s="55" t="s">
         <v>810</v>
       </c>
-      <c r="AA23" s="55" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="48">
         <v>24</v>
       </c>
@@ -6799,42 +6973,48 @@
       <c r="Q24" s="52" t="s">
         <v>911</v>
       </c>
-      <c r="R24" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S24" s="51" t="str">
+      <c r="R24" s="55" t="s">
+        <v>878</v>
+      </c>
+      <c r="S24" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T24" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T24" s="51" t="str">
+      <c r="U24" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U24" s="50" t="str">
+      <c r="V24" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V24" s="33" t="s">
+      <c r="W24" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W24" s="56" t="str">
+      <c r="X24" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-24</v>
       </c>
-      <c r="X24" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y24" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z24" s="55" t="s">
+      <c r="Z24" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA24" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB24" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC24" s="55" t="s">
         <v>811</v>
       </c>
-      <c r="AA24" s="55" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="48">
         <v>25</v>
       </c>
@@ -6890,42 +7070,48 @@
       <c r="Q25" s="52" t="s">
         <v>912</v>
       </c>
-      <c r="R25" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S25" s="51" t="str">
+      <c r="R25" s="55" t="s">
+        <v>879</v>
+      </c>
+      <c r="S25" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T25" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T25" s="51" t="str">
+      <c r="U25" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U25" s="50" t="str">
+      <c r="V25" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V25" s="33" t="s">
+      <c r="W25" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W25" s="56" t="str">
+      <c r="X25" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-25</v>
       </c>
-      <c r="X25" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y25" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z25" s="55" t="s">
+      <c r="Z25" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA25" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB25" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC25" s="55" t="s">
         <v>812</v>
       </c>
-      <c r="AA25" s="55" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="48">
         <v>26</v>
       </c>
@@ -6981,42 +7167,48 @@
       <c r="Q26" s="52" t="s">
         <v>913</v>
       </c>
-      <c r="R26" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S26" s="51" t="str">
+      <c r="R26" s="55" t="s">
+        <v>880</v>
+      </c>
+      <c r="S26" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T26" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T26" s="51" t="str">
+      <c r="U26" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U26" s="50" t="str">
+      <c r="V26" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V26" s="33" t="s">
+      <c r="W26" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W26" s="56" t="str">
+      <c r="X26" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-26</v>
       </c>
-      <c r="X26" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y26" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z26" s="55" t="s">
+      <c r="Z26" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA26" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB26" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC26" s="55" t="s">
         <v>813</v>
       </c>
-      <c r="AA26" s="55" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="48">
         <v>27</v>
       </c>
@@ -7072,42 +7264,48 @@
       <c r="Q27" s="52" t="s">
         <v>914</v>
       </c>
-      <c r="R27" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S27" s="51" t="str">
+      <c r="R27" s="55" t="s">
+        <v>881</v>
+      </c>
+      <c r="S27" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T27" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T27" s="51" t="str">
+      <c r="U27" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U27" s="50" t="str">
+      <c r="V27" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V27" s="33" t="s">
+      <c r="W27" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W27" s="56" t="str">
+      <c r="X27" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-27</v>
       </c>
-      <c r="X27" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y27" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z27" s="55" t="s">
+      <c r="Z27" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA27" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB27" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC27" s="55" t="s">
         <v>814</v>
       </c>
-      <c r="AA27" s="55" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="48">
         <v>28</v>
       </c>
@@ -7163,42 +7361,48 @@
       <c r="Q28" s="52" t="s">
         <v>915</v>
       </c>
-      <c r="R28" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S28" s="51" t="str">
+      <c r="R28" s="55" t="s">
+        <v>882</v>
+      </c>
+      <c r="S28" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T28" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T28" s="51" t="str">
+      <c r="U28" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U28" s="50" t="str">
+      <c r="V28" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V28" s="33" t="s">
+      <c r="W28" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W28" s="56" t="str">
+      <c r="X28" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-28</v>
       </c>
-      <c r="X28" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y28" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z28" s="55" t="s">
+      <c r="Z28" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA28" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB28" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC28" s="55" t="s">
         <v>815</v>
       </c>
-      <c r="AA28" s="55" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="48">
         <v>29</v>
       </c>
@@ -7254,42 +7458,48 @@
       <c r="Q29" s="52" t="s">
         <v>916</v>
       </c>
-      <c r="R29" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S29" s="51" t="str">
+      <c r="R29" s="55" t="s">
+        <v>883</v>
+      </c>
+      <c r="S29" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T29" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T29" s="51" t="str">
+      <c r="U29" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U29" s="50" t="str">
+      <c r="V29" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V29" s="33" t="s">
+      <c r="W29" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W29" s="56" t="str">
+      <c r="X29" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-29</v>
       </c>
-      <c r="X29" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y29" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z29" s="55" t="s">
+      <c r="Z29" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA29" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB29" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC29" s="55" t="s">
         <v>816</v>
       </c>
-      <c r="AA29" s="55" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="48">
         <v>30</v>
       </c>
@@ -7345,42 +7555,48 @@
       <c r="Q30" s="52" t="s">
         <v>917</v>
       </c>
-      <c r="R30" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S30" s="51" t="str">
+      <c r="R30" s="55" t="s">
+        <v>884</v>
+      </c>
+      <c r="S30" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T30" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T30" s="51" t="str">
+      <c r="U30" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U30" s="50" t="str">
+      <c r="V30" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V30" s="33" t="s">
+      <c r="W30" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W30" s="56" t="str">
+      <c r="X30" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-30</v>
       </c>
-      <c r="X30" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y30" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z30" s="55" t="s">
+      <c r="Z30" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA30" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB30" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC30" s="55" t="s">
         <v>817</v>
       </c>
-      <c r="AA30" s="55" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="48">
         <v>31</v>
       </c>
@@ -7436,42 +7652,48 @@
       <c r="Q31" s="52" t="s">
         <v>918</v>
       </c>
-      <c r="R31" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S31" s="51" t="str">
+      <c r="R31" s="55" t="s">
+        <v>885</v>
+      </c>
+      <c r="S31" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T31" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T31" s="51" t="str">
+      <c r="U31" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U31" s="50" t="str">
+      <c r="V31" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V31" s="33" t="s">
+      <c r="W31" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W31" s="56" t="str">
+      <c r="X31" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-31</v>
       </c>
-      <c r="X31" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y31" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z31" s="55" t="s">
+      <c r="Z31" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA31" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB31" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC31" s="55" t="s">
         <v>818</v>
       </c>
-      <c r="AA31" s="55" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="48">
         <v>32</v>
       </c>
@@ -7527,42 +7749,48 @@
       <c r="Q32" s="52" t="s">
         <v>919</v>
       </c>
-      <c r="R32" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S32" s="51" t="str">
+      <c r="R32" s="55" t="s">
+        <v>886</v>
+      </c>
+      <c r="S32" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T32" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T32" s="51" t="str">
+      <c r="U32" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U32" s="50" t="str">
+      <c r="V32" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V32" s="33" t="s">
+      <c r="W32" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W32" s="56" t="str">
+      <c r="X32" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-32</v>
       </c>
-      <c r="X32" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y32" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z32" s="55" t="s">
+      <c r="Z32" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA32" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB32" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC32" s="55" t="s">
         <v>819</v>
       </c>
-      <c r="AA32" s="55" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48">
         <v>33</v>
       </c>
@@ -7618,42 +7846,48 @@
       <c r="Q33" s="52" t="s">
         <v>920</v>
       </c>
-      <c r="R33" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S33" s="51" t="str">
+      <c r="R33" s="55" t="s">
+        <v>887</v>
+      </c>
+      <c r="S33" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T33" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T33" s="51" t="str">
+      <c r="U33" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U33" s="50" t="str">
+      <c r="V33" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V33" s="33" t="s">
+      <c r="W33" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W33" s="56" t="str">
+      <c r="X33" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-33</v>
       </c>
-      <c r="X33" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y33" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z33" s="55" t="s">
+      <c r="Z33" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA33" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB33" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC33" s="55" t="s">
         <v>820</v>
       </c>
-      <c r="AA33" s="55" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="48">
         <v>34</v>
       </c>
@@ -7709,42 +7943,48 @@
       <c r="Q34" s="52" t="s">
         <v>921</v>
       </c>
-      <c r="R34" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S34" s="51" t="str">
+      <c r="R34" s="55" t="s">
+        <v>888</v>
+      </c>
+      <c r="S34" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T34" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T34" s="51" t="str">
+      <c r="U34" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U34" s="50" t="str">
+      <c r="V34" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V34" s="33" t="s">
+      <c r="W34" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W34" s="56" t="str">
+      <c r="X34" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-34</v>
       </c>
-      <c r="X34" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y34" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z34" s="55" t="s">
+      <c r="Z34" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA34" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB34" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC34" s="55" t="s">
         <v>821</v>
       </c>
-      <c r="AA34" s="55" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="48">
         <v>35</v>
       </c>
@@ -7800,42 +8040,48 @@
       <c r="Q35" s="52" t="s">
         <v>922</v>
       </c>
-      <c r="R35" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S35" s="51" t="str">
+      <c r="R35" s="55" t="s">
+        <v>889</v>
+      </c>
+      <c r="S35" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T35" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T35" s="51" t="str">
+      <c r="U35" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U35" s="50" t="str">
+      <c r="V35" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V35" s="33" t="s">
+      <c r="W35" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W35" s="56" t="str">
+      <c r="X35" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-35</v>
       </c>
-      <c r="X35" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y35" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z35" s="55" t="s">
+      <c r="Z35" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA35" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB35" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC35" s="55" t="s">
         <v>822</v>
       </c>
-      <c r="AA35" s="55" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="48">
         <v>36</v>
       </c>
@@ -7891,42 +8137,48 @@
       <c r="Q36" s="52" t="s">
         <v>923</v>
       </c>
-      <c r="R36" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S36" s="51" t="str">
+      <c r="R36" s="55" t="s">
+        <v>890</v>
+      </c>
+      <c r="S36" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T36" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T36" s="51" t="str">
+      <c r="U36" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U36" s="50" t="str">
+      <c r="V36" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V36" s="33" t="s">
+      <c r="W36" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W36" s="56" t="str">
+      <c r="X36" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-36</v>
       </c>
-      <c r="X36" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y36" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z36" s="55" t="s">
+      <c r="Z36" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA36" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB36" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC36" s="55" t="s">
         <v>823</v>
       </c>
-      <c r="AA36" s="55" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="48">
         <v>37</v>
       </c>
@@ -7982,42 +8234,48 @@
       <c r="Q37" s="52" t="s">
         <v>924</v>
       </c>
-      <c r="R37" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S37" s="51" t="str">
+      <c r="R37" s="55" t="s">
+        <v>891</v>
+      </c>
+      <c r="S37" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T37" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T37" s="51" t="str">
+      <c r="U37" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U37" s="50" t="str">
+      <c r="V37" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V37" s="33" t="s">
+      <c r="W37" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W37" s="56" t="str">
+      <c r="X37" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-37</v>
       </c>
-      <c r="X37" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y37" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z37" s="55" t="s">
+      <c r="Z37" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA37" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB37" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC37" s="55" t="s">
         <v>824</v>
       </c>
-      <c r="AA37" s="55" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="48">
         <v>38</v>
       </c>
@@ -8073,42 +8331,48 @@
       <c r="Q38" s="52" t="s">
         <v>925</v>
       </c>
-      <c r="R38" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S38" s="51" t="str">
+      <c r="R38" s="55" t="s">
+        <v>892</v>
+      </c>
+      <c r="S38" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T38" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T38" s="51" t="str">
+      <c r="U38" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U38" s="50" t="str">
+      <c r="V38" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V38" s="33" t="s">
+      <c r="W38" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W38" s="56" t="str">
+      <c r="X38" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-38</v>
       </c>
-      <c r="X38" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y38" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z38" s="55" t="s">
+      <c r="Z38" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA38" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB38" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC38" s="55" t="s">
         <v>825</v>
       </c>
-      <c r="AA38" s="55" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="48">
         <v>39</v>
       </c>
@@ -8164,42 +8428,48 @@
       <c r="Q39" s="52" t="s">
         <v>926</v>
       </c>
-      <c r="R39" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S39" s="51" t="str">
+      <c r="R39" s="55" t="s">
+        <v>893</v>
+      </c>
+      <c r="S39" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T39" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T39" s="51" t="str">
+      <c r="U39" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U39" s="50" t="str">
+      <c r="V39" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V39" s="33" t="s">
+      <c r="W39" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W39" s="56" t="str">
+      <c r="X39" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-39</v>
       </c>
-      <c r="X39" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y39" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z39" s="55" t="s">
+      <c r="Z39" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA39" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB39" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC39" s="55" t="s">
         <v>826</v>
       </c>
-      <c r="AA39" s="55" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="48">
         <v>40</v>
       </c>
@@ -8255,42 +8525,48 @@
       <c r="Q40" s="52" t="s">
         <v>927</v>
       </c>
-      <c r="R40" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S40" s="51" t="str">
+      <c r="R40" s="55" t="s">
+        <v>894</v>
+      </c>
+      <c r="S40" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T40" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T40" s="51" t="str">
+      <c r="U40" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U40" s="50" t="str">
+      <c r="V40" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V40" s="33" t="s">
+      <c r="W40" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W40" s="56" t="str">
+      <c r="X40" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-40</v>
       </c>
-      <c r="X40" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y40" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z40" s="55" t="s">
+      <c r="Z40" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA40" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB40" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC40" s="55" t="s">
         <v>827</v>
       </c>
-      <c r="AA40" s="55" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="48">
         <v>41</v>
       </c>
@@ -8346,42 +8622,48 @@
       <c r="Q41" s="52" t="s">
         <v>928</v>
       </c>
-      <c r="R41" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S41" s="51" t="str">
+      <c r="R41" s="55" t="s">
+        <v>895</v>
+      </c>
+      <c r="S41" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T41" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T41" s="51" t="str">
+      <c r="U41" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U41" s="50" t="str">
+      <c r="V41" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V41" s="33" t="s">
+      <c r="W41" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W41" s="56" t="str">
+      <c r="X41" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-41</v>
       </c>
-      <c r="X41" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y41" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z41" s="55" t="s">
+      <c r="Z41" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA41" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB41" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC41" s="55" t="s">
         <v>828</v>
       </c>
-      <c r="AA41" s="55" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="48">
         <v>42</v>
       </c>
@@ -8437,42 +8719,48 @@
       <c r="Q42" s="52" t="s">
         <v>929</v>
       </c>
-      <c r="R42" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S42" s="51" t="str">
+      <c r="R42" s="55" t="s">
+        <v>896</v>
+      </c>
+      <c r="S42" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T42" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T42" s="51" t="str">
+      <c r="U42" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U42" s="50" t="str">
+      <c r="V42" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V42" s="33" t="s">
+      <c r="W42" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W42" s="56" t="str">
+      <c r="X42" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-42</v>
       </c>
-      <c r="X42" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y42" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z42" s="55" t="s">
+      <c r="Z42" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA42" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB42" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC42" s="55" t="s">
         <v>829</v>
       </c>
-      <c r="AA42" s="55" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="48">
         <v>43</v>
       </c>
@@ -8528,42 +8816,48 @@
       <c r="Q43" s="52" t="s">
         <v>930</v>
       </c>
-      <c r="R43" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S43" s="51" t="str">
+      <c r="R43" s="55" t="s">
+        <v>897</v>
+      </c>
+      <c r="S43" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T43" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T43" s="51" t="str">
+      <c r="U43" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U43" s="50" t="str">
+      <c r="V43" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V43" s="33" t="s">
+      <c r="W43" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W43" s="56" t="str">
+      <c r="X43" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-43</v>
       </c>
-      <c r="X43" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y43" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z43" s="55" t="s">
+      <c r="Z43" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA43" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB43" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC43" s="55" t="s">
         <v>830</v>
       </c>
-      <c r="AA43" s="55" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="48">
         <v>44</v>
       </c>
@@ -8619,42 +8913,48 @@
       <c r="Q44" s="52" t="s">
         <v>931</v>
       </c>
-      <c r="R44" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S44" s="51" t="str">
+      <c r="R44" s="55" t="s">
+        <v>898</v>
+      </c>
+      <c r="S44" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T44" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T44" s="51" t="str">
+      <c r="U44" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U44" s="50" t="str">
+      <c r="V44" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V44" s="33" t="s">
+      <c r="W44" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W44" s="56" t="str">
+      <c r="X44" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-44</v>
       </c>
-      <c r="X44" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y44" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z44" s="55" t="s">
+      <c r="Z44" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA44" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB44" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC44" s="55" t="s">
         <v>831</v>
       </c>
-      <c r="AA44" s="55" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="48">
         <v>45</v>
       </c>
@@ -8710,42 +9010,48 @@
       <c r="Q45" s="52" t="s">
         <v>932</v>
       </c>
-      <c r="R45" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S45" s="51" t="str">
+      <c r="R45" s="55" t="s">
+        <v>899</v>
+      </c>
+      <c r="S45" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T45" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T45" s="51" t="str">
+      <c r="U45" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U45" s="50" t="str">
+      <c r="V45" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V45" s="33" t="s">
+      <c r="W45" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W45" s="56" t="str">
+      <c r="X45" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-45</v>
       </c>
-      <c r="X45" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y45" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z45" s="55" t="s">
+      <c r="Z45" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA45" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB45" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC45" s="55" t="s">
         <v>832</v>
       </c>
-      <c r="AA45" s="55" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="48">
         <v>46</v>
       </c>
@@ -8801,42 +9107,48 @@
       <c r="Q46" s="52" t="s">
         <v>933</v>
       </c>
-      <c r="R46" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S46" s="51" t="str">
+      <c r="R46" s="55" t="s">
+        <v>900</v>
+      </c>
+      <c r="S46" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T46" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T46" s="51" t="str">
+      <c r="U46" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U46" s="50" t="str">
+      <c r="V46" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V46" s="33" t="s">
+      <c r="W46" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W46" s="56" t="str">
+      <c r="X46" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-46</v>
       </c>
-      <c r="X46" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y46" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z46" s="55" t="s">
+      <c r="Z46" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA46" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB46" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC46" s="55" t="s">
         <v>833</v>
       </c>
-      <c r="AA46" s="55" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="47" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="48">
         <v>47</v>
       </c>
@@ -8892,58 +9204,73 @@
       <c r="Q47" s="52" t="s">
         <v>934</v>
       </c>
-      <c r="R47" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="S47" s="51" t="str">
+      <c r="R47" s="55" t="s">
+        <v>901</v>
+      </c>
+      <c r="S47" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T47" s="51" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T47" s="51" t="str">
+      <c r="U47" s="51" t="str">
         <f t="shared" si="9"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U47" s="50" t="str">
+      <c r="V47" s="50" t="str">
         <f t="shared" si="10"/>
         <v>NBR.Recursos</v>
       </c>
-      <c r="V47" s="33" t="s">
+      <c r="W47" s="33" t="s">
         <v>716</v>
       </c>
-      <c r="W47" s="56" t="str">
+      <c r="X47" s="56" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-47</v>
       </c>
-      <c r="X47" s="33" t="s">
-        <v>1017</v>
-      </c>
       <c r="Y47" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z47" s="55" t="s">
+      <c r="Z47" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AA47" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AB47" s="33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AC47" s="55" t="s">
         <v>834</v>
       </c>
-      <c r="AA47" s="55" t="s">
-        <v>901</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y2">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B47">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z15:AA47">
-    <cfRule type="duplicateValues" dxfId="8" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="26"/>
+  <conditionalFormatting sqref="F2:F14">
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA14 A2:B47">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+  <conditionalFormatting sqref="R1:R14">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R15:R47">
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2 AA2">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC15:AC47">
+    <cfRule type="duplicateValues" dxfId="7" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="31"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -8956,13 +9283,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B5591C-1220-489B-957E-6F42AD7CFACA}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>650</v>
       </c>
@@ -9027,7 +9354,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -9109,13 +9436,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26462613-E7D7-4ABD-BD2B-4B8A0B104ED0}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="17.19921875" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="26">
         <v>1</v>
       </c>
@@ -9126,7 +9453,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="17">
         <v>2</v>
       </c>
@@ -9151,35 +9478,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4160801D-A855-4DB1-BB60-92D2B856BA2E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AA303"/>
-  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.69921875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.19921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="47" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.296875" style="47" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" style="47" customWidth="1"/>
     <col min="8" max="8" width="5" style="47" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.69921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" style="47" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" style="47" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.19921875" style="47" customWidth="1"/>
+    <col min="11" max="11" width="9.1640625" style="47" customWidth="1"/>
     <col min="12" max="12" width="6.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="25.296875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="25.33203125" style="1" customWidth="1"/>
     <col min="14" max="14" width="7" style="47" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="82.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.796875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="82.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" style="1" customWidth="1"/>
     <col min="17" max="17" width="4.5" style="1" customWidth="1"/>
     <col min="18" max="18" width="6.5" style="1" customWidth="1"/>
     <col min="19" max="19" width="4.5" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.296875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="5.69921875" style="1" customWidth="1"/>
-    <col min="22" max="26" width="5.19921875" style="47" customWidth="1"/>
-    <col min="27" max="27" width="4.296875" style="47" customWidth="1"/>
-    <col min="28" max="16384" width="9.19921875" style="1"/>
+    <col min="20" max="20" width="6.33203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" style="1" customWidth="1"/>
+    <col min="22" max="26" width="5.1640625" style="47" customWidth="1"/>
+    <col min="27" max="27" width="4.33203125" style="47" customWidth="1"/>
+    <col min="28" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>333</v>
       </c>
@@ -9262,7 +9589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -9345,7 +9672,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -9428,7 +9755,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>4</v>
       </c>
@@ -9511,7 +9838,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>5</v>
       </c>
@@ -9594,7 +9921,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>6</v>
       </c>
@@ -9677,7 +10004,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>7</v>
       </c>
@@ -9760,7 +10087,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>8</v>
       </c>
@@ -9843,7 +10170,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>9</v>
       </c>
@@ -9926,7 +10253,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>10</v>
       </c>
@@ -10009,7 +10336,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>11</v>
       </c>
@@ -10092,7 +10419,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>12</v>
       </c>
@@ -10175,7 +10502,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>13</v>
       </c>
@@ -10258,7 +10585,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>14</v>
       </c>
@@ -10341,7 +10668,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>15</v>
       </c>
@@ -10424,7 +10751,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>16</v>
       </c>
@@ -10507,7 +10834,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>17</v>
       </c>
@@ -10590,7 +10917,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>18</v>
       </c>
@@ -10673,7 +11000,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>19</v>
       </c>
@@ -10756,7 +11083,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>20</v>
       </c>
@@ -10839,7 +11166,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>21</v>
       </c>
@@ -10922,7 +11249,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>22</v>
       </c>
@@ -11005,7 +11332,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>23</v>
       </c>
@@ -11088,7 +11415,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>24</v>
       </c>
@@ -11171,7 +11498,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>25</v>
       </c>
@@ -11254,7 +11581,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>26</v>
       </c>
@@ -11337,7 +11664,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>27</v>
       </c>
@@ -11420,7 +11747,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>28</v>
       </c>
@@ -11503,7 +11830,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>29</v>
       </c>
@@ -11586,7 +11913,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>30</v>
       </c>
@@ -11669,7 +11996,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>31</v>
       </c>
@@ -11752,7 +12079,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>32</v>
       </c>
@@ -11835,7 +12162,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>33</v>
       </c>
@@ -11918,7 +12245,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>34</v>
       </c>
@@ -12001,7 +12328,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>35</v>
       </c>
@@ -12084,7 +12411,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>36</v>
       </c>
@@ -12167,7 +12494,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>37</v>
       </c>
@@ -12250,7 +12577,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>38</v>
       </c>
@@ -12333,7 +12660,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>39</v>
       </c>
@@ -12416,7 +12743,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>40</v>
       </c>
@@ -12499,7 +12826,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>41</v>
       </c>
@@ -12582,7 +12909,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>42</v>
       </c>
@@ -12665,7 +12992,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>43</v>
       </c>
@@ -12748,7 +13075,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>44</v>
       </c>
@@ -12831,7 +13158,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>45</v>
       </c>
@@ -12914,7 +13241,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>46</v>
       </c>
@@ -12997,7 +13324,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>47</v>
       </c>
@@ -13080,7 +13407,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>48</v>
       </c>
@@ -13163,7 +13490,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>49</v>
       </c>
@@ -13246,7 +13573,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>50</v>
       </c>
@@ -13329,7 +13656,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>51</v>
       </c>
@@ -13412,7 +13739,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>52</v>
       </c>
@@ -13495,7 +13822,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>53</v>
       </c>
@@ -13578,7 +13905,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>54</v>
       </c>
@@ -13661,7 +13988,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>55</v>
       </c>
@@ -13744,7 +14071,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>56</v>
       </c>
@@ -13827,7 +14154,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>57</v>
       </c>
@@ -13910,7 +14237,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>58</v>
       </c>
@@ -13993,7 +14320,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>59</v>
       </c>
@@ -14076,7 +14403,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>60</v>
       </c>
@@ -14159,7 +14486,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>61</v>
       </c>
@@ -14242,7 +14569,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>62</v>
       </c>
@@ -14325,7 +14652,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>63</v>
       </c>
@@ -14408,7 +14735,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>64</v>
       </c>
@@ -14491,7 +14818,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>65</v>
       </c>
@@ -14574,7 +14901,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>66</v>
       </c>
@@ -14657,7 +14984,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>67</v>
       </c>
@@ -14740,7 +15067,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>68</v>
       </c>
@@ -14823,7 +15150,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>69</v>
       </c>
@@ -14906,7 +15233,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>70</v>
       </c>
@@ -14989,7 +15316,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>71</v>
       </c>
@@ -15072,7 +15399,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>72</v>
       </c>
@@ -15155,7 +15482,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>73</v>
       </c>
@@ -15238,7 +15565,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>74</v>
       </c>
@@ -15321,7 +15648,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>75</v>
       </c>
@@ -15404,7 +15731,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>76</v>
       </c>
@@ -15487,7 +15814,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>77</v>
       </c>
@@ -15570,7 +15897,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>78</v>
       </c>
@@ -15653,7 +15980,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>79</v>
       </c>
@@ -15736,7 +16063,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>80</v>
       </c>
@@ -15819,7 +16146,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>81</v>
       </c>
@@ -15902,7 +16229,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>82</v>
       </c>
@@ -15985,7 +16312,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>83</v>
       </c>
@@ -16068,7 +16395,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>84</v>
       </c>
@@ -16151,7 +16478,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>85</v>
       </c>
@@ -16234,7 +16561,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>86</v>
       </c>
@@ -16317,7 +16644,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>87</v>
       </c>
@@ -16400,7 +16727,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>88</v>
       </c>
@@ -16483,7 +16810,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -16566,7 +16893,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>90</v>
       </c>
@@ -16649,7 +16976,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>91</v>
       </c>
@@ -16732,7 +17059,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>92</v>
       </c>
@@ -16815,7 +17142,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>93</v>
       </c>
@@ -16898,7 +17225,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>94</v>
       </c>
@@ -16981,7 +17308,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>95</v>
       </c>
@@ -17064,7 +17391,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>96</v>
       </c>
@@ -17147,7 +17474,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>97</v>
       </c>
@@ -17230,7 +17557,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>98</v>
       </c>
@@ -17313,7 +17640,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -17396,7 +17723,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>100</v>
       </c>
@@ -17479,7 +17806,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>101</v>
       </c>
@@ -17562,7 +17889,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>102</v>
       </c>
@@ -17645,7 +17972,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>103</v>
       </c>
@@ -17728,7 +18055,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>104</v>
       </c>
@@ -17811,7 +18138,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>105</v>
       </c>
@@ -17894,7 +18221,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>106</v>
       </c>
@@ -17977,7 +18304,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -18060,7 +18387,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -18143,7 +18470,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>109</v>
       </c>
@@ -18226,7 +18553,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>110</v>
       </c>
@@ -18309,7 +18636,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>111</v>
       </c>
@@ -18392,7 +18719,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>112</v>
       </c>
@@ -18475,7 +18802,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>113</v>
       </c>
@@ -18558,7 +18885,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>114</v>
       </c>
@@ -18641,7 +18968,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>115</v>
       </c>
@@ -18724,7 +19051,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>116</v>
       </c>
@@ -18807,7 +19134,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>117</v>
       </c>
@@ -18890,7 +19217,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>118</v>
       </c>
@@ -18973,7 +19300,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>119</v>
       </c>
@@ -19056,7 +19383,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>120</v>
       </c>
@@ -19139,7 +19466,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>121</v>
       </c>
@@ -19222,7 +19549,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>122</v>
       </c>
@@ -19305,7 +19632,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>123</v>
       </c>
@@ -19388,7 +19715,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>124</v>
       </c>
@@ -19471,7 +19798,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>125</v>
       </c>
@@ -19554,7 +19881,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>126</v>
       </c>
@@ -19637,7 +19964,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>127</v>
       </c>
@@ -19720,7 +20047,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>128</v>
       </c>
@@ -19803,7 +20130,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>129</v>
       </c>
@@ -19886,7 +20213,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="6">
         <v>130</v>
       </c>
@@ -19969,7 +20296,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>131</v>
       </c>
@@ -20052,7 +20379,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="6">
         <v>132</v>
       </c>
@@ -20135,7 +20462,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>133</v>
       </c>
@@ -20218,7 +20545,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="6">
         <v>134</v>
       </c>
@@ -20301,7 +20628,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>135</v>
       </c>
@@ -20384,7 +20711,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="6">
         <v>136</v>
       </c>
@@ -20467,7 +20794,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>137</v>
       </c>
@@ -20550,7 +20877,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="6">
         <v>138</v>
       </c>
@@ -20633,7 +20960,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>139</v>
       </c>
@@ -20716,7 +21043,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="6">
         <v>140</v>
       </c>
@@ -20799,7 +21126,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>141</v>
       </c>
@@ -20882,7 +21209,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="6">
         <v>142</v>
       </c>
@@ -20965,7 +21292,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>143</v>
       </c>
@@ -21048,7 +21375,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="6">
         <v>144</v>
       </c>
@@ -21131,7 +21458,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>145</v>
       </c>
@@ -21214,7 +21541,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="6">
         <v>146</v>
       </c>
@@ -21297,7 +21624,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="147" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>147</v>
       </c>
@@ -21380,7 +21707,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="6">
         <v>148</v>
       </c>
@@ -21463,7 +21790,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="149" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>149</v>
       </c>
@@ -21546,7 +21873,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="150" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="6">
         <v>150</v>
       </c>
@@ -21629,7 +21956,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>151</v>
       </c>
@@ -21712,7 +22039,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="6">
         <v>152</v>
       </c>
@@ -21795,7 +22122,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="153" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>153</v>
       </c>
@@ -21878,7 +22205,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="154" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="6">
         <v>154</v>
       </c>
@@ -21961,7 +22288,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="155" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>155</v>
       </c>
@@ -22044,7 +22371,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="6">
         <v>156</v>
       </c>
@@ -22127,7 +22454,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>157</v>
       </c>
@@ -22210,7 +22537,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="158" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="6">
         <v>158</v>
       </c>
@@ -22293,7 +22620,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="159" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>159</v>
       </c>
@@ -22376,7 +22703,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="160" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="6">
         <v>160</v>
       </c>
@@ -22459,7 +22786,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="161" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>161</v>
       </c>
@@ -22542,7 +22869,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="162" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="6">
         <v>162</v>
       </c>
@@ -22625,7 +22952,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="163" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>163</v>
       </c>
@@ -22708,7 +23035,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="164" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="6">
         <v>164</v>
       </c>
@@ -22791,7 +23118,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="165" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>165</v>
       </c>
@@ -22874,7 +23201,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="166" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="6">
         <v>166</v>
       </c>
@@ -22957,7 +23284,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>167</v>
       </c>
@@ -23040,7 +23367,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="168" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="6">
         <v>168</v>
       </c>
@@ -23123,7 +23450,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="169" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>169</v>
       </c>
@@ -23206,7 +23533,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="170" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="6">
         <v>170</v>
       </c>
@@ -23289,7 +23616,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="171" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>171</v>
       </c>
@@ -23372,7 +23699,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="172" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="6">
         <v>172</v>
       </c>
@@ -23455,7 +23782,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="173" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>173</v>
       </c>
@@ -23538,7 +23865,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="174" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="6">
         <v>174</v>
       </c>
@@ -23621,7 +23948,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="175" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>175</v>
       </c>
@@ -23704,7 +24031,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="176" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="6">
         <v>176</v>
       </c>
@@ -23787,7 +24114,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="177" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>177</v>
       </c>
@@ -23870,7 +24197,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="178" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="6">
         <v>178</v>
       </c>
@@ -23953,7 +24280,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="179" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>179</v>
       </c>
@@ -24036,7 +24363,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="180" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="6">
         <v>180</v>
       </c>
@@ -24119,7 +24446,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="181" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -24202,7 +24529,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="182" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="6">
         <v>182</v>
       </c>
@@ -24285,7 +24612,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="183" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>183</v>
       </c>
@@ -24368,7 +24695,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="184" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="6">
         <v>184</v>
       </c>
@@ -24451,7 +24778,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="185" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>185</v>
       </c>
@@ -24534,7 +24861,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="186" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="6">
         <v>186</v>
       </c>
@@ -24617,7 +24944,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="187" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>187</v>
       </c>
@@ -24700,7 +25027,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="188" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="6">
         <v>188</v>
       </c>
@@ -24783,7 +25110,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="189" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>189</v>
       </c>
@@ -24866,7 +25193,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="190" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="6">
         <v>190</v>
       </c>
@@ -24949,7 +25276,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="191" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>191</v>
       </c>
@@ -25032,7 +25359,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="192" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="6">
         <v>192</v>
       </c>
@@ -25115,7 +25442,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="193" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>193</v>
       </c>
@@ -25198,7 +25525,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="194" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="6">
         <v>194</v>
       </c>
@@ -25281,7 +25608,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="195" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>195</v>
       </c>
@@ -25364,7 +25691,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="196" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="6">
         <v>196</v>
       </c>
@@ -25447,7 +25774,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="197" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>197</v>
       </c>
@@ -25530,7 +25857,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="198" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="6">
         <v>198</v>
       </c>
@@ -25613,7 +25940,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="199" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>199</v>
       </c>
@@ -25696,7 +26023,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="200" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="6">
         <v>200</v>
       </c>
@@ -25779,7 +26106,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="201" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>201</v>
       </c>
@@ -25862,7 +26189,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="202" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="6">
         <v>202</v>
       </c>
@@ -25945,7 +26272,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="203" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>203</v>
       </c>
@@ -26028,7 +26355,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="204" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="6">
         <v>204</v>
       </c>
@@ -26111,7 +26438,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="205" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>205</v>
       </c>
@@ -26194,7 +26521,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="206" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="6">
         <v>206</v>
       </c>
@@ -26277,7 +26604,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="207" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>207</v>
       </c>
@@ -26360,7 +26687,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="208" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="6">
         <v>208</v>
       </c>
@@ -26443,7 +26770,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="209" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>209</v>
       </c>
@@ -26526,7 +26853,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="210" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="6">
         <v>210</v>
       </c>
@@ -26609,7 +26936,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="211" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>211</v>
       </c>
@@ -26692,7 +27019,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="212" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="6">
         <v>212</v>
       </c>
@@ -26775,7 +27102,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="213" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>213</v>
       </c>
@@ -26858,7 +27185,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="214" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="6">
         <v>214</v>
       </c>
@@ -26941,7 +27268,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="215" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>215</v>
       </c>
@@ -27024,7 +27351,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="216" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="6">
         <v>216</v>
       </c>
@@ -27107,7 +27434,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="217" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>217</v>
       </c>
@@ -27190,7 +27517,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="218" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -27273,7 +27600,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="219" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>219</v>
       </c>
@@ -27356,7 +27683,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="220" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="6">
         <v>220</v>
       </c>
@@ -27439,7 +27766,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="221" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>221</v>
       </c>
@@ -27522,7 +27849,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="222" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="6">
         <v>222</v>
       </c>
@@ -27605,7 +27932,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="223" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>223</v>
       </c>
@@ -27688,7 +28015,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="224" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="6">
         <v>224</v>
       </c>
@@ -27771,7 +28098,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="225" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>225</v>
       </c>
@@ -27854,7 +28181,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="226" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="6">
         <v>226</v>
       </c>
@@ -27937,7 +28264,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="227" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>227</v>
       </c>
@@ -28020,7 +28347,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="228" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="6">
         <v>228</v>
       </c>
@@ -28103,7 +28430,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="229" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>229</v>
       </c>
@@ -28186,7 +28513,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="230" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="6">
         <v>230</v>
       </c>
@@ -28269,7 +28596,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="231" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>231</v>
       </c>
@@ -28352,7 +28679,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="232" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="6">
         <v>232</v>
       </c>
@@ -28435,7 +28762,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="233" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>233</v>
       </c>
@@ -28518,7 +28845,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="234" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="6">
         <v>234</v>
       </c>
@@ -28601,7 +28928,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="235" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>235</v>
       </c>
@@ -28684,7 +29011,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="236" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="6">
         <v>236</v>
       </c>
@@ -28767,7 +29094,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="237" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>237</v>
       </c>
@@ -28850,7 +29177,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="238" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="6">
         <v>238</v>
       </c>
@@ -28933,7 +29260,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="239" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>239</v>
       </c>
@@ -29016,7 +29343,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="240" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="6">
         <v>240</v>
       </c>
@@ -29099,7 +29426,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="241" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>241</v>
       </c>
@@ -29182,7 +29509,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="242" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="6">
         <v>242</v>
       </c>
@@ -29265,7 +29592,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="243" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>243</v>
       </c>
@@ -29348,7 +29675,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="244" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="6">
         <v>244</v>
       </c>
@@ -29431,7 +29758,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="245" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>245</v>
       </c>
@@ -29514,7 +29841,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="246" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="6">
         <v>246</v>
       </c>
@@ -29597,7 +29924,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="247" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>247</v>
       </c>
@@ -29680,7 +30007,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="248" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="6">
         <v>248</v>
       </c>
@@ -29763,7 +30090,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="249" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>249</v>
       </c>
@@ -29846,7 +30173,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="250" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="6">
         <v>250</v>
       </c>
@@ -29929,7 +30256,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="251" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -30012,7 +30339,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="252" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="6">
         <v>252</v>
       </c>
@@ -30095,7 +30422,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="253" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>253</v>
       </c>
@@ -30178,7 +30505,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="254" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="6">
         <v>254</v>
       </c>
@@ -30261,7 +30588,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="255" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>255</v>
       </c>
@@ -30344,7 +30671,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="256" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="6">
         <v>256</v>
       </c>
@@ -30427,7 +30754,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="257" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="6">
         <v>257</v>
       </c>
@@ -30510,7 +30837,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="258" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="6">
         <v>258</v>
       </c>
@@ -30593,7 +30920,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="259" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="6">
         <v>259</v>
       </c>
@@ -30676,7 +31003,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="260" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="6">
         <v>260</v>
       </c>
@@ -30759,7 +31086,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="261" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="6">
         <v>261</v>
       </c>
@@ -30842,7 +31169,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="262" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="6">
         <v>262</v>
       </c>
@@ -30925,7 +31252,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="263" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="6">
         <v>263</v>
       </c>
@@ -31008,7 +31335,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="264" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="6">
         <v>264</v>
       </c>
@@ -31091,7 +31418,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="265" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="6">
         <v>265</v>
       </c>
@@ -31174,7 +31501,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="266" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="6">
         <v>266</v>
       </c>
@@ -31257,7 +31584,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="267" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="6">
         <v>267</v>
       </c>
@@ -31340,7 +31667,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="268" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="6">
         <v>268</v>
       </c>
@@ -31423,7 +31750,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="269" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="6">
         <v>269</v>
       </c>
@@ -31506,7 +31833,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="270" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="6">
         <v>270</v>
       </c>
@@ -31589,7 +31916,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="271" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -31672,7 +31999,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="272" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="6">
         <v>272</v>
       </c>
@@ -31755,7 +32082,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="273" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="6">
         <v>273</v>
       </c>
@@ -31838,7 +32165,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="274" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="6">
         <v>274</v>
       </c>
@@ -31921,7 +32248,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="275" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="6">
         <v>275</v>
       </c>
@@ -32004,7 +32331,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="276" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="6">
         <v>276</v>
       </c>
@@ -32087,7 +32414,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="277" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="6">
         <v>277</v>
       </c>
@@ -32170,7 +32497,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="278" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="6">
         <v>278</v>
       </c>
@@ -32253,7 +32580,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="279" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="6">
         <v>279</v>
       </c>
@@ -32336,7 +32663,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="280" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="6">
         <v>280</v>
       </c>
@@ -32419,7 +32746,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="281" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="6">
         <v>281</v>
       </c>
@@ -32502,7 +32829,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="282" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="6">
         <v>282</v>
       </c>
@@ -32585,7 +32912,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="283" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="6">
         <v>283</v>
       </c>
@@ -32668,7 +32995,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="284" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="6">
         <v>284</v>
       </c>
@@ -32751,7 +33078,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="285" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="6">
         <v>285</v>
       </c>
@@ -32834,7 +33161,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="286" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="6">
         <v>286</v>
       </c>
@@ -32917,7 +33244,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="287" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="6">
         <v>287</v>
       </c>
@@ -33000,7 +33327,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="288" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="6">
         <v>288</v>
       </c>
@@ -33083,7 +33410,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="289" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="6">
         <v>289</v>
       </c>
@@ -33166,7 +33493,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="290" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="6">
         <v>290</v>
       </c>
@@ -33249,7 +33576,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="291" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="6">
         <v>291</v>
       </c>
@@ -33332,7 +33659,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="292" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="6">
         <v>292</v>
       </c>
@@ -33415,7 +33742,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="293" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="6">
         <v>293</v>
       </c>
@@ -33498,7 +33825,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="294" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="6">
         <v>294</v>
       </c>
@@ -33581,7 +33908,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="295" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="6">
         <v>295</v>
       </c>
@@ -33664,7 +33991,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="296" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="6">
         <v>296</v>
       </c>
@@ -33747,7 +34074,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="297" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="6">
         <v>297</v>
       </c>
@@ -33830,7 +34157,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="298" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="6">
         <v>298</v>
       </c>
@@ -33913,7 +34240,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="299" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="6">
         <v>299</v>
       </c>
@@ -33996,7 +34323,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="300" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="6">
         <v>300</v>
       </c>
@@ -34079,7 +34406,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="301" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="6">
         <v>301</v>
       </c>
@@ -34162,7 +34489,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="302" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="6">
         <v>302</v>
       </c>
@@ -34245,7 +34572,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="303" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="6">
         <v>303</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6B90B7-8645-4EF7-93EF-1DD655283CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88926F46-D3CC-41F0-BDEA-F1A8E257BCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="601" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="601" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="10" r:id="rId1"/>
@@ -3258,19 +3258,19 @@
     <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
   </si>
   <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(SpatialElement)).Cast&lt;SpatialElement&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(Level)).Cast&lt;Level&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ EleBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilyInstance)).Cast&lt;FamilyInstance&gt;().FirstOrDefault( e =&gt; e.Symbol.Name == 'InsBuscada') ]"</t>
-  </si>
-  <si>
-    <t>"[ TipBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilySymbol )).Cast&lt;FamilySymbol&gt;( ).FirstOrDefault( e =&gt; e.Name        == 'TipBuscado') ]"</t>
-  </si>
-  <si>
-    <t>"[ MtlBuscado : FilteredElementCollector(doc).OfClass(typeof(Material)).Cast&lt;Material&gt;( ).FirstOrDefault( e =&gt; e.Name  == 'MtlBuscado') ]"</t>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
   </si>
 </sst>
 </file>
@@ -4451,14 +4451,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B80B61-09F0-4F35-A733-85777283AFC6}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="56.69921875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="56.6640625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.19921875" customWidth="1"/>
-    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.296875" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" customWidth="1"/>
+    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>320</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>321</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
         <v>9</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>322</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>324</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>325</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>326</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>327</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>328</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>329</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -4647,19 +4647,19 @@
         <v>704</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B18" s="38">
         <f ca="1">NOW()</f>
-        <v>46257.756680208331</v>
+        <v>46258.544801388889</v>
       </c>
       <c r="C18" s="37" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>713</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="34" t="s">
         <v>708</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="34" t="s">
         <v>714</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="34" t="s">
         <v>319</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="34" t="s">
         <v>331</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>336</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>338</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="34" t="s">
         <v>700</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
         <v>988</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="34" t="s">
         <v>990</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="34" t="s">
         <v>992</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="34" t="s">
         <v>994</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="34" t="s">
         <v>996</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="34" t="s">
         <v>998</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="34" t="s">
         <v>1000</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="34" t="s">
         <v>1002</v>
       </c>
@@ -4837,7 +4837,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="34" t="s">
         <v>1004</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="34" t="s">
         <v>1006</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="34" t="s">
         <v>1008</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>1010</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="34" t="s">
         <v>1012</v>
       </c>
@@ -4908,37 +4908,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFFE5C0-D3D8-4876-B71B-E260AD929073}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC48"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.796875" style="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.296875" style="66" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.19921875" style="66" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="66" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="66" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="66" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.19921875" style="66" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="66" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" style="66" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="66" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" style="39" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.19921875" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="39" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.19921875" style="39" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="62.296875" style="39" customWidth="1"/>
+    <col min="16" max="16" width="78.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="62.33203125" style="39" customWidth="1"/>
     <col min="18" max="18" width="54.5" style="39" customWidth="1"/>
     <col min="19" max="19" width="5" style="66" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.19921875" style="39" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" style="39" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.19921875" style="39" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" style="39" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.796875" style="66" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="66" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="38.5" style="39" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9" style="39" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="44.796875" style="39" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" style="39" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.69921875" style="39" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.796875" style="39"/>
+    <col min="29" max="29" width="6.6640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.83203125" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>649</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48">
         <v>2</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="48">
         <v>3</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="48">
         <v>4</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="48">
         <v>5</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="48">
         <v>6</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="7" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="48">
         <v>7</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="8" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="48">
         <v>8</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="9" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="48">
         <v>9</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="10" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="48">
         <v>10</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="11" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="48">
         <v>11</v>
       </c>
@@ -5997,7 +5997,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="12" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="48">
         <v>12</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="13" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="48">
         <v>13</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="14" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="48">
         <v>14</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="48">
         <v>15</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="48">
         <v>16</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="48">
         <v>17</v>
       </c>
@@ -6579,7 +6579,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="48">
         <v>18</v>
       </c>
@@ -6676,7 +6676,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="48">
         <v>19</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="48">
         <v>20</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="48">
         <v>21</v>
       </c>
@@ -6967,7 +6967,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="48">
         <v>22</v>
       </c>
@@ -7064,7 +7064,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="48">
         <v>23</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="48">
         <v>24</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="48">
         <v>25</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="48">
         <v>26</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="48">
         <v>27</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="48">
         <v>28</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="48">
         <v>29</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="48">
         <v>30</v>
       </c>
@@ -7840,7 +7840,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="48">
         <v>31</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="48">
         <v>32</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48">
         <v>33</v>
       </c>
@@ -8131,7 +8131,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="48">
         <v>34</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="48">
         <v>35</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="48">
         <v>36</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="48">
         <v>37</v>
       </c>
@@ -8519,7 +8519,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="48">
         <v>38</v>
       </c>
@@ -8616,7 +8616,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="48">
         <v>39</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="48">
         <v>40</v>
       </c>
@@ -8810,7 +8810,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="48">
         <v>41</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="48">
         <v>42</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="48">
         <v>43</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="48">
         <v>44</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="48">
         <v>45</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="48">
         <v>46</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="48">
         <v>47</v>
       </c>
@@ -9489,7 +9489,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="48" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="48">
         <v>48</v>
       </c>
@@ -9632,13 +9632,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B5591C-1220-489B-957E-6F42AD7CFACA}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>650</v>
       </c>
@@ -9703,7 +9703,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -9785,13 +9785,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26462613-E7D7-4ABD-BD2B-4B8A0B104ED0}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="17.19921875" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="26">
         <v>1</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="17">
         <v>2</v>
       </c>
@@ -9827,45 +9827,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4160801D-A855-4DB1-BB60-92D2B856BA2E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG308"/>
-  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.09765625" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" style="47" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" style="47" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.69921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.59765625" style="47" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.09765625" style="47" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.19921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.09765625" style="47" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.8984375" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.296875" style="47" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="81.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="79.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.83203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.33203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="56.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.09765625" style="47" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.69921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.19921875" style="1"/>
+    <col min="34" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>333</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -10067,7 +10067,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>4</v>
       </c>
@@ -10269,7 +10269,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>5</v>
       </c>
@@ -10370,7 +10370,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>6</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>7</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>8</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>9</v>
       </c>
@@ -10774,7 +10774,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>10</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>11</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>12</v>
       </c>
@@ -11077,7 +11077,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>13</v>
       </c>
@@ -11178,7 +11178,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>14</v>
       </c>
@@ -11279,7 +11279,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>15</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>16</v>
       </c>
@@ -11481,7 +11481,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>17</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>18</v>
       </c>
@@ -11683,7 +11683,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>19</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>20</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>21</v>
       </c>
@@ -11986,7 +11986,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>22</v>
       </c>
@@ -12087,7 +12087,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>23</v>
       </c>
@@ -12188,7 +12188,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>24</v>
       </c>
@@ -12289,7 +12289,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>25</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>26</v>
       </c>
@@ -12491,7 +12491,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>27</v>
       </c>
@@ -12592,7 +12592,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>28</v>
       </c>
@@ -12693,7 +12693,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>29</v>
       </c>
@@ -12794,7 +12794,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>30</v>
       </c>
@@ -12895,7 +12895,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>31</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>32</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>33</v>
       </c>
@@ -13198,7 +13198,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>34</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>35</v>
       </c>
@@ -13400,7 +13400,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>36</v>
       </c>
@@ -13501,7 +13501,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>37</v>
       </c>
@@ -13602,7 +13602,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>38</v>
       </c>
@@ -13703,7 +13703,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>39</v>
       </c>
@@ -13804,7 +13804,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>40</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>41</v>
       </c>
@@ -14006,7 +14006,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>42</v>
       </c>
@@ -14107,7 +14107,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>43</v>
       </c>
@@ -14208,7 +14208,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>44</v>
       </c>
@@ -14309,7 +14309,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>45</v>
       </c>
@@ -14410,7 +14410,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>46</v>
       </c>
@@ -14511,7 +14511,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>47</v>
       </c>
@@ -14612,7 +14612,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>48</v>
       </c>
@@ -14713,7 +14713,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>49</v>
       </c>
@@ -14814,7 +14814,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>50</v>
       </c>
@@ -14915,7 +14915,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>51</v>
       </c>
@@ -15016,7 +15016,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>52</v>
       </c>
@@ -15117,7 +15117,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>53</v>
       </c>
@@ -15218,7 +15218,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>54</v>
       </c>
@@ -15319,7 +15319,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>55</v>
       </c>
@@ -15420,7 +15420,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>56</v>
       </c>
@@ -15521,7 +15521,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>57</v>
       </c>
@@ -15622,7 +15622,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>58</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>59</v>
       </c>
@@ -15824,7 +15824,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>60</v>
       </c>
@@ -15925,7 +15925,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>61</v>
       </c>
@@ -16026,7 +16026,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>62</v>
       </c>
@@ -16127,7 +16127,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>63</v>
       </c>
@@ -16228,7 +16228,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>64</v>
       </c>
@@ -16329,7 +16329,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>65</v>
       </c>
@@ -16430,7 +16430,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>66</v>
       </c>
@@ -16531,7 +16531,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>67</v>
       </c>
@@ -16632,7 +16632,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>68</v>
       </c>
@@ -16733,7 +16733,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>69</v>
       </c>
@@ -16834,7 +16834,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>70</v>
       </c>
@@ -16935,7 +16935,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>71</v>
       </c>
@@ -17036,7 +17036,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>72</v>
       </c>
@@ -17137,7 +17137,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>73</v>
       </c>
@@ -17238,7 +17238,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>74</v>
       </c>
@@ -17339,7 +17339,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>75</v>
       </c>
@@ -17440,7 +17440,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>76</v>
       </c>
@@ -17541,7 +17541,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>77</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>78</v>
       </c>
@@ -17743,7 +17743,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>79</v>
       </c>
@@ -17844,7 +17844,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>80</v>
       </c>
@@ -17945,7 +17945,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>81</v>
       </c>
@@ -18046,7 +18046,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>82</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>83</v>
       </c>
@@ -18248,7 +18248,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>84</v>
       </c>
@@ -18349,7 +18349,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>85</v>
       </c>
@@ -18450,7 +18450,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>86</v>
       </c>
@@ -18551,7 +18551,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>87</v>
       </c>
@@ -18652,7 +18652,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>88</v>
       </c>
@@ -18753,7 +18753,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -18854,7 +18854,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>90</v>
       </c>
@@ -18955,7 +18955,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>91</v>
       </c>
@@ -19056,7 +19056,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>92</v>
       </c>
@@ -19157,7 +19157,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>93</v>
       </c>
@@ -19258,7 +19258,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>94</v>
       </c>
@@ -19359,7 +19359,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>95</v>
       </c>
@@ -19460,7 +19460,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>96</v>
       </c>
@@ -19561,7 +19561,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>97</v>
       </c>
@@ -19662,7 +19662,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>98</v>
       </c>
@@ -19763,7 +19763,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -19864,7 +19864,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>100</v>
       </c>
@@ -19965,7 +19965,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>101</v>
       </c>
@@ -20066,7 +20066,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>102</v>
       </c>
@@ -20167,7 +20167,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>103</v>
       </c>
@@ -20268,7 +20268,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>104</v>
       </c>
@@ -20369,7 +20369,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>105</v>
       </c>
@@ -20470,7 +20470,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>106</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -20672,7 +20672,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -20773,7 +20773,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>109</v>
       </c>
@@ -20874,7 +20874,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>110</v>
       </c>
@@ -20975,7 +20975,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>111</v>
       </c>
@@ -21076,7 +21076,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>112</v>
       </c>
@@ -21177,7 +21177,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>113</v>
       </c>
@@ -21278,7 +21278,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>114</v>
       </c>
@@ -21379,7 +21379,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>115</v>
       </c>
@@ -21480,7 +21480,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>116</v>
       </c>
@@ -21581,7 +21581,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>117</v>
       </c>
@@ -21682,7 +21682,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>118</v>
       </c>
@@ -21783,7 +21783,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>119</v>
       </c>
@@ -21884,7 +21884,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>120</v>
       </c>
@@ -21985,7 +21985,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>121</v>
       </c>
@@ -22086,7 +22086,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>122</v>
       </c>
@@ -22187,7 +22187,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>123</v>
       </c>
@@ -22288,7 +22288,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>124</v>
       </c>
@@ -22389,7 +22389,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>125</v>
       </c>
@@ -22490,7 +22490,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>126</v>
       </c>
@@ -22591,7 +22591,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>127</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>128</v>
       </c>
@@ -22793,7 +22793,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>129</v>
       </c>
@@ -22894,7 +22894,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="6">
         <v>130</v>
       </c>
@@ -22995,7 +22995,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>131</v>
       </c>
@@ -23096,7 +23096,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="6">
         <v>132</v>
       </c>
@@ -23197,7 +23197,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>133</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="6">
         <v>134</v>
       </c>
@@ -23399,7 +23399,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>135</v>
       </c>
@@ -23500,7 +23500,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="6">
         <v>136</v>
       </c>
@@ -23601,7 +23601,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>137</v>
       </c>
@@ -23702,7 +23702,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="6">
         <v>138</v>
       </c>
@@ -23803,7 +23803,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>139</v>
       </c>
@@ -23904,7 +23904,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="6">
         <v>140</v>
       </c>
@@ -24005,7 +24005,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>141</v>
       </c>
@@ -24106,7 +24106,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="6">
         <v>142</v>
       </c>
@@ -24207,7 +24207,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>143</v>
       </c>
@@ -24308,7 +24308,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="6">
         <v>144</v>
       </c>
@@ -24409,7 +24409,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>145</v>
       </c>
@@ -24510,7 +24510,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="6">
         <v>146</v>
       </c>
@@ -24611,7 +24611,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>147</v>
       </c>
@@ -24712,7 +24712,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="6">
         <v>148</v>
       </c>
@@ -24813,7 +24813,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>149</v>
       </c>
@@ -24914,7 +24914,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="6">
         <v>150</v>
       </c>
@@ -25015,7 +25015,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>151</v>
       </c>
@@ -25116,7 +25116,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="6">
         <v>152</v>
       </c>
@@ -25217,7 +25217,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>153</v>
       </c>
@@ -25318,7 +25318,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="6">
         <v>154</v>
       </c>
@@ -25419,7 +25419,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>155</v>
       </c>
@@ -25520,7 +25520,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="6">
         <v>156</v>
       </c>
@@ -25621,7 +25621,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>157</v>
       </c>
@@ -25722,7 +25722,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="6">
         <v>158</v>
       </c>
@@ -25823,7 +25823,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>159</v>
       </c>
@@ -25924,7 +25924,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="6">
         <v>160</v>
       </c>
@@ -26025,7 +26025,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>161</v>
       </c>
@@ -26126,7 +26126,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="6">
         <v>162</v>
       </c>
@@ -26227,7 +26227,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>163</v>
       </c>
@@ -26328,7 +26328,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="6">
         <v>164</v>
       </c>
@@ -26429,7 +26429,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>165</v>
       </c>
@@ -26530,7 +26530,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="6">
         <v>166</v>
       </c>
@@ -26631,7 +26631,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>167</v>
       </c>
@@ -26732,7 +26732,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="6">
         <v>168</v>
       </c>
@@ -26833,7 +26833,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>169</v>
       </c>
@@ -26934,7 +26934,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="6">
         <v>170</v>
       </c>
@@ -27035,7 +27035,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>171</v>
       </c>
@@ -27136,7 +27136,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="6">
         <v>172</v>
       </c>
@@ -27237,7 +27237,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>173</v>
       </c>
@@ -27338,7 +27338,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="6">
         <v>174</v>
       </c>
@@ -27439,7 +27439,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>175</v>
       </c>
@@ -27540,7 +27540,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="6">
         <v>176</v>
       </c>
@@ -27641,7 +27641,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>177</v>
       </c>
@@ -27742,7 +27742,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="6">
         <v>178</v>
       </c>
@@ -27843,7 +27843,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="179" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>179</v>
       </c>
@@ -27944,7 +27944,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="180" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="6">
         <v>180</v>
       </c>
@@ -28045,7 +28045,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="181" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -28146,7 +28146,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="182" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="6">
         <v>182</v>
       </c>
@@ -28247,7 +28247,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="183" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>183</v>
       </c>
@@ -28348,7 +28348,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="6">
         <v>184</v>
       </c>
@@ -28449,7 +28449,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="185" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>185</v>
       </c>
@@ -28550,7 +28550,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="6">
         <v>186</v>
       </c>
@@ -28651,7 +28651,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>187</v>
       </c>
@@ -28752,7 +28752,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="188" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="6">
         <v>188</v>
       </c>
@@ -28853,7 +28853,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="189" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>189</v>
       </c>
@@ -28954,7 +28954,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="190" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="6">
         <v>190</v>
       </c>
@@ -29055,7 +29055,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="191" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>191</v>
       </c>
@@ -29156,7 +29156,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="192" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="6">
         <v>192</v>
       </c>
@@ -29257,7 +29257,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="193" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>193</v>
       </c>
@@ -29358,7 +29358,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="194" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="6">
         <v>194</v>
       </c>
@@ -29459,7 +29459,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="195" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>195</v>
       </c>
@@ -29560,7 +29560,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="196" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="6">
         <v>196</v>
       </c>
@@ -29661,7 +29661,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="197" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>197</v>
       </c>
@@ -29762,7 +29762,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="198" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="6">
         <v>198</v>
       </c>
@@ -29863,7 +29863,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="199" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>199</v>
       </c>
@@ -29964,7 +29964,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="200" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="6">
         <v>200</v>
       </c>
@@ -30065,7 +30065,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="201" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>201</v>
       </c>
@@ -30166,7 +30166,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="202" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="6">
         <v>202</v>
       </c>
@@ -30267,7 +30267,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="203" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>203</v>
       </c>
@@ -30368,7 +30368,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="204" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="6">
         <v>204</v>
       </c>
@@ -30469,7 +30469,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="205" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>205</v>
       </c>
@@ -30570,7 +30570,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="206" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="6">
         <v>206</v>
       </c>
@@ -30671,7 +30671,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="207" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>207</v>
       </c>
@@ -30772,7 +30772,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="208" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="6">
         <v>208</v>
       </c>
@@ -30873,7 +30873,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="209" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>209</v>
       </c>
@@ -30974,7 +30974,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="210" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="6">
         <v>210</v>
       </c>
@@ -31075,7 +31075,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="211" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>211</v>
       </c>
@@ -31176,7 +31176,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="212" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="6">
         <v>212</v>
       </c>
@@ -31277,7 +31277,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="213" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>213</v>
       </c>
@@ -31378,7 +31378,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="214" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="6">
         <v>214</v>
       </c>
@@ -31479,7 +31479,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="215" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>215</v>
       </c>
@@ -31580,7 +31580,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="216" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="6">
         <v>216</v>
       </c>
@@ -31681,7 +31681,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="217" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>217</v>
       </c>
@@ -31782,7 +31782,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="218" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -31883,7 +31883,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="219" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>219</v>
       </c>
@@ -31984,7 +31984,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="220" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="6">
         <v>220</v>
       </c>
@@ -32085,7 +32085,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="221" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>221</v>
       </c>
@@ -32186,7 +32186,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="222" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="6">
         <v>222</v>
       </c>
@@ -32287,7 +32287,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="223" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>223</v>
       </c>
@@ -32388,7 +32388,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="224" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="6">
         <v>224</v>
       </c>
@@ -32489,7 +32489,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="225" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>225</v>
       </c>
@@ -32590,7 +32590,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="226" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="6">
         <v>226</v>
       </c>
@@ -32691,7 +32691,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="227" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>227</v>
       </c>
@@ -32792,7 +32792,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="228" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="6">
         <v>228</v>
       </c>
@@ -32893,7 +32893,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="229" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>229</v>
       </c>
@@ -32994,7 +32994,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="230" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="6">
         <v>230</v>
       </c>
@@ -33095,7 +33095,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="231" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>231</v>
       </c>
@@ -33196,7 +33196,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="232" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="6">
         <v>232</v>
       </c>
@@ -33297,7 +33297,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="233" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>233</v>
       </c>
@@ -33398,7 +33398,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="234" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="6">
         <v>234</v>
       </c>
@@ -33499,7 +33499,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="235" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>235</v>
       </c>
@@ -33600,7 +33600,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="236" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="6">
         <v>236</v>
       </c>
@@ -33701,7 +33701,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="237" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>237</v>
       </c>
@@ -33802,7 +33802,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="238" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="6">
         <v>238</v>
       </c>
@@ -33903,7 +33903,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="239" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>239</v>
       </c>
@@ -34004,7 +34004,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="240" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="6">
         <v>240</v>
       </c>
@@ -34105,7 +34105,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="241" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>241</v>
       </c>
@@ -34206,7 +34206,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="242" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="6">
         <v>242</v>
       </c>
@@ -34307,7 +34307,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="243" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>243</v>
       </c>
@@ -34408,7 +34408,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="244" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="6">
         <v>244</v>
       </c>
@@ -34509,7 +34509,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="245" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>245</v>
       </c>
@@ -34610,7 +34610,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="246" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="6">
         <v>246</v>
       </c>
@@ -34711,7 +34711,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="247" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>247</v>
       </c>
@@ -34812,7 +34812,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="6">
         <v>248</v>
       </c>
@@ -34913,7 +34913,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="249" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>249</v>
       </c>
@@ -35014,7 +35014,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="250" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="6">
         <v>250</v>
       </c>
@@ -35115,7 +35115,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="251" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -35216,7 +35216,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="252" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="6">
         <v>252</v>
       </c>
@@ -35317,7 +35317,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>253</v>
       </c>
@@ -35418,7 +35418,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="254" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="6">
         <v>254</v>
       </c>
@@ -35519,7 +35519,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="255" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>255</v>
       </c>
@@ -35620,7 +35620,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="256" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="6">
         <v>256</v>
       </c>
@@ -35721,7 +35721,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="257" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="6">
         <v>257</v>
       </c>
@@ -35822,7 +35822,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="258" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="6">
         <v>258</v>
       </c>
@@ -35923,7 +35923,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="259" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="6">
         <v>259</v>
       </c>
@@ -36024,7 +36024,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="260" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="6">
         <v>260</v>
       </c>
@@ -36125,7 +36125,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="261" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="6">
         <v>261</v>
       </c>
@@ -36226,7 +36226,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="262" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="6">
         <v>262</v>
       </c>
@@ -36327,7 +36327,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="263" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="6">
         <v>263</v>
       </c>
@@ -36428,7 +36428,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="264" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="6">
         <v>264</v>
       </c>
@@ -36529,7 +36529,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="265" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="6">
         <v>265</v>
       </c>
@@ -36630,7 +36630,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="266" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="6">
         <v>266</v>
       </c>
@@ -36731,7 +36731,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="267" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="6">
         <v>267</v>
       </c>
@@ -36832,7 +36832,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="268" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="6">
         <v>268</v>
       </c>
@@ -36933,7 +36933,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="269" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="6">
         <v>269</v>
       </c>
@@ -37034,7 +37034,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="270" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="6">
         <v>270</v>
       </c>
@@ -37135,7 +37135,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="271" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -37236,7 +37236,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="272" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="6">
         <v>272</v>
       </c>
@@ -37337,7 +37337,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="273" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="6">
         <v>273</v>
       </c>
@@ -37438,7 +37438,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="274" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="6">
         <v>274</v>
       </c>
@@ -37539,7 +37539,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="275" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="6">
         <v>275</v>
       </c>
@@ -37640,7 +37640,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="276" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="6">
         <v>276</v>
       </c>
@@ -37741,7 +37741,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="277" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="6">
         <v>277</v>
       </c>
@@ -37842,7 +37842,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="278" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="6">
         <v>278</v>
       </c>
@@ -37943,7 +37943,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="279" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="6">
         <v>279</v>
       </c>
@@ -38044,7 +38044,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="280" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="6">
         <v>280</v>
       </c>
@@ -38145,7 +38145,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="281" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="6">
         <v>281</v>
       </c>
@@ -38246,7 +38246,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="282" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="6">
         <v>282</v>
       </c>
@@ -38347,7 +38347,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="283" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="6">
         <v>283</v>
       </c>
@@ -38448,7 +38448,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="284" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="6">
         <v>284</v>
       </c>
@@ -38549,7 +38549,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="285" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="6">
         <v>285</v>
       </c>
@@ -38650,7 +38650,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="286" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="6">
         <v>286</v>
       </c>
@@ -38751,7 +38751,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="287" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="6">
         <v>287</v>
       </c>
@@ -38852,7 +38852,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="288" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="6">
         <v>288</v>
       </c>
@@ -38953,7 +38953,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="289" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="6">
         <v>289</v>
       </c>
@@ -39054,7 +39054,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="290" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="6">
         <v>290</v>
       </c>
@@ -39155,7 +39155,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="291" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="6">
         <v>291</v>
       </c>
@@ -39256,7 +39256,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="292" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="6">
         <v>292</v>
       </c>
@@ -39357,7 +39357,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="293" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="6">
         <v>293</v>
       </c>
@@ -39458,7 +39458,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="294" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="6">
         <v>294</v>
       </c>
@@ -39559,7 +39559,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="295" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="6">
         <v>295</v>
       </c>
@@ -39660,7 +39660,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="296" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="6">
         <v>296</v>
       </c>
@@ -39761,7 +39761,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="297" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="6">
         <v>297</v>
       </c>
@@ -39862,7 +39862,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="298" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="6">
         <v>298</v>
       </c>
@@ -39963,7 +39963,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="299" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="6">
         <v>299</v>
       </c>
@@ -40064,7 +40064,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="300" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="6">
         <v>300</v>
       </c>
@@ -40165,7 +40165,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="301" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="6">
         <v>301</v>
       </c>
@@ -40266,7 +40266,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="302" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="6">
         <v>302</v>
       </c>
@@ -40367,7 +40367,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="303" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="6">
         <v>303</v>
       </c>
@@ -40468,7 +40468,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="6">
         <v>304</v>
       </c>
@@ -40570,7 +40570,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="305" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="6">
         <v>305</v>
       </c>
@@ -40672,7 +40672,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="306" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="6">
         <v>306</v>
       </c>
@@ -40774,7 +40774,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="307" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="6">
         <v>307</v>
       </c>
@@ -40876,7 +40876,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="308" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="6">
         <v>308</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88926F46-D3CC-41F0-BDEA-F1A8E257BCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D44FAFE-1176-4F9D-A3F6-B76E769C13A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="601" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="10" r:id="rId1"/>
@@ -4451,14 +4451,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B80B61-09F0-4F35-A733-85777283AFC6}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="56.6640625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="56.69921875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" customWidth="1"/>
-    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="1" max="1" width="11.19921875" customWidth="1"/>
+    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>320</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>321</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
         <v>9</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>322</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>324</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>325</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>326</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>327</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>328</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>329</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -4647,19 +4647,19 @@
         <v>704</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B18" s="38">
         <f ca="1">NOW()</f>
-        <v>46258.544801388889</v>
+        <v>46264.561929513889</v>
       </c>
       <c r="C18" s="37" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>713</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34" t="s">
         <v>708</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>714</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34" t="s">
         <v>319</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>331</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>336</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>338</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34" t="s">
         <v>700</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34" t="s">
         <v>988</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34" t="s">
         <v>990</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34" t="s">
         <v>992</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="34" t="s">
         <v>994</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="34" t="s">
         <v>996</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="34" t="s">
         <v>998</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="34" t="s">
         <v>1000</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="34" t="s">
         <v>1002</v>
       </c>
@@ -4837,7 +4837,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="34" t="s">
         <v>1004</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="34" t="s">
         <v>1006</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="34" t="s">
         <v>1008</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>1010</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="34" t="s">
         <v>1012</v>
       </c>
@@ -4908,37 +4908,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFFE5C0-D3D8-4876-B71B-E260AD929073}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC48"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="66" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="66" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.296875" style="66" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.19921875" style="66" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="66" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="66" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" style="66" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" style="66" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="66" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.296875" style="39" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.19921875" style="39" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="39" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="62.33203125" style="39" customWidth="1"/>
+    <col min="16" max="16" width="78.19921875" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="62.296875" style="39" customWidth="1"/>
     <col min="18" max="18" width="54.5" style="39" customWidth="1"/>
     <col min="19" max="19" width="5" style="66" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.19921875" style="39" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.19921875" style="39" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" style="39" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.83203125" style="66" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.796875" style="66" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="38.5" style="39" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9" style="39" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="44.83203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.796875" style="39" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.6640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.83203125" style="39"/>
+    <col min="29" max="29" width="6.69921875" style="39" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.796875" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>649</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48">
         <v>2</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="48">
         <v>3</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="48">
         <v>4</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="48">
         <v>5</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="48">
         <v>6</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="7" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="48">
         <v>7</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="8" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="48">
         <v>8</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="9" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="48">
         <v>9</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="10" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48">
         <v>10</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="11" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="48">
         <v>11</v>
       </c>
@@ -5997,7 +5997,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="12" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48">
         <v>12</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="13" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="48">
         <v>13</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="14" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="48">
         <v>14</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="48">
         <v>15</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="48">
         <v>16</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48">
         <v>17</v>
       </c>
@@ -6579,7 +6579,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="48">
         <v>18</v>
       </c>
@@ -6676,7 +6676,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48">
         <v>19</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="48">
         <v>20</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48">
         <v>21</v>
       </c>
@@ -6967,7 +6967,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48">
         <v>22</v>
       </c>
@@ -7064,7 +7064,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="48">
         <v>23</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="48">
         <v>24</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="48">
         <v>25</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="48">
         <v>26</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="48">
         <v>27</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="48">
         <v>28</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="48">
         <v>29</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="48">
         <v>30</v>
       </c>
@@ -7840,7 +7840,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="48">
         <v>31</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="48">
         <v>32</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="48">
         <v>33</v>
       </c>
@@ -8131,7 +8131,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="48">
         <v>34</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="48">
         <v>35</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="48">
         <v>36</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="48">
         <v>37</v>
       </c>
@@ -8519,7 +8519,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="48">
         <v>38</v>
       </c>
@@ -8616,7 +8616,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="48">
         <v>39</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="48">
         <v>40</v>
       </c>
@@ -8810,7 +8810,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="48">
         <v>41</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="48">
         <v>42</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="48">
         <v>43</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="48">
         <v>44</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="48">
         <v>45</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="48">
         <v>46</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="48">
         <v>47</v>
       </c>
@@ -9489,7 +9489,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="48" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="48">
         <v>48</v>
       </c>
@@ -9500,10 +9500,10 @@
         <v>1032</v>
       </c>
       <c r="D48" s="29" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E48" s="29" t="s">
         <v>1033</v>
-      </c>
-      <c r="E48" s="29" t="s">
-        <v>1034</v>
       </c>
       <c r="F48" s="29" t="s">
         <v>1035</v>
@@ -9529,11 +9529,11 @@
       </c>
       <c r="M48" s="50" t="str">
         <f t="shared" si="12"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N48" s="50" t="str">
         <f t="shared" si="12"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O48" s="50" t="str">
         <f t="shared" si="12"/>
@@ -9557,11 +9557,11 @@
       </c>
       <c r="U48" s="33" t="str">
         <f t="shared" si="13"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V48" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W48" s="33" t="s">
         <v>716</v>
@@ -9632,13 +9632,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B5591C-1220-489B-957E-6F42AD7CFACA}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>650</v>
       </c>
@@ -9703,7 +9703,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -9785,13 +9785,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26462613-E7D7-4ABD-BD2B-4B8A0B104ED0}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="26">
         <v>1</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="17">
         <v>2</v>
       </c>
@@ -9827,45 +9827,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4160801D-A855-4DB1-BB60-92D2B856BA2E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG308"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.19921875" style="47" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" style="47" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.1640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.1640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.83203125" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.33203125" style="47" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="56.33203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.69921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.69921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.19921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.19921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.19921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.796875" style="47" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.296875" style="47" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="56.296875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="7.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.1640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.6640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.19921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.69921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.1640625" style="1"/>
+    <col min="34" max="16384" width="9.19921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>333</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -10067,7 +10067,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>4</v>
       </c>
@@ -10269,7 +10269,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>5</v>
       </c>
@@ -10370,7 +10370,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>6</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>7</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>8</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>9</v>
       </c>
@@ -10774,7 +10774,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>10</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>11</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>12</v>
       </c>
@@ -11077,7 +11077,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>13</v>
       </c>
@@ -11178,7 +11178,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>14</v>
       </c>
@@ -11279,7 +11279,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>15</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>16</v>
       </c>
@@ -11481,7 +11481,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>17</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>18</v>
       </c>
@@ -11683,7 +11683,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>19</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>20</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>21</v>
       </c>
@@ -11986,7 +11986,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>22</v>
       </c>
@@ -12087,7 +12087,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>23</v>
       </c>
@@ -12188,7 +12188,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>24</v>
       </c>
@@ -12289,7 +12289,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>25</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>26</v>
       </c>
@@ -12491,7 +12491,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>27</v>
       </c>
@@ -12592,7 +12592,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>28</v>
       </c>
@@ -12693,7 +12693,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>29</v>
       </c>
@@ -12794,7 +12794,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>30</v>
       </c>
@@ -12895,7 +12895,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>31</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>32</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>33</v>
       </c>
@@ -13198,7 +13198,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>34</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>35</v>
       </c>
@@ -13400,7 +13400,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>36</v>
       </c>
@@ -13501,7 +13501,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>37</v>
       </c>
@@ -13602,7 +13602,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>38</v>
       </c>
@@ -13703,7 +13703,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>39</v>
       </c>
@@ -13804,7 +13804,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>40</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>41</v>
       </c>
@@ -14006,7 +14006,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>42</v>
       </c>
@@ -14107,7 +14107,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43</v>
       </c>
@@ -14208,7 +14208,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>44</v>
       </c>
@@ -14309,7 +14309,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>45</v>
       </c>
@@ -14410,7 +14410,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>46</v>
       </c>
@@ -14511,7 +14511,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>47</v>
       </c>
@@ -14612,7 +14612,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>48</v>
       </c>
@@ -14713,7 +14713,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>49</v>
       </c>
@@ -14814,7 +14814,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>50</v>
       </c>
@@ -14915,7 +14915,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>51</v>
       </c>
@@ -15016,7 +15016,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>52</v>
       </c>
@@ -15117,7 +15117,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>53</v>
       </c>
@@ -15218,7 +15218,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>54</v>
       </c>
@@ -15319,7 +15319,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>55</v>
       </c>
@@ -15420,7 +15420,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>56</v>
       </c>
@@ -15521,7 +15521,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>57</v>
       </c>
@@ -15622,7 +15622,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>58</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>59</v>
       </c>
@@ -15824,7 +15824,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>60</v>
       </c>
@@ -15925,7 +15925,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>61</v>
       </c>
@@ -16026,7 +16026,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>62</v>
       </c>
@@ -16127,7 +16127,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>63</v>
       </c>
@@ -16228,7 +16228,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>64</v>
       </c>
@@ -16329,7 +16329,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>65</v>
       </c>
@@ -16430,7 +16430,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>66</v>
       </c>
@@ -16531,7 +16531,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>67</v>
       </c>
@@ -16632,7 +16632,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>68</v>
       </c>
@@ -16733,7 +16733,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>69</v>
       </c>
@@ -16834,7 +16834,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>70</v>
       </c>
@@ -16935,7 +16935,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>71</v>
       </c>
@@ -17036,7 +17036,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>72</v>
       </c>
@@ -17137,7 +17137,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>73</v>
       </c>
@@ -17238,7 +17238,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>74</v>
       </c>
@@ -17339,7 +17339,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>75</v>
       </c>
@@ -17440,7 +17440,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>76</v>
       </c>
@@ -17541,7 +17541,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>77</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>78</v>
       </c>
@@ -17743,7 +17743,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>79</v>
       </c>
@@ -17844,7 +17844,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>80</v>
       </c>
@@ -17945,7 +17945,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>81</v>
       </c>
@@ -18046,7 +18046,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>82</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>83</v>
       </c>
@@ -18248,7 +18248,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>84</v>
       </c>
@@ -18349,7 +18349,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>85</v>
       </c>
@@ -18450,7 +18450,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>86</v>
       </c>
@@ -18551,7 +18551,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>87</v>
       </c>
@@ -18652,7 +18652,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>88</v>
       </c>
@@ -18753,7 +18753,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -18854,7 +18854,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>90</v>
       </c>
@@ -18955,7 +18955,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>91</v>
       </c>
@@ -19056,7 +19056,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>92</v>
       </c>
@@ -19157,7 +19157,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>93</v>
       </c>
@@ -19258,7 +19258,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>94</v>
       </c>
@@ -19359,7 +19359,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>95</v>
       </c>
@@ -19460,7 +19460,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>96</v>
       </c>
@@ -19561,7 +19561,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>97</v>
       </c>
@@ -19662,7 +19662,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>98</v>
       </c>
@@ -19763,7 +19763,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -19864,7 +19864,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>100</v>
       </c>
@@ -19965,7 +19965,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>101</v>
       </c>
@@ -20066,7 +20066,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>102</v>
       </c>
@@ -20167,7 +20167,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>103</v>
       </c>
@@ -20268,7 +20268,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>104</v>
       </c>
@@ -20369,7 +20369,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>105</v>
       </c>
@@ -20470,7 +20470,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>106</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -20672,7 +20672,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -20773,7 +20773,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>109</v>
       </c>
@@ -20874,7 +20874,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>110</v>
       </c>
@@ -20975,7 +20975,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>111</v>
       </c>
@@ -21076,7 +21076,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>112</v>
       </c>
@@ -21177,7 +21177,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>113</v>
       </c>
@@ -21278,7 +21278,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>114</v>
       </c>
@@ -21379,7 +21379,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>115</v>
       </c>
@@ -21480,7 +21480,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>116</v>
       </c>
@@ -21581,7 +21581,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>117</v>
       </c>
@@ -21682,7 +21682,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>118</v>
       </c>
@@ -21783,7 +21783,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>119</v>
       </c>
@@ -21884,7 +21884,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>120</v>
       </c>
@@ -21985,7 +21985,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>121</v>
       </c>
@@ -22086,7 +22086,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>122</v>
       </c>
@@ -22187,7 +22187,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>123</v>
       </c>
@@ -22288,7 +22288,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>124</v>
       </c>
@@ -22389,7 +22389,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>125</v>
       </c>
@@ -22490,7 +22490,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>126</v>
       </c>
@@ -22591,7 +22591,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>127</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>128</v>
       </c>
@@ -22793,7 +22793,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>129</v>
       </c>
@@ -22894,7 +22894,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>130</v>
       </c>
@@ -22995,7 +22995,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>131</v>
       </c>
@@ -23096,7 +23096,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>132</v>
       </c>
@@ -23197,7 +23197,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>133</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>134</v>
       </c>
@@ -23399,7 +23399,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>135</v>
       </c>
@@ -23500,7 +23500,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>136</v>
       </c>
@@ -23601,7 +23601,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>137</v>
       </c>
@@ -23702,7 +23702,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>138</v>
       </c>
@@ -23803,7 +23803,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>139</v>
       </c>
@@ -23904,7 +23904,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>140</v>
       </c>
@@ -24005,7 +24005,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>141</v>
       </c>
@@ -24106,7 +24106,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>142</v>
       </c>
@@ -24207,7 +24207,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>143</v>
       </c>
@@ -24308,7 +24308,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>144</v>
       </c>
@@ -24409,7 +24409,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>145</v>
       </c>
@@ -24510,7 +24510,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>146</v>
       </c>
@@ -24611,7 +24611,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>147</v>
       </c>
@@ -24712,7 +24712,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>148</v>
       </c>
@@ -24813,7 +24813,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>149</v>
       </c>
@@ -24914,7 +24914,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>150</v>
       </c>
@@ -25015,7 +25015,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>151</v>
       </c>
@@ -25116,7 +25116,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>152</v>
       </c>
@@ -25217,7 +25217,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>153</v>
       </c>
@@ -25318,7 +25318,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>154</v>
       </c>
@@ -25419,7 +25419,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>155</v>
       </c>
@@ -25520,7 +25520,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>156</v>
       </c>
@@ -25621,7 +25621,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>157</v>
       </c>
@@ -25722,7 +25722,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>158</v>
       </c>
@@ -25823,7 +25823,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>159</v>
       </c>
@@ -25924,7 +25924,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>160</v>
       </c>
@@ -26025,7 +26025,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>161</v>
       </c>
@@ -26126,7 +26126,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>162</v>
       </c>
@@ -26227,7 +26227,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>163</v>
       </c>
@@ -26328,7 +26328,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>164</v>
       </c>
@@ -26429,7 +26429,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>165</v>
       </c>
@@ -26530,7 +26530,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>166</v>
       </c>
@@ -26631,7 +26631,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>167</v>
       </c>
@@ -26732,7 +26732,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>168</v>
       </c>
@@ -26833,7 +26833,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>169</v>
       </c>
@@ -26934,7 +26934,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>170</v>
       </c>
@@ -27035,7 +27035,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>171</v>
       </c>
@@ -27136,7 +27136,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>172</v>
       </c>
@@ -27237,7 +27237,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>173</v>
       </c>
@@ -27338,7 +27338,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>174</v>
       </c>
@@ -27439,7 +27439,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>175</v>
       </c>
@@ -27540,7 +27540,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>176</v>
       </c>
@@ -27641,7 +27641,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>177</v>
       </c>
@@ -27742,7 +27742,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>178</v>
       </c>
@@ -27843,7 +27843,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="179" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>179</v>
       </c>
@@ -27944,7 +27944,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="180" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>180</v>
       </c>
@@ -28045,7 +28045,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="181" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -28146,7 +28146,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="182" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>182</v>
       </c>
@@ -28247,7 +28247,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="183" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>183</v>
       </c>
@@ -28348,7 +28348,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>184</v>
       </c>
@@ -28449,7 +28449,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="185" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>185</v>
       </c>
@@ -28550,7 +28550,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>186</v>
       </c>
@@ -28651,7 +28651,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>187</v>
       </c>
@@ -28752,7 +28752,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="188" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>188</v>
       </c>
@@ -28853,7 +28853,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="189" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>189</v>
       </c>
@@ -28954,7 +28954,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="190" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>190</v>
       </c>
@@ -29055,7 +29055,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="191" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>191</v>
       </c>
@@ -29156,7 +29156,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="192" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>192</v>
       </c>
@@ -29257,7 +29257,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="193" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>193</v>
       </c>
@@ -29358,7 +29358,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="194" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>194</v>
       </c>
@@ -29459,7 +29459,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="195" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>195</v>
       </c>
@@ -29560,7 +29560,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="196" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>196</v>
       </c>
@@ -29661,7 +29661,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="197" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>197</v>
       </c>
@@ -29762,7 +29762,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="198" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>198</v>
       </c>
@@ -29863,7 +29863,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="199" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>199</v>
       </c>
@@ -29964,7 +29964,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="200" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>200</v>
       </c>
@@ -30065,7 +30065,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="201" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>201</v>
       </c>
@@ -30166,7 +30166,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="202" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>202</v>
       </c>
@@ -30267,7 +30267,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="203" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>203</v>
       </c>
@@ -30368,7 +30368,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="204" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>204</v>
       </c>
@@ -30469,7 +30469,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="205" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>205</v>
       </c>
@@ -30570,7 +30570,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="206" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>206</v>
       </c>
@@ -30671,7 +30671,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="207" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>207</v>
       </c>
@@ -30772,7 +30772,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="208" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>208</v>
       </c>
@@ -30873,7 +30873,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="209" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>209</v>
       </c>
@@ -30974,7 +30974,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="210" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>210</v>
       </c>
@@ -31075,7 +31075,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="211" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>211</v>
       </c>
@@ -31176,7 +31176,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="212" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>212</v>
       </c>
@@ -31277,7 +31277,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="213" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>213</v>
       </c>
@@ -31378,7 +31378,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="214" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>214</v>
       </c>
@@ -31479,7 +31479,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="215" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>215</v>
       </c>
@@ -31580,7 +31580,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="216" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>216</v>
       </c>
@@ -31681,7 +31681,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="217" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>217</v>
       </c>
@@ -31782,7 +31782,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="218" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -31883,7 +31883,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="219" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>219</v>
       </c>
@@ -31984,7 +31984,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="220" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>220</v>
       </c>
@@ -32085,7 +32085,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="221" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>221</v>
       </c>
@@ -32186,7 +32186,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="222" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>222</v>
       </c>
@@ -32287,7 +32287,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="223" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>223</v>
       </c>
@@ -32388,7 +32388,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="224" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>224</v>
       </c>
@@ -32489,7 +32489,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="225" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>225</v>
       </c>
@@ -32590,7 +32590,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="226" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>226</v>
       </c>
@@ -32691,7 +32691,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="227" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>227</v>
       </c>
@@ -32792,7 +32792,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="228" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>228</v>
       </c>
@@ -32893,7 +32893,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="229" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>229</v>
       </c>
@@ -32994,7 +32994,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="230" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>230</v>
       </c>
@@ -33095,7 +33095,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="231" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>231</v>
       </c>
@@ -33196,7 +33196,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="232" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>232</v>
       </c>
@@ -33297,7 +33297,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="233" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>233</v>
       </c>
@@ -33398,7 +33398,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="234" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>234</v>
       </c>
@@ -33499,7 +33499,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="235" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>235</v>
       </c>
@@ -33600,7 +33600,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="236" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>236</v>
       </c>
@@ -33701,7 +33701,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="237" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>237</v>
       </c>
@@ -33802,7 +33802,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="238" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>238</v>
       </c>
@@ -33903,7 +33903,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="239" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>239</v>
       </c>
@@ -34004,7 +34004,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="240" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>240</v>
       </c>
@@ -34105,7 +34105,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="241" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>241</v>
       </c>
@@ -34206,7 +34206,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="242" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>242</v>
       </c>
@@ -34307,7 +34307,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="243" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>243</v>
       </c>
@@ -34408,7 +34408,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="244" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>244</v>
       </c>
@@ -34509,7 +34509,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="245" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>245</v>
       </c>
@@ -34610,7 +34610,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="246" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>246</v>
       </c>
@@ -34711,7 +34711,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="247" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>247</v>
       </c>
@@ -34812,7 +34812,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>248</v>
       </c>
@@ -34913,7 +34913,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="249" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>249</v>
       </c>
@@ -35014,7 +35014,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="250" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>250</v>
       </c>
@@ -35115,7 +35115,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="251" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -35216,7 +35216,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="252" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>252</v>
       </c>
@@ -35317,7 +35317,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6">
         <v>253</v>
       </c>
@@ -35418,7 +35418,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="254" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6">
         <v>254</v>
       </c>
@@ -35519,7 +35519,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="255" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6">
         <v>255</v>
       </c>
@@ -35620,7 +35620,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="256" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6">
         <v>256</v>
       </c>
@@ -35721,7 +35721,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="257" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6">
         <v>257</v>
       </c>
@@ -35822,7 +35822,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="258" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6">
         <v>258</v>
       </c>
@@ -35923,7 +35923,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="259" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
         <v>259</v>
       </c>
@@ -36024,7 +36024,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="260" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6">
         <v>260</v>
       </c>
@@ -36125,7 +36125,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="261" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6">
         <v>261</v>
       </c>
@@ -36226,7 +36226,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="262" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6">
         <v>262</v>
       </c>
@@ -36327,7 +36327,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="263" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>263</v>
       </c>
@@ -36428,7 +36428,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="264" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6">
         <v>264</v>
       </c>
@@ -36529,7 +36529,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="265" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6">
         <v>265</v>
       </c>
@@ -36630,7 +36630,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="266" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6">
         <v>266</v>
       </c>
@@ -36731,7 +36731,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="267" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6">
         <v>267</v>
       </c>
@@ -36832,7 +36832,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="268" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6">
         <v>268</v>
       </c>
@@ -36933,7 +36933,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="269" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6">
         <v>269</v>
       </c>
@@ -37034,7 +37034,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="270" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6">
         <v>270</v>
       </c>
@@ -37135,7 +37135,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="271" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -37236,7 +37236,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="272" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6">
         <v>272</v>
       </c>
@@ -37337,7 +37337,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="273" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
         <v>273</v>
       </c>
@@ -37438,7 +37438,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="274" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6">
         <v>274</v>
       </c>
@@ -37539,7 +37539,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="275" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6">
         <v>275</v>
       </c>
@@ -37640,7 +37640,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="276" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6">
         <v>276</v>
       </c>
@@ -37741,7 +37741,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="277" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6">
         <v>277</v>
       </c>
@@ -37842,7 +37842,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="278" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6">
         <v>278</v>
       </c>
@@ -37943,7 +37943,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="279" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6">
         <v>279</v>
       </c>
@@ -38044,7 +38044,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="280" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6">
         <v>280</v>
       </c>
@@ -38145,7 +38145,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="281" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
         <v>281</v>
       </c>
@@ -38246,7 +38246,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="282" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6">
         <v>282</v>
       </c>
@@ -38347,7 +38347,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="283" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6">
         <v>283</v>
       </c>
@@ -38448,7 +38448,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="284" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6">
         <v>284</v>
       </c>
@@ -38549,7 +38549,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="285" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
         <v>285</v>
       </c>
@@ -38650,7 +38650,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="286" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6">
         <v>286</v>
       </c>
@@ -38751,7 +38751,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="287" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6">
         <v>287</v>
       </c>
@@ -38852,7 +38852,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="288" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6">
         <v>288</v>
       </c>
@@ -38953,7 +38953,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="289" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6">
         <v>289</v>
       </c>
@@ -39054,7 +39054,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="290" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6">
         <v>290</v>
       </c>
@@ -39155,7 +39155,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="291" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6">
         <v>291</v>
       </c>
@@ -39256,7 +39256,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="292" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6">
         <v>292</v>
       </c>
@@ -39357,7 +39357,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="293" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6">
         <v>293</v>
       </c>
@@ -39458,7 +39458,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="294" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6">
         <v>294</v>
       </c>
@@ -39559,7 +39559,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="295" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
         <v>295</v>
       </c>
@@ -39660,7 +39660,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="296" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6">
         <v>296</v>
       </c>
@@ -39761,7 +39761,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="297" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6">
         <v>297</v>
       </c>
@@ -39862,7 +39862,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="298" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6">
         <v>298</v>
       </c>
@@ -39963,7 +39963,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="299" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6">
         <v>299</v>
       </c>
@@ -40064,7 +40064,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="300" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6">
         <v>300</v>
       </c>
@@ -40165,7 +40165,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="301" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6">
         <v>301</v>
       </c>
@@ -40266,7 +40266,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="302" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6">
         <v>302</v>
       </c>
@@ -40367,7 +40367,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="303" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6">
         <v>303</v>
       </c>
@@ -40468,7 +40468,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6">
         <v>304</v>
       </c>
@@ -40570,7 +40570,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="305" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6">
         <v>305</v>
       </c>
@@ -40672,7 +40672,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="306" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6">
         <v>306</v>
       </c>
@@ -40774,7 +40774,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="307" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6">
         <v>307</v>
       </c>
@@ -40876,7 +40876,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="308" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6">
         <v>308</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D44FAFE-1176-4F9D-A3F6-B76E769C13A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96204BFE-BC59-486D-B478-010B00289A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="10" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10978" uniqueCount="1060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="1076">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -3144,9 +3144,6 @@
     <t>NBR.Temáticas</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>[ IfcActor ]</t>
   </si>
   <si>
@@ -3198,18 +3195,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -3271,6 +3256,69 @@
   </si>
   <si>
     <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
   </si>
 </sst>
 </file>
@@ -3872,7 +3920,169 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{001CC4A1-5641-437E-9DC4-857BB9658EC6}"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="46">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4052,14 +4262,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -4108,11 +4310,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4451,14 +4655,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B80B61-09F0-4F35-A733-85777283AFC6}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="56.69921875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="56.6640625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.19921875" customWidth="1"/>
-    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.296875" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" customWidth="1"/>
+    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -4469,7 +4673,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>320</v>
       </c>
@@ -4480,7 +4684,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>321</v>
       </c>
@@ -4491,7 +4695,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4502,7 +4706,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -4514,7 +4718,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -4526,7 +4730,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4537,7 +4741,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
         <v>9</v>
       </c>
@@ -4548,7 +4752,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>322</v>
       </c>
@@ -4559,7 +4763,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>324</v>
       </c>
@@ -4570,7 +4774,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>325</v>
       </c>
@@ -4581,7 +4785,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -4592,7 +4796,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>326</v>
       </c>
@@ -4603,7 +4807,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>327</v>
       </c>
@@ -4614,7 +4818,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>328</v>
       </c>
@@ -4625,7 +4829,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>329</v>
       </c>
@@ -4636,7 +4840,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -4647,19 +4851,19 @@
         <v>704</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B18" s="38">
         <f ca="1">NOW()</f>
-        <v>46264.561929513889</v>
+        <v>46268.459468981484</v>
       </c>
       <c r="C18" s="37" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>713</v>
       </c>
@@ -4670,7 +4874,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="34" t="s">
         <v>708</v>
       </c>
@@ -4682,7 +4886,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="34" t="s">
         <v>714</v>
       </c>
@@ -4694,7 +4898,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="34" t="s">
         <v>319</v>
       </c>
@@ -4705,7 +4909,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="34" t="s">
         <v>331</v>
       </c>
@@ -4716,7 +4920,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>336</v>
       </c>
@@ -4727,7 +4931,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>338</v>
       </c>
@@ -4738,7 +4942,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="39" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" s="39" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="34" t="s">
         <v>700</v>
       </c>
@@ -4749,7 +4953,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
         <v>988</v>
       </c>
@@ -4760,7 +4964,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="34" t="s">
         <v>990</v>
       </c>
@@ -4771,7 +4975,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="34" t="s">
         <v>992</v>
       </c>
@@ -4782,7 +4986,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="34" t="s">
         <v>994</v>
       </c>
@@ -4793,7 +4997,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="34" t="s">
         <v>996</v>
       </c>
@@ -4804,7 +5008,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="34" t="s">
         <v>998</v>
       </c>
@@ -4815,7 +5019,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="34" t="s">
         <v>1000</v>
       </c>
@@ -4826,7 +5030,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="34" t="s">
         <v>1002</v>
       </c>
@@ -4837,7 +5041,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="34" t="s">
         <v>1004</v>
       </c>
@@ -4848,7 +5052,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="34" t="s">
         <v>1006</v>
       </c>
@@ -4859,7 +5063,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="34" t="s">
         <v>1008</v>
       </c>
@@ -4870,7 +5074,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>1010</v>
       </c>
@@ -4881,7 +5085,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="34" t="s">
         <v>1012</v>
       </c>
@@ -4907,38 +5111,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFFE5C0-D3D8-4876-B71B-E260AD929073}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC48"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC52"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.796875" style="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.296875" style="66" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.19921875" style="66" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="66" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="66" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="66" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.19921875" style="66" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="66" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" style="66" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="66" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" style="39" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.19921875" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="39" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.19921875" style="39" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="62.296875" style="39" customWidth="1"/>
+    <col min="16" max="16" width="78.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="62.33203125" style="39" customWidth="1"/>
     <col min="18" max="18" width="54.5" style="39" customWidth="1"/>
     <col min="19" max="19" width="5" style="66" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.19921875" style="39" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" style="39" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.19921875" style="39" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" style="39" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.796875" style="66" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="66" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="38.5" style="39" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9" style="39" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="44.796875" style="39" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" style="39" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.69921875" style="39" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.796875" style="39"/>
+    <col min="29" max="29" width="6.6640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.83203125" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>649</v>
       </c>
@@ -5015,19 +5219,19 @@
         <v>697</v>
       </c>
       <c r="Z1" s="20" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AA1" s="20" t="s">
         <v>698</v>
       </c>
       <c r="AB1" s="20" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AC1" s="20" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48">
         <v>2</v>
       </c>
@@ -5109,22 +5313,22 @@
         <v>Key-ABNT-2</v>
       </c>
       <c r="Y2" s="33" t="s">
+        <v>1023</v>
+      </c>
+      <c r="Z2" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA2" s="33" t="s">
         <v>1024</v>
       </c>
-      <c r="Z2" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA2" s="33" t="s">
-        <v>1025</v>
-      </c>
-      <c r="AB2" s="33" t="s">
-        <v>1017</v>
+      <c r="AB2" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC2" s="33" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="48">
         <v>3</v>
       </c>
@@ -5206,22 +5410,22 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="Y3" s="33" t="s">
+        <v>1025</v>
+      </c>
+      <c r="Z3" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA3" s="33" t="s">
         <v>1026</v>
       </c>
-      <c r="Z3" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA3" s="33" t="s">
-        <v>1027</v>
-      </c>
-      <c r="AB3" s="33" t="s">
-        <v>1017</v>
+      <c r="AB3" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC3" s="33" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="48">
         <v>4</v>
       </c>
@@ -5302,23 +5506,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-4</v>
       </c>
-      <c r="Y4" s="33" t="s">
+      <c r="Y4" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z4" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA4" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z4" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA4" s="33" t="s">
-        <v>1018</v>
-      </c>
-      <c r="AB4" s="33" t="s">
-        <v>1017</v>
+      <c r="AB4" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC4" s="33" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="48">
         <v>5</v>
       </c>
@@ -5400,22 +5604,22 @@
         <v>Key-ABNT-5</v>
       </c>
       <c r="Y5" s="33" t="s">
+        <v>1018</v>
+      </c>
+      <c r="Z5" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA5" s="33" t="s">
         <v>1019</v>
       </c>
-      <c r="Z5" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA5" s="33" t="s">
-        <v>1020</v>
-      </c>
-      <c r="AB5" s="33" t="s">
-        <v>1017</v>
+      <c r="AB5" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC5" s="33" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="48">
         <v>6</v>
       </c>
@@ -5496,23 +5700,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-6</v>
       </c>
-      <c r="Y6" s="33" t="s">
+      <c r="Y6" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z6" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA6" s="33" t="s">
         <v>1017</v>
       </c>
-      <c r="Z6" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA6" s="33" t="s">
-        <v>1018</v>
-      </c>
-      <c r="AB6" s="33" t="s">
-        <v>1017</v>
+      <c r="AB6" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC6" s="33" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="7" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="48">
         <v>7</v>
       </c>
@@ -5593,23 +5797,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-7</v>
       </c>
-      <c r="Y7" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z7" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA7" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB7" s="33" t="s">
-        <v>1017</v>
+      <c r="Y7" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z7" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA7" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB7" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC7" s="33" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="8" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="48">
         <v>8</v>
       </c>
@@ -5690,23 +5894,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-8</v>
       </c>
-      <c r="Y8" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z8" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA8" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB8" s="33" t="s">
-        <v>1017</v>
+      <c r="Y8" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z8" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA8" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB8" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC8" s="33" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="9" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="48">
         <v>9</v>
       </c>
@@ -5787,23 +5991,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-9</v>
       </c>
-      <c r="Y9" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z9" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA9" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB9" s="33" t="s">
-        <v>1017</v>
+      <c r="Y9" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z9" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA9" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB9" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC9" s="33" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="10" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="48">
         <v>10</v>
       </c>
@@ -5884,23 +6088,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-10</v>
       </c>
-      <c r="Y10" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z10" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA10" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB10" s="33" t="s">
-        <v>1017</v>
+      <c r="Y10" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z10" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA10" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB10" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC10" s="33" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="11" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="48">
         <v>11</v>
       </c>
@@ -5981,23 +6185,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-11</v>
       </c>
-      <c r="Y11" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z11" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA11" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB11" s="33" t="s">
-        <v>1017</v>
+      <c r="Y11" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z11" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA11" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB11" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC11" s="33" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="12" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="48">
         <v>12</v>
       </c>
@@ -6079,22 +6283,22 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="Y12" s="33" t="s">
-        <v>1021</v>
-      </c>
-      <c r="Z12" s="33" t="s">
-        <v>1017</v>
+        <v>1020</v>
+      </c>
+      <c r="Z12" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AA12" s="33" t="s">
-        <v>1028</v>
-      </c>
-      <c r="AB12" s="33" t="s">
-        <v>1017</v>
+        <v>1027</v>
+      </c>
+      <c r="AB12" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC12" s="33" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="13" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="48">
         <v>13</v>
       </c>
@@ -6176,22 +6380,22 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="Y13" s="33" t="s">
-        <v>1021</v>
-      </c>
-      <c r="Z13" s="33" t="s">
-        <v>1017</v>
+        <v>1020</v>
+      </c>
+      <c r="Z13" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AA13" s="33" t="s">
-        <v>1028</v>
-      </c>
-      <c r="AB13" s="33" t="s">
-        <v>1017</v>
+        <v>1027</v>
+      </c>
+      <c r="AB13" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC13" s="33" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="14" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="48">
         <v>14</v>
       </c>
@@ -6273,22 +6477,22 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="Y14" s="67" t="s">
+        <v>1021</v>
+      </c>
+      <c r="Z14" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA14" s="68" t="s">
         <v>1022</v>
       </c>
-      <c r="Z14" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA14" s="68" t="s">
-        <v>1023</v>
-      </c>
-      <c r="AB14" s="33" t="s">
-        <v>1017</v>
+      <c r="AB14" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC14" s="33" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="48">
         <v>15</v>
       </c>
@@ -6366,26 +6570,26 @@
         <v>716</v>
       </c>
       <c r="X15" s="56" t="str">
-        <f t="shared" ref="X15:X48" si="11">CONCATENATE("Key-ABNT-",A15)</f>
+        <f t="shared" ref="X15:X52" si="11">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
       </c>
-      <c r="Y15" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z15" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA15" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB15" s="33" t="s">
-        <v>1017</v>
+      <c r="Y15" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z15" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA15" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB15" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC15" s="55" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="48">
         <v>16</v>
       </c>
@@ -6466,23 +6670,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-16</v>
       </c>
-      <c r="Y16" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z16" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA16" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB16" s="33" t="s">
-        <v>1017</v>
+      <c r="Y16" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z16" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA16" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB16" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC16" s="55" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="48">
         <v>17</v>
       </c>
@@ -6563,23 +6767,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-17</v>
       </c>
-      <c r="Y17" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z17" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA17" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB17" s="33" t="s">
-        <v>1017</v>
+      <c r="Y17" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z17" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA17" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB17" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC17" s="55" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="48">
         <v>18</v>
       </c>
@@ -6660,23 +6864,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-18</v>
       </c>
-      <c r="Y18" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z18" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA18" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB18" s="33" t="s">
-        <v>1017</v>
+      <c r="Y18" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z18" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA18" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB18" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC18" s="55" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="48">
         <v>19</v>
       </c>
@@ -6757,23 +6961,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-19</v>
       </c>
-      <c r="Y19" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z19" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA19" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB19" s="33" t="s">
-        <v>1017</v>
+      <c r="Y19" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z19" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA19" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB19" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC19" s="55" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="48">
         <v>20</v>
       </c>
@@ -6854,23 +7058,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-20</v>
       </c>
-      <c r="Y20" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z20" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA20" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB20" s="33" t="s">
-        <v>1017</v>
+      <c r="Y20" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z20" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA20" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB20" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC20" s="55" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="48">
         <v>21</v>
       </c>
@@ -6951,23 +7155,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-21</v>
       </c>
-      <c r="Y21" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z21" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA21" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB21" s="33" t="s">
-        <v>1017</v>
+      <c r="Y21" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z21" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA21" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB21" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC21" s="55" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="48">
         <v>22</v>
       </c>
@@ -7048,23 +7252,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-22</v>
       </c>
-      <c r="Y22" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z22" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA22" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB22" s="33" t="s">
-        <v>1017</v>
+      <c r="Y22" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z22" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA22" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB22" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC22" s="55" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="48">
         <v>23</v>
       </c>
@@ -7145,23 +7349,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-23</v>
       </c>
-      <c r="Y23" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z23" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA23" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB23" s="33" t="s">
-        <v>1017</v>
+      <c r="Y23" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z23" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA23" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB23" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC23" s="55" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="48">
         <v>24</v>
       </c>
@@ -7242,23 +7446,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-24</v>
       </c>
-      <c r="Y24" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z24" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA24" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB24" s="33" t="s">
-        <v>1017</v>
+      <c r="Y24" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z24" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA24" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB24" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC24" s="55" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="48">
         <v>25</v>
       </c>
@@ -7339,23 +7543,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-25</v>
       </c>
-      <c r="Y25" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z25" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA25" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB25" s="33" t="s">
-        <v>1017</v>
+      <c r="Y25" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z25" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA25" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB25" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC25" s="55" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="48">
         <v>26</v>
       </c>
@@ -7436,23 +7640,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-26</v>
       </c>
-      <c r="Y26" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z26" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA26" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB26" s="33" t="s">
-        <v>1017</v>
+      <c r="Y26" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z26" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA26" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB26" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC26" s="55" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="48">
         <v>27</v>
       </c>
@@ -7533,23 +7737,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-27</v>
       </c>
-      <c r="Y27" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z27" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA27" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB27" s="33" t="s">
-        <v>1017</v>
+      <c r="Y27" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z27" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA27" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB27" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC27" s="55" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="48">
         <v>28</v>
       </c>
@@ -7630,23 +7834,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-28</v>
       </c>
-      <c r="Y28" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z28" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA28" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB28" s="33" t="s">
-        <v>1017</v>
+      <c r="Y28" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z28" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA28" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB28" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC28" s="55" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="48">
         <v>29</v>
       </c>
@@ -7727,23 +7931,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-29</v>
       </c>
-      <c r="Y29" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z29" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA29" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB29" s="33" t="s">
-        <v>1017</v>
+      <c r="Y29" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z29" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA29" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB29" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC29" s="55" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="48">
         <v>30</v>
       </c>
@@ -7824,23 +8028,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-30</v>
       </c>
-      <c r="Y30" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z30" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA30" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB30" s="33" t="s">
-        <v>1017</v>
+      <c r="Y30" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z30" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA30" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB30" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC30" s="55" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="48">
         <v>31</v>
       </c>
@@ -7921,23 +8125,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-31</v>
       </c>
-      <c r="Y31" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z31" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA31" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB31" s="33" t="s">
-        <v>1017</v>
+      <c r="Y31" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z31" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA31" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB31" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC31" s="55" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="48">
         <v>32</v>
       </c>
@@ -8018,23 +8222,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-32</v>
       </c>
-      <c r="Y32" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z32" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA32" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB32" s="33" t="s">
-        <v>1017</v>
+      <c r="Y32" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z32" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA32" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB32" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC32" s="55" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48">
         <v>33</v>
       </c>
@@ -8115,23 +8319,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-33</v>
       </c>
-      <c r="Y33" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z33" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA33" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB33" s="33" t="s">
-        <v>1017</v>
+      <c r="Y33" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z33" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA33" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB33" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC33" s="55" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="48">
         <v>34</v>
       </c>
@@ -8212,23 +8416,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-34</v>
       </c>
-      <c r="Y34" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z34" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA34" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB34" s="33" t="s">
-        <v>1017</v>
+      <c r="Y34" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z34" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA34" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB34" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC34" s="55" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="48">
         <v>35</v>
       </c>
@@ -8309,23 +8513,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-35</v>
       </c>
-      <c r="Y35" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z35" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA35" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB35" s="33" t="s">
-        <v>1017</v>
+      <c r="Y35" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z35" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA35" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB35" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC35" s="55" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="48">
         <v>36</v>
       </c>
@@ -8406,23 +8610,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-36</v>
       </c>
-      <c r="Y36" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z36" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA36" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB36" s="33" t="s">
-        <v>1017</v>
+      <c r="Y36" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z36" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA36" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB36" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC36" s="55" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="48">
         <v>37</v>
       </c>
@@ -8503,23 +8707,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-37</v>
       </c>
-      <c r="Y37" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z37" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA37" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB37" s="33" t="s">
-        <v>1017</v>
+      <c r="Y37" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z37" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA37" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB37" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC37" s="55" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="48">
         <v>38</v>
       </c>
@@ -8600,23 +8804,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-38</v>
       </c>
-      <c r="Y38" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z38" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA38" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB38" s="33" t="s">
-        <v>1017</v>
+      <c r="Y38" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z38" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA38" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB38" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC38" s="55" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="48">
         <v>39</v>
       </c>
@@ -8697,23 +8901,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-39</v>
       </c>
-      <c r="Y39" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z39" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA39" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB39" s="33" t="s">
-        <v>1017</v>
+      <c r="Y39" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z39" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA39" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB39" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC39" s="55" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="48">
         <v>40</v>
       </c>
@@ -8794,23 +8998,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-40</v>
       </c>
-      <c r="Y40" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z40" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA40" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB40" s="33" t="s">
-        <v>1017</v>
+      <c r="Y40" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z40" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA40" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB40" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC40" s="55" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="48">
         <v>41</v>
       </c>
@@ -8891,23 +9095,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-41</v>
       </c>
-      <c r="Y41" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z41" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA41" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB41" s="33" t="s">
-        <v>1017</v>
+      <c r="Y41" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z41" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA41" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB41" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC41" s="55" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="48">
         <v>42</v>
       </c>
@@ -8988,23 +9192,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-42</v>
       </c>
-      <c r="Y42" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z42" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA42" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB42" s="33" t="s">
-        <v>1017</v>
+      <c r="Y42" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z42" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA42" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB42" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC42" s="55" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="48">
         <v>43</v>
       </c>
@@ -9085,23 +9289,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-43</v>
       </c>
-      <c r="Y43" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z43" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA43" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB43" s="33" t="s">
-        <v>1017</v>
+      <c r="Y43" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z43" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA43" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB43" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC43" s="55" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="48">
         <v>44</v>
       </c>
@@ -9182,23 +9386,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-44</v>
       </c>
-      <c r="Y44" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z44" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA44" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB44" s="33" t="s">
-        <v>1017</v>
+      <c r="Y44" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z44" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA44" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB44" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC44" s="55" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="48">
         <v>45</v>
       </c>
@@ -9279,23 +9483,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-45</v>
       </c>
-      <c r="Y45" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z45" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA45" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB45" s="33" t="s">
-        <v>1017</v>
+      <c r="Y45" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z45" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA45" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB45" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC45" s="55" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="48">
         <v>46</v>
       </c>
@@ -9376,23 +9580,23 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-46</v>
       </c>
-      <c r="Y46" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z46" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA46" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB46" s="33" t="s">
-        <v>1017</v>
+      <c r="Y46" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z46" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA46" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB46" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC46" s="55" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="48">
         <v>47</v>
       </c>
@@ -9473,40 +9677,40 @@
         <f t="shared" si="11"/>
         <v>Key-ABNT-47</v>
       </c>
-      <c r="Y47" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="Z47" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AA47" s="33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AB47" s="33" t="s">
-        <v>1017</v>
+      <c r="Y47" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z47" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA47" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB47" s="69" t="s">
+        <v>332</v>
       </c>
       <c r="AC47" s="55" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="48" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="48">
         <v>48</v>
       </c>
       <c r="B48" s="49" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C48" s="29" t="s">
         <v>1031</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="D48" s="29" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E48" s="29" t="s">
         <v>1032</v>
       </c>
-      <c r="D48" s="29" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E48" s="29" t="s">
-        <v>1033</v>
-      </c>
       <c r="F48" s="29" t="s">
-        <v>1035</v>
+        <v>1055</v>
       </c>
       <c r="G48" s="31" t="s">
         <v>332</v>
@@ -9524,7 +9728,7 @@
         <v>332</v>
       </c>
       <c r="L48" s="50" t="str">
-        <f t="shared" ref="L48:O48" si="12">SUBSTITUTE(CONCATENATE("", C48), ".", " ")</f>
+        <f t="shared" ref="L48:O52" si="12">SUBSTITUTE(CONCATENATE("", C48), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M48" s="50" t="str">
@@ -9537,22 +9741,22 @@
       </c>
       <c r="O48" s="50" t="str">
         <f t="shared" si="12"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P48" s="33" t="s">
-        <v>1036</v>
+        <v>1056</v>
       </c>
       <c r="Q48" s="33" t="s">
-        <v>1037</v>
+        <v>1057</v>
       </c>
       <c r="R48" s="33" t="s">
-        <v>1038</v>
+        <v>1058</v>
       </c>
       <c r="S48" s="33" t="s">
         <v>332</v>
       </c>
       <c r="T48" s="33" t="str">
-        <f t="shared" ref="T48:V48" si="13">SUBSTITUTE(C48, ".", " ")</f>
+        <f t="shared" ref="T48:V52" si="13">SUBSTITUTE(C48, ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="U48" s="33" t="str">
@@ -9586,40 +9790,426 @@
         <v>332</v>
       </c>
     </row>
+    <row r="49" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="48">
+        <v>49</v>
+      </c>
+      <c r="B49" s="49" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C49" s="29" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E49" s="29" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F49" s="29" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G49" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="H49" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="I49" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="J49" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="K49" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="L49" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>De API</v>
+      </c>
+      <c r="M49" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Macros</v>
+      </c>
+      <c r="N49" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O49" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P49" s="33" t="s">
+        <v>1060</v>
+      </c>
+      <c r="Q49" s="33" t="s">
+        <v>1061</v>
+      </c>
+      <c r="R49" s="33" t="s">
+        <v>1062</v>
+      </c>
+      <c r="S49" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T49" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>De API</v>
+      </c>
+      <c r="U49" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Macros</v>
+      </c>
+      <c r="V49" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W49" s="33" t="s">
+        <v>716</v>
+      </c>
+      <c r="X49" s="56" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-ABNT-49</v>
+      </c>
+      <c r="Y49" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z49" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA49" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB49" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AC49" s="69" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="48">
+        <v>50</v>
+      </c>
+      <c r="B50" s="49" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C50" s="29" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E50" s="29" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F50" s="29" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G50" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="H50" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="I50" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="J50" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="K50" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="L50" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>De API</v>
+      </c>
+      <c r="M50" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Macros</v>
+      </c>
+      <c r="N50" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O50" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P50" s="33" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Q50" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="R50" s="33" t="s">
+        <v>1066</v>
+      </c>
+      <c r="S50" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T50" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>De API</v>
+      </c>
+      <c r="U50" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Macros</v>
+      </c>
+      <c r="V50" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W50" s="33" t="s">
+        <v>716</v>
+      </c>
+      <c r="X50" s="56" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-ABNT-50</v>
+      </c>
+      <c r="Y50" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z50" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA50" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB50" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AC50" s="69" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="48">
+        <v>51</v>
+      </c>
+      <c r="B51" s="49" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C51" s="29" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E51" s="29" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F51" s="29" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G51" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="H51" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="I51" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="J51" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="K51" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="L51" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>De API</v>
+      </c>
+      <c r="M51" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Macros</v>
+      </c>
+      <c r="N51" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O51" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P51" s="33" t="s">
+        <v>1068</v>
+      </c>
+      <c r="Q51" s="33" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R51" s="33" t="s">
+        <v>1070</v>
+      </c>
+      <c r="S51" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T51" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>De API</v>
+      </c>
+      <c r="U51" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Macros</v>
+      </c>
+      <c r="V51" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W51" s="33" t="s">
+        <v>716</v>
+      </c>
+      <c r="X51" s="56" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-ABNT-51</v>
+      </c>
+      <c r="Y51" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z51" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA51" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB51" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AC51" s="69" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="48">
+        <v>52</v>
+      </c>
+      <c r="B52" s="49" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C52" s="29" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E52" s="29" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F52" s="29" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G52" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="H52" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="I52" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="J52" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="K52" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="L52" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>De API</v>
+      </c>
+      <c r="M52" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Macros</v>
+      </c>
+      <c r="N52" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O52" s="50" t="str">
+        <f t="shared" si="12"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P52" s="33" t="s">
+        <v>1073</v>
+      </c>
+      <c r="Q52" s="33" t="s">
+        <v>1074</v>
+      </c>
+      <c r="R52" s="33" t="s">
+        <v>1075</v>
+      </c>
+      <c r="S52" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T52" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>De API</v>
+      </c>
+      <c r="U52" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Macros</v>
+      </c>
+      <c r="V52" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W52" s="33" t="s">
+        <v>716</v>
+      </c>
+      <c r="X52" s="56" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-ABNT-52</v>
+      </c>
+      <c r="Y52" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z52" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA52" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB52" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="AC52" s="69" t="s">
+        <v>332</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B48">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B52">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E52:F52">
+    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="26" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
+  <conditionalFormatting sqref="F48:F51">
+    <cfRule type="duplicateValues" dxfId="43" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R14">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R15:R47">
-    <cfRule type="duplicateValues" dxfId="23" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R48">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="41" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC15:AC47">
-    <cfRule type="duplicateValues" dxfId="19" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="42"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -9632,13 +10222,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B5591C-1220-489B-957E-6F42AD7CFACA}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>650</v>
       </c>
@@ -9703,7 +10293,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -9770,7 +10360,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9785,13 +10375,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26462613-E7D7-4ABD-BD2B-4B8A0B104ED0}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="17.19921875" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="26">
         <v>1</v>
       </c>
@@ -9802,7 +10392,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="17">
         <v>2</v>
       </c>
@@ -9815,7 +10405,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9827,45 +10417,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4160801D-A855-4DB1-BB60-92D2B856BA2E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG308"/>
-  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.19921875" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" style="47" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" style="47" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.69921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.69921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.19921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.19921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.19921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.796875" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.296875" style="47" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="56.296875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="7.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.83203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.33203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="56.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.19921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.69921875" style="47" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.19921875" style="1"/>
+    <col min="34" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>333</v>
       </c>
@@ -9966,7 +10556,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -10067,7 +10657,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -10168,7 +10758,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>4</v>
       </c>
@@ -10269,7 +10859,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>5</v>
       </c>
@@ -10370,7 +10960,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>6</v>
       </c>
@@ -10471,7 +11061,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>7</v>
       </c>
@@ -10572,7 +11162,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>8</v>
       </c>
@@ -10673,7 +11263,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>9</v>
       </c>
@@ -10774,7 +11364,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>10</v>
       </c>
@@ -10875,7 +11465,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>11</v>
       </c>
@@ -10976,7 +11566,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>12</v>
       </c>
@@ -11077,7 +11667,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>13</v>
       </c>
@@ -11178,7 +11768,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>14</v>
       </c>
@@ -11279,7 +11869,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>15</v>
       </c>
@@ -11380,7 +11970,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>16</v>
       </c>
@@ -11481,7 +12071,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>17</v>
       </c>
@@ -11582,7 +12172,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>18</v>
       </c>
@@ -11683,7 +12273,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>19</v>
       </c>
@@ -11784,7 +12374,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>20</v>
       </c>
@@ -11885,7 +12475,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>21</v>
       </c>
@@ -11986,7 +12576,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>22</v>
       </c>
@@ -12087,7 +12677,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>23</v>
       </c>
@@ -12188,7 +12778,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>24</v>
       </c>
@@ -12289,7 +12879,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>25</v>
       </c>
@@ -12390,7 +12980,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>26</v>
       </c>
@@ -12491,7 +13081,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>27</v>
       </c>
@@ -12592,7 +13182,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>28</v>
       </c>
@@ -12693,7 +13283,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>29</v>
       </c>
@@ -12794,7 +13384,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>30</v>
       </c>
@@ -12895,7 +13485,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>31</v>
       </c>
@@ -12996,7 +13586,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>32</v>
       </c>
@@ -13097,7 +13687,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>33</v>
       </c>
@@ -13198,7 +13788,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>34</v>
       </c>
@@ -13299,7 +13889,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>35</v>
       </c>
@@ -13400,7 +13990,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>36</v>
       </c>
@@ -13501,7 +14091,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>37</v>
       </c>
@@ -13602,7 +14192,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>38</v>
       </c>
@@ -13703,7 +14293,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>39</v>
       </c>
@@ -13804,7 +14394,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>40</v>
       </c>
@@ -13905,7 +14495,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>41</v>
       </c>
@@ -14006,7 +14596,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>42</v>
       </c>
@@ -14107,7 +14697,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>43</v>
       </c>
@@ -14208,7 +14798,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>44</v>
       </c>
@@ -14309,7 +14899,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>45</v>
       </c>
@@ -14410,7 +15000,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>46</v>
       </c>
@@ -14511,7 +15101,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>47</v>
       </c>
@@ -14612,7 +15202,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>48</v>
       </c>
@@ -14713,7 +15303,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>49</v>
       </c>
@@ -14814,7 +15404,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>50</v>
       </c>
@@ -14915,7 +15505,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>51</v>
       </c>
@@ -15016,7 +15606,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>52</v>
       </c>
@@ -15117,7 +15707,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>53</v>
       </c>
@@ -15218,7 +15808,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>54</v>
       </c>
@@ -15319,7 +15909,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>55</v>
       </c>
@@ -15420,7 +16010,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>56</v>
       </c>
@@ -15521,7 +16111,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>57</v>
       </c>
@@ -15622,7 +16212,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>58</v>
       </c>
@@ -15723,7 +16313,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>59</v>
       </c>
@@ -15824,7 +16414,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>60</v>
       </c>
@@ -15925,7 +16515,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>61</v>
       </c>
@@ -16026,7 +16616,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>62</v>
       </c>
@@ -16127,7 +16717,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>63</v>
       </c>
@@ -16228,7 +16818,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>64</v>
       </c>
@@ -16329,7 +16919,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>65</v>
       </c>
@@ -16430,7 +17020,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>66</v>
       </c>
@@ -16531,7 +17121,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>67</v>
       </c>
@@ -16632,7 +17222,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>68</v>
       </c>
@@ -16733,7 +17323,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>69</v>
       </c>
@@ -16834,7 +17424,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>70</v>
       </c>
@@ -16935,7 +17525,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>71</v>
       </c>
@@ -17036,7 +17626,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>72</v>
       </c>
@@ -17137,7 +17727,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>73</v>
       </c>
@@ -17238,7 +17828,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>74</v>
       </c>
@@ -17339,7 +17929,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>75</v>
       </c>
@@ -17440,7 +18030,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>76</v>
       </c>
@@ -17541,7 +18131,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>77</v>
       </c>
@@ -17642,7 +18232,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>78</v>
       </c>
@@ -17743,7 +18333,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>79</v>
       </c>
@@ -17844,7 +18434,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>80</v>
       </c>
@@ -17945,7 +18535,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>81</v>
       </c>
@@ -18046,7 +18636,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>82</v>
       </c>
@@ -18147,7 +18737,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>83</v>
       </c>
@@ -18248,7 +18838,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>84</v>
       </c>
@@ -18349,7 +18939,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>85</v>
       </c>
@@ -18450,7 +19040,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>86</v>
       </c>
@@ -18551,7 +19141,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>87</v>
       </c>
@@ -18652,7 +19242,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>88</v>
       </c>
@@ -18753,7 +19343,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -18854,7 +19444,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>90</v>
       </c>
@@ -18955,7 +19545,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>91</v>
       </c>
@@ -19056,7 +19646,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>92</v>
       </c>
@@ -19157,7 +19747,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>93</v>
       </c>
@@ -19258,7 +19848,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>94</v>
       </c>
@@ -19359,7 +19949,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>95</v>
       </c>
@@ -19460,7 +20050,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>96</v>
       </c>
@@ -19561,7 +20151,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>97</v>
       </c>
@@ -19662,7 +20252,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>98</v>
       </c>
@@ -19763,7 +20353,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -19864,7 +20454,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>100</v>
       </c>
@@ -19965,7 +20555,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>101</v>
       </c>
@@ -20066,7 +20656,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>102</v>
       </c>
@@ -20167,7 +20757,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>103</v>
       </c>
@@ -20268,7 +20858,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>104</v>
       </c>
@@ -20369,7 +20959,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>105</v>
       </c>
@@ -20470,7 +21060,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>106</v>
       </c>
@@ -20571,7 +21161,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -20672,7 +21262,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -20773,7 +21363,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>109</v>
       </c>
@@ -20874,7 +21464,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>110</v>
       </c>
@@ -20975,7 +21565,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>111</v>
       </c>
@@ -21076,7 +21666,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>112</v>
       </c>
@@ -21177,7 +21767,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>113</v>
       </c>
@@ -21278,7 +21868,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>114</v>
       </c>
@@ -21379,7 +21969,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>115</v>
       </c>
@@ -21480,7 +22070,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>116</v>
       </c>
@@ -21581,7 +22171,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>117</v>
       </c>
@@ -21682,7 +22272,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>118</v>
       </c>
@@ -21783,7 +22373,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>119</v>
       </c>
@@ -21884,7 +22474,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>120</v>
       </c>
@@ -21985,7 +22575,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>121</v>
       </c>
@@ -22086,7 +22676,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>122</v>
       </c>
@@ -22187,7 +22777,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>123</v>
       </c>
@@ -22288,7 +22878,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>124</v>
       </c>
@@ -22389,7 +22979,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>125</v>
       </c>
@@ -22490,7 +23080,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>126</v>
       </c>
@@ -22591,7 +23181,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>127</v>
       </c>
@@ -22692,7 +23282,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>128</v>
       </c>
@@ -22793,7 +23383,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>129</v>
       </c>
@@ -22894,7 +23484,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="6">
         <v>130</v>
       </c>
@@ -22995,7 +23585,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>131</v>
       </c>
@@ -23096,7 +23686,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="6">
         <v>132</v>
       </c>
@@ -23197,7 +23787,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>133</v>
       </c>
@@ -23298,7 +23888,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="6">
         <v>134</v>
       </c>
@@ -23399,7 +23989,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>135</v>
       </c>
@@ -23500,7 +24090,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="6">
         <v>136</v>
       </c>
@@ -23601,7 +24191,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>137</v>
       </c>
@@ -23702,7 +24292,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="6">
         <v>138</v>
       </c>
@@ -23803,7 +24393,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>139</v>
       </c>
@@ -23904,7 +24494,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="6">
         <v>140</v>
       </c>
@@ -24005,7 +24595,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>141</v>
       </c>
@@ -24106,7 +24696,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="6">
         <v>142</v>
       </c>
@@ -24207,7 +24797,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>143</v>
       </c>
@@ -24308,7 +24898,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="6">
         <v>144</v>
       </c>
@@ -24409,7 +24999,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>145</v>
       </c>
@@ -24510,7 +25100,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="6">
         <v>146</v>
       </c>
@@ -24611,7 +25201,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>147</v>
       </c>
@@ -24712,7 +25302,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="6">
         <v>148</v>
       </c>
@@ -24813,7 +25403,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>149</v>
       </c>
@@ -24914,7 +25504,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="6">
         <v>150</v>
       </c>
@@ -25015,7 +25605,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>151</v>
       </c>
@@ -25116,7 +25706,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="6">
         <v>152</v>
       </c>
@@ -25217,7 +25807,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>153</v>
       </c>
@@ -25318,7 +25908,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="6">
         <v>154</v>
       </c>
@@ -25419,7 +26009,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>155</v>
       </c>
@@ -25520,7 +26110,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="6">
         <v>156</v>
       </c>
@@ -25621,7 +26211,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>157</v>
       </c>
@@ -25722,7 +26312,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="6">
         <v>158</v>
       </c>
@@ -25823,7 +26413,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>159</v>
       </c>
@@ -25924,7 +26514,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="6">
         <v>160</v>
       </c>
@@ -26025,7 +26615,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>161</v>
       </c>
@@ -26126,7 +26716,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="6">
         <v>162</v>
       </c>
@@ -26227,7 +26817,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>163</v>
       </c>
@@ -26328,7 +26918,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="6">
         <v>164</v>
       </c>
@@ -26429,7 +27019,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>165</v>
       </c>
@@ -26530,7 +27120,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="6">
         <v>166</v>
       </c>
@@ -26631,7 +27221,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>167</v>
       </c>
@@ -26732,7 +27322,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="6">
         <v>168</v>
       </c>
@@ -26833,7 +27423,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>169</v>
       </c>
@@ -26934,7 +27524,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="6">
         <v>170</v>
       </c>
@@ -27035,7 +27625,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>171</v>
       </c>
@@ -27136,7 +27726,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="6">
         <v>172</v>
       </c>
@@ -27237,7 +27827,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>173</v>
       </c>
@@ -27338,7 +27928,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="6">
         <v>174</v>
       </c>
@@ -27439,7 +28029,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>175</v>
       </c>
@@ -27540,7 +28130,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="6">
         <v>176</v>
       </c>
@@ -27641,7 +28231,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>177</v>
       </c>
@@ -27742,7 +28332,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="6">
         <v>178</v>
       </c>
@@ -27843,7 +28433,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="179" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>179</v>
       </c>
@@ -27944,7 +28534,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="180" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="6">
         <v>180</v>
       </c>
@@ -28045,7 +28635,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="181" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -28146,7 +28736,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="182" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="6">
         <v>182</v>
       </c>
@@ -28247,7 +28837,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="183" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>183</v>
       </c>
@@ -28348,7 +28938,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="6">
         <v>184</v>
       </c>
@@ -28449,7 +29039,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="185" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>185</v>
       </c>
@@ -28550,7 +29140,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="6">
         <v>186</v>
       </c>
@@ -28651,7 +29241,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>187</v>
       </c>
@@ -28752,7 +29342,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="188" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="6">
         <v>188</v>
       </c>
@@ -28853,7 +29443,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="189" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>189</v>
       </c>
@@ -28954,7 +29544,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="190" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="6">
         <v>190</v>
       </c>
@@ -29055,7 +29645,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="191" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>191</v>
       </c>
@@ -29156,7 +29746,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="192" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="6">
         <v>192</v>
       </c>
@@ -29257,7 +29847,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="193" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>193</v>
       </c>
@@ -29358,7 +29948,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="194" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="6">
         <v>194</v>
       </c>
@@ -29459,7 +30049,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="195" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>195</v>
       </c>
@@ -29560,7 +30150,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="196" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="6">
         <v>196</v>
       </c>
@@ -29661,7 +30251,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="197" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>197</v>
       </c>
@@ -29762,7 +30352,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="198" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="6">
         <v>198</v>
       </c>
@@ -29863,7 +30453,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="199" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>199</v>
       </c>
@@ -29964,7 +30554,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="200" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="6">
         <v>200</v>
       </c>
@@ -30065,7 +30655,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="201" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>201</v>
       </c>
@@ -30166,7 +30756,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="202" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="6">
         <v>202</v>
       </c>
@@ -30267,7 +30857,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="203" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>203</v>
       </c>
@@ -30368,7 +30958,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="204" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="6">
         <v>204</v>
       </c>
@@ -30469,7 +31059,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="205" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>205</v>
       </c>
@@ -30570,7 +31160,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="206" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="6">
         <v>206</v>
       </c>
@@ -30671,7 +31261,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="207" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>207</v>
       </c>
@@ -30772,7 +31362,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="208" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="6">
         <v>208</v>
       </c>
@@ -30873,7 +31463,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="209" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>209</v>
       </c>
@@ -30974,7 +31564,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="210" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="6">
         <v>210</v>
       </c>
@@ -31075,7 +31665,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="211" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>211</v>
       </c>
@@ -31176,7 +31766,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="212" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="6">
         <v>212</v>
       </c>
@@ -31277,7 +31867,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="213" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>213</v>
       </c>
@@ -31378,7 +31968,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="214" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="6">
         <v>214</v>
       </c>
@@ -31479,7 +32069,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="215" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>215</v>
       </c>
@@ -31580,7 +32170,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="216" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="6">
         <v>216</v>
       </c>
@@ -31681,7 +32271,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="217" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>217</v>
       </c>
@@ -31782,7 +32372,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="218" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -31883,7 +32473,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="219" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>219</v>
       </c>
@@ -31984,7 +32574,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="220" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="6">
         <v>220</v>
       </c>
@@ -32085,7 +32675,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="221" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>221</v>
       </c>
@@ -32186,7 +32776,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="222" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="6">
         <v>222</v>
       </c>
@@ -32287,7 +32877,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="223" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>223</v>
       </c>
@@ -32388,7 +32978,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="224" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="6">
         <v>224</v>
       </c>
@@ -32489,7 +33079,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="225" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>225</v>
       </c>
@@ -32590,7 +33180,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="226" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="6">
         <v>226</v>
       </c>
@@ -32691,7 +33281,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="227" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>227</v>
       </c>
@@ -32792,7 +33382,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="228" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="6">
         <v>228</v>
       </c>
@@ -32893,7 +33483,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="229" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>229</v>
       </c>
@@ -32994,7 +33584,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="230" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="6">
         <v>230</v>
       </c>
@@ -33095,7 +33685,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="231" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>231</v>
       </c>
@@ -33196,7 +33786,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="232" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="6">
         <v>232</v>
       </c>
@@ -33297,7 +33887,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="233" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>233</v>
       </c>
@@ -33398,7 +33988,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="234" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="6">
         <v>234</v>
       </c>
@@ -33499,7 +34089,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="235" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>235</v>
       </c>
@@ -33600,7 +34190,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="236" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="6">
         <v>236</v>
       </c>
@@ -33701,7 +34291,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="237" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>237</v>
       </c>
@@ -33802,7 +34392,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="238" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="6">
         <v>238</v>
       </c>
@@ -33903,7 +34493,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="239" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>239</v>
       </c>
@@ -34004,7 +34594,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="240" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="6">
         <v>240</v>
       </c>
@@ -34105,7 +34695,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="241" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>241</v>
       </c>
@@ -34206,7 +34796,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="242" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="6">
         <v>242</v>
       </c>
@@ -34307,7 +34897,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="243" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>243</v>
       </c>
@@ -34408,7 +34998,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="244" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="6">
         <v>244</v>
       </c>
@@ -34509,7 +35099,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="245" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>245</v>
       </c>
@@ -34610,7 +35200,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="246" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="6">
         <v>246</v>
       </c>
@@ -34711,7 +35301,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="247" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>247</v>
       </c>
@@ -34812,7 +35402,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="6">
         <v>248</v>
       </c>
@@ -34913,7 +35503,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="249" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>249</v>
       </c>
@@ -35014,7 +35604,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="250" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="6">
         <v>250</v>
       </c>
@@ -35115,7 +35705,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="251" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -35216,7 +35806,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="252" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="6">
         <v>252</v>
       </c>
@@ -35317,7 +35907,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>253</v>
       </c>
@@ -35418,7 +36008,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="254" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="6">
         <v>254</v>
       </c>
@@ -35519,7 +36109,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="255" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>255</v>
       </c>
@@ -35620,7 +36210,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="256" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="6">
         <v>256</v>
       </c>
@@ -35721,7 +36311,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="257" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="6">
         <v>257</v>
       </c>
@@ -35822,7 +36412,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="258" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="6">
         <v>258</v>
       </c>
@@ -35923,7 +36513,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="259" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="6">
         <v>259</v>
       </c>
@@ -36024,7 +36614,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="260" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="6">
         <v>260</v>
       </c>
@@ -36125,7 +36715,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="261" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="6">
         <v>261</v>
       </c>
@@ -36226,7 +36816,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="262" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="6">
         <v>262</v>
       </c>
@@ -36327,7 +36917,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="263" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="6">
         <v>263</v>
       </c>
@@ -36428,7 +37018,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="264" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="6">
         <v>264</v>
       </c>
@@ -36529,7 +37119,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="265" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="6">
         <v>265</v>
       </c>
@@ -36630,7 +37220,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="266" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="6">
         <v>266</v>
       </c>
@@ -36731,7 +37321,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="267" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="6">
         <v>267</v>
       </c>
@@ -36832,7 +37422,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="268" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="6">
         <v>268</v>
       </c>
@@ -36933,7 +37523,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="269" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="6">
         <v>269</v>
       </c>
@@ -37034,7 +37624,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="270" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="6">
         <v>270</v>
       </c>
@@ -37135,7 +37725,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="271" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -37236,7 +37826,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="272" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="6">
         <v>272</v>
       </c>
@@ -37337,7 +37927,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="273" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="6">
         <v>273</v>
       </c>
@@ -37438,7 +38028,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="274" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="6">
         <v>274</v>
       </c>
@@ -37539,7 +38129,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="275" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="6">
         <v>275</v>
       </c>
@@ -37640,7 +38230,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="276" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="6">
         <v>276</v>
       </c>
@@ -37741,7 +38331,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="277" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="6">
         <v>277</v>
       </c>
@@ -37842,7 +38432,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="278" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="6">
         <v>278</v>
       </c>
@@ -37943,7 +38533,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="279" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="6">
         <v>279</v>
       </c>
@@ -38044,7 +38634,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="280" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="6">
         <v>280</v>
       </c>
@@ -38145,7 +38735,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="281" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="6">
         <v>281</v>
       </c>
@@ -38246,7 +38836,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="282" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="6">
         <v>282</v>
       </c>
@@ -38347,7 +38937,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="283" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="6">
         <v>283</v>
       </c>
@@ -38448,7 +39038,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="284" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="6">
         <v>284</v>
       </c>
@@ -38549,7 +39139,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="285" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="6">
         <v>285</v>
       </c>
@@ -38650,7 +39240,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="286" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="6">
         <v>286</v>
       </c>
@@ -38751,7 +39341,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="287" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="6">
         <v>287</v>
       </c>
@@ -38852,7 +39442,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="288" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="6">
         <v>288</v>
       </c>
@@ -38953,7 +39543,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="289" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="6">
         <v>289</v>
       </c>
@@ -39054,7 +39644,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="290" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="6">
         <v>290</v>
       </c>
@@ -39155,7 +39745,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="291" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="6">
         <v>291</v>
       </c>
@@ -39256,7 +39846,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="292" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="6">
         <v>292</v>
       </c>
@@ -39357,7 +39947,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="293" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="6">
         <v>293</v>
       </c>
@@ -39458,7 +40048,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="294" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="6">
         <v>294</v>
       </c>
@@ -39559,7 +40149,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="295" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="6">
         <v>295</v>
       </c>
@@ -39660,7 +40250,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="296" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="6">
         <v>296</v>
       </c>
@@ -39761,7 +40351,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="297" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="6">
         <v>297</v>
       </c>
@@ -39862,7 +40452,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="298" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="6">
         <v>298</v>
       </c>
@@ -39963,7 +40553,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="299" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="6">
         <v>299</v>
       </c>
@@ -40064,7 +40654,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="300" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="6">
         <v>300</v>
       </c>
@@ -40165,7 +40755,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="301" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="6">
         <v>301</v>
       </c>
@@ -40266,7 +40856,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="302" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="6">
         <v>302</v>
       </c>
@@ -40367,7 +40957,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="303" spans="1:33" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:33" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="6">
         <v>303</v>
       </c>
@@ -40468,15 +41058,15 @@
         <v>332</v>
       </c>
     </row>
-    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="6">
         <v>304</v>
       </c>
       <c r="B304" s="70" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="C304" s="29" t="s">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="D304" s="53" t="s">
         <v>332</v>
@@ -40500,26 +41090,26 @@
         <v>644</v>
       </c>
       <c r="K304" s="42" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="L304" s="41" t="s">
         <v>710</v>
       </c>
       <c r="M304" s="42" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="N304" s="43" t="s">
         <v>1</v>
       </c>
       <c r="O304" s="42" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="P304" s="74" t="str">
         <f t="shared" ref="P304:P308" si="0">IF(Q304="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q304" s="75" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="R304" s="41" t="s">
         <v>332</v>
@@ -40570,15 +41160,15 @@
         <v>332</v>
       </c>
     </row>
-    <row r="305" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="6">
         <v>305</v>
       </c>
       <c r="B305" s="70" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="C305" s="29" t="s">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="D305" s="53" t="s">
         <v>332</v>
@@ -40602,26 +41192,26 @@
         <v>644</v>
       </c>
       <c r="K305" s="42" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="L305" s="41" t="s">
         <v>710</v>
       </c>
       <c r="M305" s="42" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="N305" s="43" t="s">
         <v>1</v>
       </c>
       <c r="O305" s="42" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="P305" s="74" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q305" s="75" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="R305" s="41" t="s">
         <v>332</v>
@@ -40672,15 +41262,15 @@
         <v>332</v>
       </c>
     </row>
-    <row r="306" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="6">
         <v>306</v>
       </c>
       <c r="B306" s="70" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="C306" s="29" t="s">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="D306" s="53" t="s">
         <v>332</v>
@@ -40704,26 +41294,26 @@
         <v>644</v>
       </c>
       <c r="K306" s="42" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="L306" s="41" t="s">
         <v>710</v>
       </c>
       <c r="M306" s="42" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="N306" s="43" t="s">
         <v>1</v>
       </c>
       <c r="O306" s="42" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="P306" s="74" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q306" s="75" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="R306" s="41" t="s">
         <v>332</v>
@@ -40774,15 +41364,15 @@
         <v>332</v>
       </c>
     </row>
-    <row r="307" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="6">
         <v>307</v>
       </c>
       <c r="B307" s="70" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="C307" s="29" t="s">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="D307" s="53" t="s">
         <v>332</v>
@@ -40806,26 +41396,26 @@
         <v>644</v>
       </c>
       <c r="K307" s="42" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="L307" s="41" t="s">
         <v>710</v>
       </c>
       <c r="M307" s="42" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="N307" s="43" t="s">
         <v>1</v>
       </c>
       <c r="O307" s="42" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="P307" s="74" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q307" s="75" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="R307" s="41" t="s">
         <v>332</v>
@@ -40876,15 +41466,15 @@
         <v>332</v>
       </c>
     </row>
-    <row r="308" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="6">
         <v>308</v>
       </c>
       <c r="B308" s="70" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C308" s="29" t="s">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="D308" s="53" t="s">
         <v>332</v>
@@ -40908,26 +41498,26 @@
         <v>644</v>
       </c>
       <c r="K308" s="42" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="L308" s="41" t="s">
         <v>710</v>
       </c>
       <c r="M308" s="42" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="N308" s="43" t="s">
         <v>1</v>
       </c>
       <c r="O308" s="42" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="P308" s="74" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q308" s="75" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="R308" s="41" t="s">
         <v>332</v>
@@ -40981,70 +41571,70 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B303 B309:B1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304:B308">
-    <cfRule type="duplicateValues" dxfId="13" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:U4">
-    <cfRule type="cellIs" dxfId="11" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="28" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:W303 V309:W1048576">
-    <cfRule type="cellIs" dxfId="10" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y308 R304:W308">
-    <cfRule type="cellIs" dxfId="8" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AA308">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1:AC308">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1:AE308">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1:AG308">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96204BFE-BC59-486D-B478-010B00289A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B5FF71-32A4-43B6-8128-2FA8CBD2BAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11110" uniqueCount="1077">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -3319,6 +3319,9 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -3920,169 +3923,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{001CC4A1-5641-437E-9DC4-857BB9658EC6}"/>
   </cellStyles>
-  <dxfs count="46">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="28">
     <dxf>
       <font>
         <b val="0"/>
@@ -4317,6 +4158,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4857,7 +4706,7 @@
       </c>
       <c r="B18" s="38">
         <f ca="1">NOW()</f>
-        <v>46268.459468981484</v>
+        <v>46268.685053472225</v>
       </c>
       <c r="C18" s="37" t="s">
         <v>704</v>
@@ -5111,7 +4960,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFFE5C0-D3D8-4876-B71B-E260AD929073}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AD52"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" style="39" bestFit="1" customWidth="1"/>
@@ -5139,10 +4988,11 @@
     <col min="27" max="27" width="44.83203125" style="39" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.5" style="39" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="6.6640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.83203125" style="39"/>
+    <col min="30" max="30" width="10.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="8.83203125" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>649</v>
       </c>
@@ -5230,8 +5080,11 @@
       <c r="AC1" s="20" t="s">
         <v>672</v>
       </c>
+      <c r="AD1" s="20" t="s">
+        <v>1076</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48">
         <v>2</v>
       </c>
@@ -5327,8 +5180,11 @@
       <c r="AC2" s="33" t="s">
         <v>717</v>
       </c>
+      <c r="AD2" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="48">
         <v>3</v>
       </c>
@@ -5424,8 +5280,11 @@
       <c r="AC3" s="33" t="s">
         <v>718</v>
       </c>
+      <c r="AD3" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="48">
         <v>4</v>
       </c>
@@ -5521,8 +5380,11 @@
       <c r="AC4" s="33" t="s">
         <v>719</v>
       </c>
+      <c r="AD4" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="48">
         <v>5</v>
       </c>
@@ -5618,8 +5480,11 @@
       <c r="AC5" s="33" t="s">
         <v>720</v>
       </c>
+      <c r="AD5" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="48">
         <v>6</v>
       </c>
@@ -5715,8 +5580,11 @@
       <c r="AC6" s="33" t="s">
         <v>721</v>
       </c>
+      <c r="AD6" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="48">
         <v>7</v>
       </c>
@@ -5812,8 +5680,11 @@
       <c r="AC7" s="33" t="s">
         <v>722</v>
       </c>
+      <c r="AD7" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="48">
         <v>8</v>
       </c>
@@ -5909,8 +5780,11 @@
       <c r="AC8" s="33" t="s">
         <v>723</v>
       </c>
+      <c r="AD8" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="48">
         <v>9</v>
       </c>
@@ -6006,8 +5880,11 @@
       <c r="AC9" s="33" t="s">
         <v>724</v>
       </c>
+      <c r="AD9" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="48">
         <v>10</v>
       </c>
@@ -6103,8 +5980,11 @@
       <c r="AC10" s="33" t="s">
         <v>725</v>
       </c>
+      <c r="AD10" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="48">
         <v>11</v>
       </c>
@@ -6200,8 +6080,11 @@
       <c r="AC11" s="33" t="s">
         <v>341</v>
       </c>
+      <c r="AD11" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="48">
         <v>12</v>
       </c>
@@ -6297,8 +6180,11 @@
       <c r="AC12" s="33" t="s">
         <v>726</v>
       </c>
+      <c r="AD12" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="48">
         <v>13</v>
       </c>
@@ -6394,8 +6280,11 @@
       <c r="AC13" s="33" t="s">
         <v>727</v>
       </c>
+      <c r="AD13" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="48">
         <v>14</v>
       </c>
@@ -6491,8 +6380,11 @@
       <c r="AC14" s="33" t="s">
         <v>728</v>
       </c>
+      <c r="AD14" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="48">
         <v>15</v>
       </c>
@@ -6588,8 +6480,11 @@
       <c r="AC15" s="55" t="s">
         <v>802</v>
       </c>
+      <c r="AD15" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="48">
         <v>16</v>
       </c>
@@ -6685,8 +6580,11 @@
       <c r="AC16" s="55" t="s">
         <v>803</v>
       </c>
+      <c r="AD16" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="48">
         <v>17</v>
       </c>
@@ -6782,8 +6680,11 @@
       <c r="AC17" s="55" t="s">
         <v>804</v>
       </c>
+      <c r="AD17" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="48">
         <v>18</v>
       </c>
@@ -6879,8 +6780,11 @@
       <c r="AC18" s="55" t="s">
         <v>805</v>
       </c>
+      <c r="AD18" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="48">
         <v>19</v>
       </c>
@@ -6976,8 +6880,11 @@
       <c r="AC19" s="55" t="s">
         <v>806</v>
       </c>
+      <c r="AD19" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="48">
         <v>20</v>
       </c>
@@ -7073,8 +6980,11 @@
       <c r="AC20" s="55" t="s">
         <v>807</v>
       </c>
+      <c r="AD20" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="48">
         <v>21</v>
       </c>
@@ -7170,8 +7080,11 @@
       <c r="AC21" s="55" t="s">
         <v>808</v>
       </c>
+      <c r="AD21" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="48">
         <v>22</v>
       </c>
@@ -7267,8 +7180,11 @@
       <c r="AC22" s="55" t="s">
         <v>809</v>
       </c>
+      <c r="AD22" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="48">
         <v>23</v>
       </c>
@@ -7364,8 +7280,11 @@
       <c r="AC23" s="55" t="s">
         <v>810</v>
       </c>
+      <c r="AD23" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="48">
         <v>24</v>
       </c>
@@ -7461,8 +7380,11 @@
       <c r="AC24" s="55" t="s">
         <v>811</v>
       </c>
+      <c r="AD24" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="48">
         <v>25</v>
       </c>
@@ -7558,8 +7480,11 @@
       <c r="AC25" s="55" t="s">
         <v>812</v>
       </c>
+      <c r="AD25" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="48">
         <v>26</v>
       </c>
@@ -7655,8 +7580,11 @@
       <c r="AC26" s="55" t="s">
         <v>813</v>
       </c>
+      <c r="AD26" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="48">
         <v>27</v>
       </c>
@@ -7752,8 +7680,11 @@
       <c r="AC27" s="55" t="s">
         <v>814</v>
       </c>
+      <c r="AD27" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="48">
         <v>28</v>
       </c>
@@ -7849,8 +7780,11 @@
       <c r="AC28" s="55" t="s">
         <v>815</v>
       </c>
+      <c r="AD28" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="48">
         <v>29</v>
       </c>
@@ -7946,8 +7880,11 @@
       <c r="AC29" s="55" t="s">
         <v>816</v>
       </c>
+      <c r="AD29" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="48">
         <v>30</v>
       </c>
@@ -8043,8 +7980,11 @@
       <c r="AC30" s="55" t="s">
         <v>817</v>
       </c>
+      <c r="AD30" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="48">
         <v>31</v>
       </c>
@@ -8140,8 +8080,11 @@
       <c r="AC31" s="55" t="s">
         <v>818</v>
       </c>
+      <c r="AD31" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="48">
         <v>32</v>
       </c>
@@ -8237,8 +8180,11 @@
       <c r="AC32" s="55" t="s">
         <v>819</v>
       </c>
+      <c r="AD32" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48">
         <v>33</v>
       </c>
@@ -8334,8 +8280,11 @@
       <c r="AC33" s="55" t="s">
         <v>820</v>
       </c>
+      <c r="AD33" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="48">
         <v>34</v>
       </c>
@@ -8431,8 +8380,11 @@
       <c r="AC34" s="55" t="s">
         <v>821</v>
       </c>
+      <c r="AD34" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="48">
         <v>35</v>
       </c>
@@ -8528,8 +8480,11 @@
       <c r="AC35" s="55" t="s">
         <v>822</v>
       </c>
+      <c r="AD35" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="48">
         <v>36</v>
       </c>
@@ -8625,8 +8580,11 @@
       <c r="AC36" s="55" t="s">
         <v>823</v>
       </c>
+      <c r="AD36" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="48">
         <v>37</v>
       </c>
@@ -8722,8 +8680,11 @@
       <c r="AC37" s="55" t="s">
         <v>824</v>
       </c>
+      <c r="AD37" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="48">
         <v>38</v>
       </c>
@@ -8819,8 +8780,11 @@
       <c r="AC38" s="55" t="s">
         <v>825</v>
       </c>
+      <c r="AD38" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="48">
         <v>39</v>
       </c>
@@ -8916,8 +8880,11 @@
       <c r="AC39" s="55" t="s">
         <v>826</v>
       </c>
+      <c r="AD39" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="48">
         <v>40</v>
       </c>
@@ -9013,8 +8980,11 @@
       <c r="AC40" s="55" t="s">
         <v>827</v>
       </c>
+      <c r="AD40" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="48">
         <v>41</v>
       </c>
@@ -9110,8 +9080,11 @@
       <c r="AC41" s="55" t="s">
         <v>828</v>
       </c>
+      <c r="AD41" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="48">
         <v>42</v>
       </c>
@@ -9207,8 +9180,11 @@
       <c r="AC42" s="55" t="s">
         <v>829</v>
       </c>
+      <c r="AD42" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="48">
         <v>43</v>
       </c>
@@ -9304,8 +9280,11 @@
       <c r="AC43" s="55" t="s">
         <v>830</v>
       </c>
+      <c r="AD43" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="48">
         <v>44</v>
       </c>
@@ -9401,8 +9380,11 @@
       <c r="AC44" s="55" t="s">
         <v>831</v>
       </c>
+      <c r="AD44" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="48">
         <v>45</v>
       </c>
@@ -9498,8 +9480,11 @@
       <c r="AC45" s="55" t="s">
         <v>832</v>
       </c>
+      <c r="AD45" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="48">
         <v>46</v>
       </c>
@@ -9595,8 +9580,11 @@
       <c r="AC46" s="55" t="s">
         <v>833</v>
       </c>
+      <c r="AD46" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:30" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="48">
         <v>47</v>
       </c>
@@ -9692,8 +9680,11 @@
       <c r="AC47" s="55" t="s">
         <v>834</v>
       </c>
+      <c r="AD47" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="48">
         <v>48</v>
       </c>
@@ -9789,8 +9780,11 @@
       <c r="AC48" s="69" t="s">
         <v>332</v>
       </c>
+      <c r="AD48" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="48">
         <v>49</v>
       </c>
@@ -9886,8 +9880,11 @@
       <c r="AC49" s="69" t="s">
         <v>332</v>
       </c>
+      <c r="AD49" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:30" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="48">
         <v>50</v>
       </c>
@@ -9983,8 +9980,11 @@
       <c r="AC50" s="69" t="s">
         <v>332</v>
       </c>
+      <c r="AD50" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:30" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="48">
         <v>51</v>
       </c>
@@ -10080,8 +10080,11 @@
       <c r="AC51" s="69" t="s">
         <v>332</v>
       </c>
+      <c r="AD51" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:30" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="48">
         <v>52</v>
       </c>
@@ -10177,39 +10180,42 @@
       <c r="AC52" s="69" t="s">
         <v>332</v>
       </c>
+      <c r="AD52" s="69" t="s">
+        <v>332</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B52">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E52:F52">
-    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="44" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F51">
-    <cfRule type="duplicateValues" dxfId="43" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R14">
-    <cfRule type="cellIs" dxfId="42" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R15:R47">
-    <cfRule type="duplicateValues" dxfId="41" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="39" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC15:AC47">
-    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="42"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -10360,7 +10366,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10405,7 +10411,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41571,70 +41577,70 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B303 B309:B1048576">
-    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304:B308">
-    <cfRule type="duplicateValues" dxfId="32" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:U4">
-    <cfRule type="cellIs" dxfId="30" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="28" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:W303 V309:W1048576">
-    <cfRule type="cellIs" dxfId="29" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="28" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y308 R304:W308">
-    <cfRule type="cellIs" dxfId="27" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="26" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AA308">
-    <cfRule type="cellIs" dxfId="25" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1:AC308">
-    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1:AE308">
-    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1:AG308">
-    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_3R.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B5FF71-32A4-43B6-8128-2FA8CBD2BAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42448CB-DB6A-4A35-B71B-3F39CB70C6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11110" uniqueCount="1077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11145" uniqueCount="1088">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -3183,18 +3183,6 @@
     <t>Atributo Ifc</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -3306,9 +3294,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -3322,6 +3307,54 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>API Método</t>
+  </si>
+  <si>
+    <t>Função Auxiliar</t>
+  </si>
+  <si>
+    <t>API Plataforma</t>
+  </si>
+  <si>
+    <t>API Macros</t>
+  </si>
+  <si>
+    <t>Função Global</t>
+  </si>
+  <si>
+    <t>Função Local</t>
+  </si>
+  <si>
+    <t>Função Filtro</t>
+  </si>
+  <si>
+    <t>API Método Visual</t>
+  </si>
+  <si>
+    <t>Bloco de Código</t>
+  </si>
+  <si>
+    <t>API Macros Visuais</t>
   </si>
 </sst>
 </file>
@@ -3698,7 +3731,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3917,13 +3950,86 @@
     <xf numFmtId="0" fontId="7" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{001CC4A1-5641-437E-9DC4-857BB9658EC6}"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="34">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4158,14 +4264,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4706,7 +4804,7 @@
       </c>
       <c r="B18" s="38">
         <f ca="1">NOW()</f>
-        <v>46268.685053472225</v>
+        <v>46273.463485069442</v>
       </c>
       <c r="C18" s="37" t="s">
         <v>704</v>
@@ -4977,7 +5075,7 @@
     <col min="16" max="16" width="78.1640625" style="39" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="62.33203125" style="39" customWidth="1"/>
     <col min="18" max="18" width="54.5" style="39" customWidth="1"/>
-    <col min="19" max="19" width="5" style="66" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5" style="78" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.1640625" style="39" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" style="39" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
@@ -5047,7 +5145,7 @@
       <c r="R1" s="32" t="s">
         <v>699</v>
       </c>
-      <c r="S1" s="20" t="s">
+      <c r="S1" s="21" t="s">
         <v>693</v>
       </c>
       <c r="T1" s="20" t="s">
@@ -5081,7 +5179,7 @@
         <v>672</v>
       </c>
       <c r="AD1" s="20" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="2" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5143,7 +5241,7 @@
       <c r="R2" s="52" t="s">
         <v>951</v>
       </c>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T2" s="51" t="str">
@@ -5243,7 +5341,7 @@
       <c r="R3" s="52" t="s">
         <v>954</v>
       </c>
-      <c r="S3" s="33" t="s">
+      <c r="S3" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T3" s="51" t="str">
@@ -5343,7 +5441,7 @@
       <c r="R4" s="52" t="s">
         <v>957</v>
       </c>
-      <c r="S4" s="33" t="s">
+      <c r="S4" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T4" s="51" t="str">
@@ -5443,7 +5541,7 @@
       <c r="R5" s="52" t="s">
         <v>960</v>
       </c>
-      <c r="S5" s="33" t="s">
+      <c r="S5" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T5" s="51" t="str">
@@ -5543,7 +5641,7 @@
       <c r="R6" s="52" t="s">
         <v>963</v>
       </c>
-      <c r="S6" s="33" t="s">
+      <c r="S6" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T6" s="51" t="str">
@@ -5643,7 +5741,7 @@
       <c r="R7" s="52" t="s">
         <v>966</v>
       </c>
-      <c r="S7" s="33" t="s">
+      <c r="S7" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T7" s="51" t="str">
@@ -5743,7 +5841,7 @@
       <c r="R8" s="52" t="s">
         <v>969</v>
       </c>
-      <c r="S8" s="33" t="s">
+      <c r="S8" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T8" s="51" t="str">
@@ -5843,7 +5941,7 @@
       <c r="R9" s="52" t="s">
         <v>972</v>
       </c>
-      <c r="S9" s="33" t="s">
+      <c r="S9" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T9" s="51" t="str">
@@ -5943,7 +6041,7 @@
       <c r="R10" s="52" t="s">
         <v>975</v>
       </c>
-      <c r="S10" s="33" t="s">
+      <c r="S10" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T10" s="51" t="str">
@@ -6043,7 +6141,7 @@
       <c r="R11" s="52" t="s">
         <v>978</v>
       </c>
-      <c r="S11" s="33" t="s">
+      <c r="S11" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T11" s="51" t="str">
@@ -6143,7 +6241,7 @@
       <c r="R12" s="52" t="s">
         <v>981</v>
       </c>
-      <c r="S12" s="33" t="s">
+      <c r="S12" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T12" s="51" t="str">
@@ -6243,7 +6341,7 @@
       <c r="R13" s="52" t="s">
         <v>984</v>
       </c>
-      <c r="S13" s="33" t="s">
+      <c r="S13" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T13" s="51" t="str">
@@ -6343,7 +6441,7 @@
       <c r="R14" s="52" t="s">
         <v>987</v>
       </c>
-      <c r="S14" s="33" t="s">
+      <c r="S14" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T14" s="51" t="str">
@@ -6419,7 +6517,7 @@
         <v>332</v>
       </c>
       <c r="L15" s="50" t="str">
-        <f t="shared" ref="L15:L47" si="4">CONCATENATE("", C15)</f>
+        <f t="shared" ref="L15:M48" si="4">CONCATENATE("", C15)</f>
         <v>Normativos</v>
       </c>
       <c r="M15" s="50" t="str">
@@ -6443,7 +6541,7 @@
       <c r="R15" s="55" t="s">
         <v>869</v>
       </c>
-      <c r="S15" s="33" t="s">
+      <c r="S15" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T15" s="51" t="str">
@@ -6543,7 +6641,7 @@
       <c r="R16" s="55" t="s">
         <v>870</v>
       </c>
-      <c r="S16" s="33" t="s">
+      <c r="S16" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T16" s="51" t="str">
@@ -6643,7 +6741,7 @@
       <c r="R17" s="55" t="s">
         <v>871</v>
       </c>
-      <c r="S17" s="33" t="s">
+      <c r="S17" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T17" s="51" t="str">
@@ -6743,7 +6841,7 @@
       <c r="R18" s="55" t="s">
         <v>872</v>
       </c>
-      <c r="S18" s="33" t="s">
+      <c r="S18" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T18" s="51" t="str">
@@ -6843,7 +6941,7 @@
       <c r="R19" s="55" t="s">
         <v>873</v>
       </c>
-      <c r="S19" s="33" t="s">
+      <c r="S19" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T19" s="51" t="str">
@@ -6943,7 +7041,7 @@
       <c r="R20" s="55" t="s">
         <v>874</v>
       </c>
-      <c r="S20" s="33" t="s">
+      <c r="S20" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T20" s="51" t="str">
@@ -7043,7 +7141,7 @@
       <c r="R21" s="55" t="s">
         <v>875</v>
       </c>
-      <c r="S21" s="33" t="s">
+      <c r="S21" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T21" s="51" t="str">
@@ -7143,7 +7241,7 @@
       <c r="R22" s="55" t="s">
         <v>876</v>
       </c>
-      <c r="S22" s="33" t="s">
+      <c r="S22" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T22" s="51" t="str">
@@ -7243,7 +7341,7 @@
       <c r="R23" s="55" t="s">
         <v>877</v>
       </c>
-      <c r="S23" s="33" t="s">
+      <c r="S23" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T23" s="51" t="str">
@@ -7343,7 +7441,7 @@
       <c r="R24" s="55" t="s">
         <v>878</v>
       </c>
-      <c r="S24" s="33" t="s">
+      <c r="S24" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T24" s="51" t="str">
@@ -7443,7 +7541,7 @@
       <c r="R25" s="55" t="s">
         <v>879</v>
       </c>
-      <c r="S25" s="33" t="s">
+      <c r="S25" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T25" s="51" t="str">
@@ -7543,7 +7641,7 @@
       <c r="R26" s="55" t="s">
         <v>880</v>
       </c>
-      <c r="S26" s="33" t="s">
+      <c r="S26" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T26" s="51" t="str">
@@ -7643,7 +7741,7 @@
       <c r="R27" s="55" t="s">
         <v>881</v>
       </c>
-      <c r="S27" s="33" t="s">
+      <c r="S27" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T27" s="51" t="str">
@@ -7743,7 +7841,7 @@
       <c r="R28" s="55" t="s">
         <v>882</v>
       </c>
-      <c r="S28" s="33" t="s">
+      <c r="S28" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T28" s="51" t="str">
@@ -7843,7 +7941,7 @@
       <c r="R29" s="55" t="s">
         <v>883</v>
       </c>
-      <c r="S29" s="33" t="s">
+      <c r="S29" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T29" s="51" t="str">
@@ -7943,7 +8041,7 @@
       <c r="R30" s="55" t="s">
         <v>884</v>
       </c>
-      <c r="S30" s="33" t="s">
+      <c r="S30" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T30" s="51" t="str">
@@ -8043,7 +8141,7 @@
       <c r="R31" s="55" t="s">
         <v>885</v>
       </c>
-      <c r="S31" s="33" t="s">
+      <c r="S31" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T31" s="51" t="str">
@@ -8143,7 +8241,7 @@
       <c r="R32" s="55" t="s">
         <v>886</v>
       </c>
-      <c r="S32" s="33" t="s">
+      <c r="S32" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T32" s="51" t="str">
@@ -8243,7 +8341,7 @@
       <c r="R33" s="55" t="s">
         <v>887</v>
       </c>
-      <c r="S33" s="33" t="s">
+      <c r="S33" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T33" s="51" t="str">
@@ -8343,7 +8441,7 @@
       <c r="R34" s="55" t="s">
         <v>888</v>
       </c>
-      <c r="S34" s="33" t="s">
+      <c r="S34" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T34" s="51" t="str">
@@ -8443,7 +8541,7 @@
       <c r="R35" s="55" t="s">
         <v>889</v>
       </c>
-      <c r="S35" s="33" t="s">
+      <c r="S35" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T35" s="51" t="str">
@@ -8543,7 +8641,7 @@
       <c r="R36" s="55" t="s">
         <v>890</v>
       </c>
-      <c r="S36" s="33" t="s">
+      <c r="S36" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T36" s="51" t="str">
@@ -8643,7 +8741,7 @@
       <c r="R37" s="55" t="s">
         <v>891</v>
       </c>
-      <c r="S37" s="33" t="s">
+      <c r="S37" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T37" s="51" t="str">
@@ -8743,7 +8841,7 @@
       <c r="R38" s="55" t="s">
         <v>892</v>
       </c>
-      <c r="S38" s="33" t="s">
+      <c r="S38" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T38" s="51" t="str">
@@ -8843,7 +8941,7 @@
       <c r="R39" s="55" t="s">
         <v>893</v>
       </c>
-      <c r="S39" s="33" t="s">
+      <c r="S39" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T39" s="51" t="str">
@@ -8943,7 +9041,7 @@
       <c r="R40" s="55" t="s">
         <v>894</v>
       </c>
-      <c r="S40" s="33" t="s">
+      <c r="S40" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T40" s="51" t="str">
@@ -9043,7 +9141,7 @@
       <c r="R41" s="55" t="s">
         <v>895</v>
       </c>
-      <c r="S41" s="33" t="s">
+      <c r="S41" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T41" s="51" t="str">
@@ -9143,7 +9241,7 @@
       <c r="R42" s="55" t="s">
         <v>896</v>
       </c>
-      <c r="S42" s="33" t="s">
+      <c r="S42" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T42" s="51" t="str">
@@ -9243,7 +9341,7 @@
       <c r="R43" s="55" t="s">
         <v>897</v>
       </c>
-      <c r="S43" s="33" t="s">
+      <c r="S43" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T43" s="51" t="str">
@@ -9343,7 +9441,7 @@
       <c r="R44" s="55" t="s">
         <v>898</v>
       </c>
-      <c r="S44" s="33" t="s">
+      <c r="S44" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T44" s="51" t="str">
@@ -9443,7 +9541,7 @@
       <c r="R45" s="55" t="s">
         <v>899</v>
       </c>
-      <c r="S45" s="33" t="s">
+      <c r="S45" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T45" s="51" t="str">
@@ -9543,7 +9641,7 @@
       <c r="R46" s="55" t="s">
         <v>900</v>
       </c>
-      <c r="S46" s="33" t="s">
+      <c r="S46" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T46" s="51" t="str">
@@ -9643,7 +9741,7 @@
       <c r="R47" s="55" t="s">
         <v>901</v>
       </c>
-      <c r="S47" s="33" t="s">
+      <c r="S47" s="76" t="s">
         <v>332</v>
       </c>
       <c r="T47" s="51" t="str">
@@ -9684,24 +9782,24 @@
         <v>332</v>
       </c>
     </row>
-    <row r="48" spans="1:30" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="48">
         <v>48</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>1030</v>
+        <v>1072</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>1031</v>
+        <v>1073</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>1033</v>
+        <v>1074</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>1032</v>
+        <v>1075</v>
       </c>
       <c r="F48" s="29" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="G48" s="31" t="s">
         <v>332</v>
@@ -9718,45 +9816,38 @@
       <c r="K48" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="L48" s="50" t="str">
-        <f t="shared" ref="L48:O52" si="12">SUBSTITUTE(CONCATENATE("", C48), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M48" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Macros</v>
-      </c>
-      <c r="N48" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O48" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Função Auxiliar</v>
+      <c r="L48" s="50" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M48" s="50" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N48" s="50" t="s">
+        <v>1078</v>
+      </c>
+      <c r="O48" s="50" t="s">
+        <v>1079</v>
       </c>
       <c r="P48" s="33" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="Q48" s="33" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="R48" s="33" t="s">
-        <v>1058</v>
-      </c>
-      <c r="S48" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="T48" s="33" t="str">
-        <f t="shared" ref="T48:V52" si="13">SUBSTITUTE(C48, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U48" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>Macros</v>
-      </c>
-      <c r="V48" s="51" t="str">
-        <f t="shared" si="13"/>
-        <v>Métodos</v>
+        <v>1054</v>
+      </c>
+      <c r="S48" s="76" t="s">
+        <v>332</v>
+      </c>
+      <c r="T48" s="33" t="s">
+        <v>1080</v>
+      </c>
+      <c r="U48" s="33" t="s">
+        <v>1081</v>
+      </c>
+      <c r="V48" s="51" t="s">
+        <v>1078</v>
       </c>
       <c r="W48" s="33" t="s">
         <v>716</v>
@@ -9784,24 +9875,24 @@
         <v>332</v>
       </c>
     </row>
-    <row r="49" spans="1:30" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="48">
         <v>49</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>1030</v>
+        <v>1072</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>1031</v>
+        <v>1073</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>1033</v>
+        <v>1074</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>1032</v>
+        <v>1075</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="G49" s="31" t="s">
         <v>332</v>
@@ -9818,45 +9909,38 @@
       <c r="K49" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="L49" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>De API</v>
-      </c>
-      <c r="M49" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Macros</v>
-      </c>
-      <c r="N49" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O49" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Função Global</v>
+      <c r="L49" s="50" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M49" s="50" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N49" s="50" t="s">
+        <v>1078</v>
+      </c>
+      <c r="O49" s="50" t="s">
+        <v>1082</v>
       </c>
       <c r="P49" s="33" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="Q49" s="33" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="R49" s="33" t="s">
-        <v>1062</v>
-      </c>
-      <c r="S49" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="T49" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>De API</v>
-      </c>
-      <c r="U49" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>Macros</v>
-      </c>
-      <c r="V49" s="51" t="str">
-        <f t="shared" si="13"/>
-        <v>Métodos</v>
+        <v>1058</v>
+      </c>
+      <c r="S49" s="76" t="s">
+        <v>332</v>
+      </c>
+      <c r="T49" s="33" t="s">
+        <v>1080</v>
+      </c>
+      <c r="U49" s="33" t="s">
+        <v>1081</v>
+      </c>
+      <c r="V49" s="51" t="s">
+        <v>1078</v>
       </c>
       <c r="W49" s="33" t="s">
         <v>716</v>
@@ -9884,24 +9968,24 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:30" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:30" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="48">
         <v>50</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>1030</v>
+        <v>1072</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>1031</v>
+        <v>1073</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>1033</v>
+        <v>1074</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>1032</v>
+        <v>1075</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="G50" s="31" t="s">
         <v>332</v>
@@ -9918,45 +10002,38 @@
       <c r="K50" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="L50" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>De API</v>
-      </c>
-      <c r="M50" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Macros</v>
-      </c>
-      <c r="N50" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O50" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Função Local</v>
+      <c r="L50" s="50" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M50" s="50" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N50" s="50" t="s">
+        <v>1078</v>
+      </c>
+      <c r="O50" s="50" t="s">
+        <v>1083</v>
       </c>
       <c r="P50" s="33" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="Q50" s="33" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="R50" s="33" t="s">
-        <v>1066</v>
-      </c>
-      <c r="S50" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="T50" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>De API</v>
-      </c>
-      <c r="U50" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>Macros</v>
-      </c>
-      <c r="V50" s="51" t="str">
-        <f t="shared" si="13"/>
-        <v>Métodos</v>
+        <v>1062</v>
+      </c>
+      <c r="S50" s="76" t="s">
+        <v>332</v>
+      </c>
+      <c r="T50" s="33" t="s">
+        <v>1080</v>
+      </c>
+      <c r="U50" s="33" t="s">
+        <v>1081</v>
+      </c>
+      <c r="V50" s="51" t="s">
+        <v>1078</v>
       </c>
       <c r="W50" s="33" t="s">
         <v>716</v>
@@ -9984,24 +10061,24 @@
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:30" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:30" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="48">
         <v>51</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>1030</v>
+        <v>1072</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>1031</v>
+        <v>1073</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>1033</v>
+        <v>1074</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>1032</v>
+        <v>1075</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="G51" s="31" t="s">
         <v>332</v>
@@ -10018,45 +10095,38 @@
       <c r="K51" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="L51" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>De API</v>
-      </c>
-      <c r="M51" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Macros</v>
-      </c>
-      <c r="N51" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O51" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Função Filtro</v>
+      <c r="L51" s="50" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M51" s="50" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N51" s="50" t="s">
+        <v>1078</v>
+      </c>
+      <c r="O51" s="50" t="s">
+        <v>1084</v>
       </c>
       <c r="P51" s="33" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="Q51" s="33" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="R51" s="33" t="s">
-        <v>1070</v>
-      </c>
-      <c r="S51" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="T51" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>De API</v>
-      </c>
-      <c r="U51" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>Macros</v>
-      </c>
-      <c r="V51" s="51" t="str">
-        <f t="shared" si="13"/>
-        <v>Métodos</v>
+        <v>1066</v>
+      </c>
+      <c r="S51" s="76" t="s">
+        <v>332</v>
+      </c>
+      <c r="T51" s="33" t="s">
+        <v>1080</v>
+      </c>
+      <c r="U51" s="33" t="s">
+        <v>1081</v>
+      </c>
+      <c r="V51" s="51" t="s">
+        <v>1078</v>
       </c>
       <c r="W51" s="33" t="s">
         <v>716</v>
@@ -10084,24 +10154,24 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:30" s="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:30" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="48">
         <v>52</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>1030</v>
+        <v>1072</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>1031</v>
+        <v>1073</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>1033</v>
+        <v>1076</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="G52" s="31" t="s">
         <v>332</v>
@@ -10118,45 +10188,38 @@
       <c r="K52" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="L52" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>De API</v>
-      </c>
-      <c r="M52" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Macros</v>
-      </c>
-      <c r="N52" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O52" s="50" t="str">
-        <f t="shared" si="12"/>
-        <v>Bloco de Código</v>
+      <c r="L52" s="50" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M52" s="50" t="s">
+        <v>1076</v>
+      </c>
+      <c r="N52" s="50" t="s">
+        <v>1085</v>
+      </c>
+      <c r="O52" s="50" t="s">
+        <v>1086</v>
       </c>
       <c r="P52" s="33" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="Q52" s="33" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="R52" s="33" t="s">
-        <v>1075</v>
-      </c>
-      <c r="S52" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="T52" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>De API</v>
-      </c>
-      <c r="U52" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>Macros</v>
-      </c>
-      <c r="V52" s="51" t="str">
-        <f t="shared" si="13"/>
-        <v>Códigos Visuais</v>
+        <v>1070</v>
+      </c>
+      <c r="S52" s="76" t="s">
+        <v>332</v>
+      </c>
+      <c r="T52" s="33" t="s">
+        <v>1080</v>
+      </c>
+      <c r="U52" s="33" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V52" s="51" t="s">
+        <v>1085</v>
       </c>
       <c r="W52" s="33" t="s">
         <v>716</v>
@@ -10185,37 +10248,37 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B52">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B47 A48:A52">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:F52">
-    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F48:F51">
-    <cfRule type="duplicateValues" dxfId="24" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R14">
-    <cfRule type="cellIs" dxfId="23" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R15:R47">
-    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="20" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC15:AC47">
-    <cfRule type="duplicateValues" dxfId="19" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F48:F52">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F48:F52">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -10366,7 +10429,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10411,7 +10474,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41069,10 +41132,10 @@
         <v>304</v>
       </c>
       <c r="B304" s="70" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C304" s="29" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="D304" s="53" t="s">
         <v>332</v>
@@ -41096,26 +41159,26 @@
         <v>644</v>
       </c>
       <c r="K304" s="42" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="L304" s="41" t="s">
         <v>710</v>
       </c>
       <c r="M304" s="42" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="N304" s="43" t="s">
         <v>1</v>
       </c>
       <c r="O304" s="42" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="P304" s="74" t="str">
         <f t="shared" ref="P304:P308" si="0">IF(Q304="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q304" s="75" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="R304" s="41" t="s">
         <v>332</v>
@@ -41171,10 +41234,10 @@
         <v>305</v>
       </c>
       <c r="B305" s="70" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="C305" s="29" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="D305" s="53" t="s">
         <v>332</v>
@@ -41198,26 +41261,26 @@
         <v>644</v>
       </c>
       <c r="K305" s="42" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="L305" s="41" t="s">
         <v>710</v>
       </c>
       <c r="M305" s="42" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="N305" s="43" t="s">
         <v>1</v>
       </c>
       <c r="O305" s="42" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="P305" s="74" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q305" s="75" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="R305" s="41" t="s">
         <v>332</v>
@@ -41273,10 +41336,10 @@
         <v>306</v>
       </c>
       <c r="B306" s="70" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="C306" s="29" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="D306" s="53" t="s">
         <v>332</v>
@@ -41300,26 +41363,26 @@
         <v>644</v>
       </c>
       <c r="K306" s="42" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="L306" s="41" t="s">
         <v>710</v>
       </c>
       <c r="M306" s="42" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="N306" s="43" t="s">
         <v>1</v>
       </c>
       <c r="O306" s="42" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="P306" s="74" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q306" s="75" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="R306" s="41" t="s">
         <v>332</v>
@@ -41375,10 +41438,10 @@
         <v>307</v>
       </c>
       <c r="B307" s="70" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="C307" s="29" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="D307" s="53" t="s">
         <v>332</v>
@@ -41402,26 +41465,26 @@
         <v>644</v>
       </c>
       <c r="K307" s="42" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="L307" s="41" t="s">
         <v>710</v>
       </c>
       <c r="M307" s="42" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="N307" s="43" t="s">
         <v>1</v>
       </c>
       <c r="O307" s="42" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="P307" s="74" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q307" s="75" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="R307" s="41" t="s">
         <v>332</v>
@@ -41477,10 +41540,10 @@
         <v>308</v>
       </c>
       <c r="B308" s="70" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="C308" s="29" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="D308" s="53" t="s">
         <v>332</v>
@@ -41504,26 +41567,26 @@
         <v>644</v>
       </c>
       <c r="K308" s="42" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="L308" s="41" t="s">
         <v>710</v>
       </c>
       <c r="M308" s="42" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="N308" s="43" t="s">
         <v>1</v>
       </c>
       <c r="O308" s="42" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="P308" s="74" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q308" s="75" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="R308" s="41" t="s">
         <v>332</v>
@@ -41577,70 +41640,70 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B303 B309:B1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304:B308">
-    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:U4">
-    <cfRule type="cellIs" dxfId="11" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="28" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:W303 V309:W1048576">
-    <cfRule type="cellIs" dxfId="10" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y308 R304:W308">
-    <cfRule type="cellIs" dxfId="8" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AA308">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1:AC308">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1:AE308">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1:AG308">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
